--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4458" uniqueCount="1433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4494" uniqueCount="1432">
   <si>
     <t>##var</t>
   </si>
@@ -3212,9 +3212,6 @@
   </si>
   <si>
     <t>https://www.xiaohongshu.com/user/profile/647bc1b5000000001001f13a</t>
-  </si>
-  <si>
-    <t>Playtest|Release|Demo</t>
   </si>
   <si>
     <t>Test01</t>
@@ -15857,7 +15854,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>995</v>
+        <v>798</v>
       </c>
       <c r="H10" t="s">
         <v>982</v>
@@ -15913,7 +15910,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>995</v>
+        <v>798</v>
       </c>
       <c r="H11" t="s">
         <v>987</v>
@@ -16019,7 +16016,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>995</v>
+        <v>798</v>
       </c>
       <c r="H13" t="s">
         <v>973</v>
@@ -16125,7 +16122,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>995</v>
+        <v>798</v>
       </c>
       <c r="H15" t="s">
         <v>992</v>
@@ -16169,7 +16166,7 @@
         <v>410001</v>
       </c>
       <c r="C16" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D16">
         <v>2000</v>
@@ -16181,13 +16178,13 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
+        <v>996</v>
+      </c>
+      <c r="H16" t="s">
         <v>997</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>998</v>
-      </c>
-      <c r="I16" t="s">
-        <v>999</v>
       </c>
       <c r="J16" t="s">
         <v>975</v>
@@ -16225,7 +16222,7 @@
         <v>410002</v>
       </c>
       <c r="C17" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D17">
         <v>2000</v>
@@ -16237,13 +16234,13 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
+        <v>996</v>
+      </c>
+      <c r="H17" t="s">
         <v>997</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>998</v>
-      </c>
-      <c r="I17" t="s">
-        <v>999</v>
       </c>
       <c r="J17" t="s">
         <v>975</v>
@@ -16281,7 +16278,7 @@
         <v>410003</v>
       </c>
       <c r="C18" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D18">
         <v>2000</v>
@@ -16293,13 +16290,13 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
+        <v>996</v>
+      </c>
+      <c r="H18" t="s">
         <v>997</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>998</v>
-      </c>
-      <c r="I18" t="s">
-        <v>999</v>
       </c>
       <c r="J18" t="s">
         <v>975</v>
@@ -16337,7 +16334,7 @@
         <v>410004</v>
       </c>
       <c r="C19" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D19">
         <v>2000</v>
@@ -16349,13 +16346,13 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
+        <v>996</v>
+      </c>
+      <c r="H19" t="s">
         <v>997</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>998</v>
-      </c>
-      <c r="I19" t="s">
-        <v>999</v>
       </c>
       <c r="J19" t="s">
         <v>975</v>
@@ -16388,8 +16385,205 @@
         <v>410104</v>
       </c>
     </row>
-    <row r="23" spans="2:20">
-      <c r="G23" s="16"/>
+    <row r="20" customFormat="1" spans="2:20">
+      <c r="B20">
+        <v>2001</v>
+      </c>
+      <c r="C20" t="s">
+        <v>972</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>799</v>
+      </c>
+      <c r="H20" t="s">
+        <v>973</v>
+      </c>
+      <c r="I20" t="s">
+        <v>974</v>
+      </c>
+      <c r="J20" t="s">
+        <v>975</v>
+      </c>
+      <c r="K20" t="s">
+        <v>976</v>
+      </c>
+      <c r="L20" t="s">
+        <v>977</v>
+      </c>
+      <c r="M20" t="s">
+        <v>978</v>
+      </c>
+      <c r="N20" t="s">
+        <v>979</v>
+      </c>
+      <c r="O20">
+        <v>9001</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="2:20">
+      <c r="B21">
+        <v>2002</v>
+      </c>
+      <c r="C21" t="s">
+        <v>981</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>799</v>
+      </c>
+      <c r="H21" t="s">
+        <v>982</v>
+      </c>
+      <c r="I21" t="s">
+        <v>983</v>
+      </c>
+      <c r="J21" t="s">
+        <v>975</v>
+      </c>
+      <c r="K21" t="s">
+        <v>984</v>
+      </c>
+      <c r="L21" t="s">
+        <v>984</v>
+      </c>
+      <c r="M21" t="s">
+        <v>978</v>
+      </c>
+      <c r="N21" t="s">
+        <v>979</v>
+      </c>
+      <c r="O21">
+        <v>9001</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="2:20">
+      <c r="B22">
+        <v>2003</v>
+      </c>
+      <c r="C22" t="s">
+        <v>986</v>
+      </c>
+      <c r="D22">
+        <v>20</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>799</v>
+      </c>
+      <c r="H22" t="s">
+        <v>987</v>
+      </c>
+      <c r="I22" t="s">
+        <v>988</v>
+      </c>
+      <c r="J22" t="s">
+        <v>975</v>
+      </c>
+      <c r="K22" t="s">
+        <v>989</v>
+      </c>
+      <c r="L22" t="s">
+        <v>990</v>
+      </c>
+      <c r="M22" t="s">
+        <v>978</v>
+      </c>
+      <c r="N22" t="s">
+        <v>979</v>
+      </c>
+      <c r="O22">
+        <v>9001</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="2:20">
+      <c r="B23">
+        <v>2004</v>
+      </c>
+      <c r="C23" t="s">
+        <v>991</v>
+      </c>
+      <c r="D23">
+        <v>40</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>799</v>
+      </c>
+      <c r="H23" t="s">
+        <v>992</v>
+      </c>
+      <c r="I23" t="s">
+        <v>993</v>
+      </c>
+      <c r="J23" t="s">
+        <v>975</v>
+      </c>
+      <c r="K23" t="s">
+        <v>994</v>
+      </c>
+      <c r="L23" t="s">
+        <v>994</v>
+      </c>
+      <c r="M23" t="s">
+        <v>978</v>
+      </c>
+      <c r="N23" t="s">
+        <v>979</v>
+      </c>
+      <c r="O23">
+        <v>9001</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="2:20">
       <c r="G24" s="16"/>
@@ -16399,12 +16593,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F14 F16:F1048576">
-    <cfRule type="containsText" dxfId="8" priority="2" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16449,46 +16643,46 @@
         <v>916</v>
       </c>
       <c r="E1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H1" t="s">
         <v>1004</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1005</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1006</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1007</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1008</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1009</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>1010</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1011</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1012</v>
       </c>
       <c r="P1" t="s">
         <v>706</v>
       </c>
       <c r="Q1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="R1" t="s">
         <v>1013</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -16549,52 +16743,52 @@
         <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="14" t="s">
         <v>1017</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>1018</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H3" s="15" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>1028</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -16602,55 +16796,55 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C4" t="s">
         <v>954</v>
       </c>
       <c r="D4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E4" t="s">
         <v>1031</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>1032</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1033</v>
       </c>
       <c r="G4" t="s">
         <v>66</v>
       </c>
       <c r="H4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I4" t="s">
         <v>1034</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1035</v>
       </c>
       <c r="J4" t="s">
         <v>68</v>
       </c>
       <c r="K4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L4" t="s">
         <v>1036</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>1037</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1038</v>
       </c>
       <c r="N4" t="s">
         <v>70</v>
       </c>
       <c r="O4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="P4" t="s">
         <v>957</v>
       </c>
       <c r="Q4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="R4" t="s">
         <v>1040</v>
-      </c>
-      <c r="R4" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -16661,22 +16855,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D5" t="s">
         <v>1042</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1043</v>
       </c>
       <c r="E5" t="s">
         <v>83</v>
       </c>
       <c r="F5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G5" t="s">
         <v>1044</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>1045</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1046</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -16717,22 +16911,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D6" t="s">
         <v>1047</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1048</v>
       </c>
       <c r="E6" t="s">
         <v>83</v>
       </c>
       <c r="F6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G6" t="s">
         <v>1049</v>
       </c>
-      <c r="G6" t="s">
-        <v>1050</v>
-      </c>
       <c r="H6" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -16773,22 +16967,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D7" t="s">
         <v>1051</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1052</v>
       </c>
       <c r="E7" t="s">
         <v>83</v>
       </c>
       <c r="F7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G7" t="s">
         <v>1053</v>
       </c>
-      <c r="G7" t="s">
-        <v>1054</v>
-      </c>
       <c r="H7" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -16829,22 +17023,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D8" t="s">
         <v>1055</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1056</v>
       </c>
       <c r="E8" t="s">
         <v>83</v>
       </c>
       <c r="F8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G8" t="s">
         <v>1057</v>
       </c>
-      <c r="G8" t="s">
-        <v>1058</v>
-      </c>
       <c r="H8" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -16885,22 +17079,22 @@
         <v>401005</v>
       </c>
       <c r="C9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D9" t="s">
         <v>1059</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1060</v>
       </c>
       <c r="E9" t="s">
         <v>83</v>
       </c>
       <c r="F9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G9" t="s">
         <v>1044</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>1045</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1046</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -16941,22 +17135,22 @@
         <v>401006</v>
       </c>
       <c r="C10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D10" t="s">
         <v>1061</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1062</v>
       </c>
       <c r="E10" t="s">
         <v>83</v>
       </c>
       <c r="F10" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G10" t="s">
         <v>1049</v>
       </c>
-      <c r="G10" t="s">
-        <v>1050</v>
-      </c>
       <c r="H10" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -16997,22 +17191,22 @@
         <v>401007</v>
       </c>
       <c r="C11" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D11" t="s">
         <v>1063</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1064</v>
       </c>
       <c r="E11" t="s">
         <v>83</v>
       </c>
       <c r="F11" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G11" t="s">
         <v>1053</v>
       </c>
-      <c r="G11" t="s">
-        <v>1054</v>
-      </c>
       <c r="H11" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -17053,22 +17247,22 @@
         <v>401008</v>
       </c>
       <c r="C12" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D12" t="s">
         <v>1065</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1066</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
       </c>
       <c r="F12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G12" t="s">
         <v>1057</v>
       </c>
-      <c r="G12" t="s">
-        <v>1058</v>
-      </c>
       <c r="H12" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -17109,22 +17303,22 @@
         <v>410001</v>
       </c>
       <c r="C13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D13" t="s">
         <v>1067</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1068</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G13" t="s">
         <v>1069</v>
       </c>
-      <c r="G13" t="s">
-        <v>1070</v>
-      </c>
       <c r="H13" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -17162,22 +17356,22 @@
         <v>410002</v>
       </c>
       <c r="C14" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D14" t="s">
         <v>1071</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1072</v>
       </c>
       <c r="E14" t="s">
         <v>83</v>
       </c>
       <c r="F14" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G14" t="s">
         <v>1073</v>
       </c>
-      <c r="G14" t="s">
-        <v>1074</v>
-      </c>
       <c r="H14" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -17212,22 +17406,22 @@
         <v>410003</v>
       </c>
       <c r="C15" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D15" t="s">
         <v>1075</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1076</v>
       </c>
       <c r="E15" t="s">
         <v>83</v>
       </c>
       <c r="F15" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G15" t="s">
         <v>1077</v>
       </c>
-      <c r="G15" t="s">
-        <v>1078</v>
-      </c>
       <c r="H15" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -17262,22 +17456,22 @@
         <v>410004</v>
       </c>
       <c r="C16" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D16" t="s">
         <v>1079</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1080</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
       </c>
       <c r="F16" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G16" t="s">
         <v>1081</v>
       </c>
-      <c r="G16" t="s">
-        <v>1082</v>
-      </c>
       <c r="H16" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -17315,43 +17509,43 @@
         <v>410101</v>
       </c>
       <c r="C17" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D17" t="s">
         <v>1083</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F17" t="s">
         <v>1084</v>
       </c>
-      <c r="E17" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>1085</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
         <v>1086</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>1087</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
@@ -17368,43 +17562,43 @@
         <v>410102</v>
       </c>
       <c r="C18" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F18" t="s">
         <v>1088</v>
       </c>
-      <c r="D18" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>1089</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
         <v>1090</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>1091</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -17421,43 +17615,43 @@
         <v>410103</v>
       </c>
       <c r="C19" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F19" t="s">
         <v>1092</v>
       </c>
-      <c r="D19" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>1093</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
         <v>1094</v>
-      </c>
-      <c r="H19" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>1095</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
@@ -17474,43 +17668,43 @@
         <v>410104</v>
       </c>
       <c r="C20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F20" t="s">
         <v>1096</v>
       </c>
-      <c r="D20" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>1097</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
         <v>1098</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>1099</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
@@ -17527,7 +17721,7 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -17538,19 +17732,19 @@
         <v>402001</v>
       </c>
       <c r="C22" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D22" t="s">
         <v>1101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1102</v>
       </c>
       <c r="E22" t="s">
         <v>83</v>
       </c>
       <c r="F22" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G22" t="s">
         <v>1103</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1104</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -17588,19 +17782,19 @@
         <v>402002</v>
       </c>
       <c r="C23" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D23" t="s">
         <v>1105</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1106</v>
       </c>
       <c r="E23" t="s">
         <v>83</v>
       </c>
       <c r="F23" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G23" t="s">
         <v>1107</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1108</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -17635,19 +17829,19 @@
         <v>402003</v>
       </c>
       <c r="C24" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D24" t="s">
         <v>1109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1110</v>
       </c>
       <c r="E24" t="s">
         <v>83</v>
       </c>
       <c r="F24" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G24" t="s">
         <v>1111</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1112</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -17682,7 +17876,7 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -17693,43 +17887,43 @@
         <v>403001</v>
       </c>
       <c r="C26" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D26" t="s">
         <v>1114</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>1115</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>1116</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>1117</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
         <v>1118</v>
-      </c>
-      <c r="H26" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" t="b">
-        <v>1</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>1119</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -17746,40 +17940,40 @@
         <v>403002</v>
       </c>
       <c r="C27" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D27" t="s">
         <v>1120</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F27" t="s">
         <v>1121</v>
       </c>
-      <c r="E27" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>1122</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
         <v>1123</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" t="b">
-        <v>1</v>
-      </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>1124</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -17796,20 +17990,20 @@
         <v>403003</v>
       </c>
       <c r="C28" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D28" t="s">
         <v>1125</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F28" t="s">
         <v>1126</v>
       </c>
-      <c r="E28" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>1127</v>
       </c>
-      <c r="G28" t="s">
-        <v>1128</v>
-      </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
@@ -17829,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -17846,7 +18040,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -17854,40 +18048,40 @@
         <v>404001</v>
       </c>
       <c r="C30" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D30" t="s">
         <v>1130</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1131</v>
       </c>
       <c r="E30" t="s">
         <v>686</v>
       </c>
       <c r="F30" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G30" t="s">
         <v>1132</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
         <v>1133</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="b">
-        <v>1</v>
-      </c>
-      <c r="M30" t="b">
-        <v>1</v>
-      </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>1134</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -17904,40 +18098,40 @@
         <v>404002</v>
       </c>
       <c r="C31" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D31" t="s">
         <v>1135</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1136</v>
       </c>
       <c r="E31" t="s">
         <v>686</v>
       </c>
       <c r="F31" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G31" t="s">
         <v>1137</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
         <v>1138</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M31" t="b">
-        <v>1</v>
-      </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>1139</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -17954,40 +18148,40 @@
         <v>404004</v>
       </c>
       <c r="C32" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D32" t="s">
         <v>1140</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1141</v>
       </c>
       <c r="E32" t="s">
         <v>686</v>
       </c>
       <c r="F32" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G32" t="s">
         <v>1142</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
         <v>1143</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>1144</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -18004,20 +18198,20 @@
         <v>404005</v>
       </c>
       <c r="C33" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D33" t="s">
         <v>1145</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1146</v>
       </c>
       <c r="E33" t="s">
         <v>686</v>
       </c>
       <c r="F33" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G33" t="s">
         <v>1147</v>
       </c>
-      <c r="G33" t="s">
-        <v>1148</v>
-      </c>
       <c r="I33" t="b">
         <v>0</v>
       </c>
@@ -18037,7 +18231,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -18054,20 +18248,20 @@
         <v>404007</v>
       </c>
       <c r="C34" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D34" t="s">
         <v>1149</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1150</v>
       </c>
       <c r="E34" t="s">
         <v>686</v>
       </c>
       <c r="F34" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G34" t="s">
         <v>1151</v>
       </c>
-      <c r="G34" t="s">
-        <v>1152</v>
-      </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
@@ -18087,7 +18281,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -18104,20 +18298,20 @@
         <v>404008</v>
       </c>
       <c r="C35" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D35" t="s">
         <v>1153</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1154</v>
       </c>
       <c r="E35" t="s">
         <v>686</v>
       </c>
       <c r="F35" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G35" t="s">
         <v>1155</v>
       </c>
-      <c r="G35" t="s">
-        <v>1156</v>
-      </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
@@ -18137,7 +18331,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -18154,20 +18348,20 @@
         <v>404010</v>
       </c>
       <c r="C36" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D36" t="s">
         <v>1157</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1158</v>
       </c>
       <c r="E36" t="s">
         <v>686</v>
       </c>
       <c r="F36" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G36" t="s">
         <v>1159</v>
       </c>
-      <c r="G36" t="s">
-        <v>1160</v>
-      </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
@@ -18187,7 +18381,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -18204,20 +18398,20 @@
         <v>404011</v>
       </c>
       <c r="C37" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D37" t="s">
         <v>1161</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1162</v>
       </c>
       <c r="E37" t="s">
         <v>686</v>
       </c>
       <c r="F37" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G37" t="s">
         <v>1163</v>
       </c>
-      <c r="G37" t="s">
-        <v>1164</v>
-      </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
@@ -18237,7 +18431,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -18254,20 +18448,20 @@
         <v>404013</v>
       </c>
       <c r="C38" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D38" t="s">
         <v>1165</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1166</v>
       </c>
       <c r="E38" t="s">
         <v>686</v>
       </c>
       <c r="F38" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G38" t="s">
         <v>1167</v>
       </c>
-      <c r="G38" t="s">
-        <v>1168</v>
-      </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
@@ -18287,7 +18481,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -18304,7 +18498,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -18312,20 +18506,20 @@
         <v>405001</v>
       </c>
       <c r="C40" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D40" t="s">
         <v>1170</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1171</v>
       </c>
       <c r="E40" t="s">
         <v>686</v>
       </c>
       <c r="F40" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G40" t="s">
         <v>1172</v>
       </c>
-      <c r="G40" t="s">
-        <v>1173</v>
-      </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
@@ -18345,7 +18539,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -18362,7 +18556,7 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -18370,43 +18564,43 @@
         <v>406005</v>
       </c>
       <c r="C42" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D42" t="s">
         <v>1175</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F42" t="s">
         <v>1176</v>
       </c>
-      <c r="E42" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>1177</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" t="b">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
         <v>1178</v>
-      </c>
-      <c r="H42" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" t="b">
-        <v>1</v>
-      </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>1179</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -18423,43 +18617,43 @@
         <v>406006</v>
       </c>
       <c r="C43" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D43" t="s">
         <v>1180</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F43" t="s">
         <v>1181</v>
       </c>
-      <c r="E43" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>1182</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="b">
+        <v>1</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
         <v>1183</v>
-      </c>
-      <c r="H43" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" t="b">
-        <v>1</v>
-      </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
-      <c r="O43" t="s">
-        <v>1184</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -18476,43 +18670,43 @@
         <v>406007</v>
       </c>
       <c r="C44" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D44" t="s">
         <v>1185</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F44" t="s">
         <v>1186</v>
       </c>
-      <c r="E44" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>1187</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="b">
+        <v>1</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
         <v>1188</v>
-      </c>
-      <c r="H44" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" t="b">
-        <v>1</v>
-      </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
-        <v>1189</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -18529,43 +18723,43 @@
         <v>406008</v>
       </c>
       <c r="C45" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F45" t="s">
         <v>1190</v>
       </c>
-      <c r="D45" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>1191</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
         <v>1192</v>
-      </c>
-      <c r="H45" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" t="b">
-        <v>1</v>
-      </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>1193</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -18587,7 +18781,7 @@
         <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
@@ -18646,19 +18840,19 @@
         <v>201001</v>
       </c>
       <c r="C48" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D48" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E48" t="s">
         <v>83</v>
       </c>
       <c r="F48" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G48" t="s">
         <v>1107</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1108</v>
       </c>
       <c r="H48" t="s">
         <v>10</v>
@@ -18702,19 +18896,19 @@
         <v>201002</v>
       </c>
       <c r="C49" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D49" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E49" t="s">
         <v>83</v>
       </c>
       <c r="F49" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G49" t="s">
         <v>1111</v>
-      </c>
-      <c r="G49" t="s">
-        <v>1112</v>
       </c>
       <c r="H49" t="s">
         <v>10</v>
@@ -18758,19 +18952,19 @@
         <v>204001</v>
       </c>
       <c r="C50" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D50" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E50" t="s">
         <v>83</v>
       </c>
       <c r="F50" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G50" t="s">
         <v>1103</v>
-      </c>
-      <c r="G50" t="s">
-        <v>1104</v>
       </c>
       <c r="H50" t="s">
         <v>10</v>
@@ -18811,7 +19005,7 @@
         <v>36</v>
       </c>
       <c r="B51" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -18870,43 +19064,43 @@
         <v>301001</v>
       </c>
       <c r="C52" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D52" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F52" t="s">
         <v>1121</v>
       </c>
-      <c r="E52" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>1122</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
         <v>1123</v>
-      </c>
-      <c r="H52" t="s">
-        <v>10</v>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" t="b">
-        <v>1</v>
-      </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
-      <c r="O52" t="s">
-        <v>1124</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -18926,20 +19120,20 @@
         <v>301002</v>
       </c>
       <c r="C53" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D53" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F53" t="s">
         <v>1126</v>
       </c>
-      <c r="E53" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>1127</v>
       </c>
-      <c r="G53" t="s">
-        <v>1128</v>
-      </c>
       <c r="H53" t="s">
         <v>10</v>
       </c>
@@ -18962,7 +19156,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -18979,7 +19173,7 @@
         <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -18987,22 +19181,22 @@
         <v>500005</v>
       </c>
       <c r="C55" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D55" t="s">
         <v>1202</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1203</v>
       </c>
       <c r="E55" t="s">
         <v>83</v>
       </c>
       <c r="F55" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G55" t="s">
         <v>1204</v>
       </c>
-      <c r="G55" t="s">
-        <v>1205</v>
-      </c>
       <c r="H55" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -19040,22 +19234,22 @@
         <v>500012</v>
       </c>
       <c r="C56" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D56" t="s">
         <v>1206</v>
-      </c>
-      <c r="D56" t="s">
-        <v>1207</v>
       </c>
       <c r="E56" t="s">
         <v>83</v>
       </c>
       <c r="F56" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G56" t="s">
         <v>1208</v>
       </c>
-      <c r="G56" t="s">
-        <v>1209</v>
-      </c>
       <c r="H56" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
@@ -19093,7 +19287,7 @@
         <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
@@ -19152,22 +19346,22 @@
         <v>501001</v>
       </c>
       <c r="C58" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D58" t="s">
         <v>1211</v>
-      </c>
-      <c r="D58" t="s">
-        <v>1212</v>
       </c>
       <c r="E58" t="s">
         <v>83</v>
       </c>
       <c r="F58" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G58" t="s">
         <v>1044</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>1045</v>
-      </c>
-      <c r="H58" t="s">
-        <v>1046</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
@@ -19208,22 +19402,22 @@
         <v>501002</v>
       </c>
       <c r="C59" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D59" t="s">
         <v>1213</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1214</v>
       </c>
       <c r="E59" t="s">
         <v>83</v>
       </c>
       <c r="F59" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G59" t="s">
         <v>1049</v>
       </c>
-      <c r="G59" t="s">
-        <v>1050</v>
-      </c>
       <c r="H59" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
@@ -19264,22 +19458,22 @@
         <v>501003</v>
       </c>
       <c r="C60" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D60" t="s">
         <v>1215</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1216</v>
       </c>
       <c r="E60" t="s">
         <v>83</v>
       </c>
       <c r="F60" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G60" t="s">
         <v>1053</v>
       </c>
-      <c r="G60" t="s">
-        <v>1054</v>
-      </c>
       <c r="H60" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
@@ -19320,22 +19514,22 @@
         <v>501004</v>
       </c>
       <c r="C61" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D61" t="s">
         <v>1217</v>
-      </c>
-      <c r="D61" t="s">
-        <v>1218</v>
       </c>
       <c r="E61" t="s">
         <v>83</v>
       </c>
       <c r="F61" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G61" t="s">
         <v>1057</v>
       </c>
-      <c r="G61" t="s">
-        <v>1058</v>
-      </c>
       <c r="H61" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
@@ -19376,22 +19570,22 @@
         <v>501005</v>
       </c>
       <c r="C62" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D62" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E62" t="s">
         <v>83</v>
       </c>
       <c r="F62" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G62" t="s">
         <v>1044</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>1045</v>
-      </c>
-      <c r="H62" t="s">
-        <v>1046</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
@@ -19432,22 +19626,22 @@
         <v>501006</v>
       </c>
       <c r="C63" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D63" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E63" t="s">
         <v>83</v>
       </c>
       <c r="F63" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G63" t="s">
         <v>1057</v>
       </c>
-      <c r="G63" t="s">
-        <v>1058</v>
-      </c>
       <c r="H63" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
@@ -19488,22 +19682,22 @@
         <v>501007</v>
       </c>
       <c r="C64" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D64" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E64" t="s">
         <v>83</v>
       </c>
       <c r="F64" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G64" t="s">
         <v>1057</v>
       </c>
-      <c r="G64" t="s">
-        <v>1058</v>
-      </c>
       <c r="H64" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
@@ -19541,7 +19735,7 @@
         <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C65" t="s">
         <v>10</v>
@@ -19600,43 +19794,43 @@
         <v>601001</v>
       </c>
       <c r="C66" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
         <v>1223</v>
-      </c>
-      <c r="D66" t="s">
-        <v>1176</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G66" t="s">
-        <v>1178</v>
-      </c>
-      <c r="H66" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" t="b">
-        <v>1</v>
-      </c>
-      <c r="M66" t="b">
-        <v>1</v>
-      </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
-      <c r="O66" t="s">
-        <v>1224</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
@@ -19656,43 +19850,43 @@
         <v>601002</v>
       </c>
       <c r="C67" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="M67" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
         <v>1225</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1181</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F67" t="s">
-        <v>1182</v>
-      </c>
-      <c r="G67" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H67" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" t="b">
-        <v>1</v>
-      </c>
-      <c r="M67" t="b">
-        <v>1</v>
-      </c>
-      <c r="N67" t="b">
-        <v>0</v>
-      </c>
-      <c r="O67" t="s">
-        <v>1226</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -19712,43 +19906,43 @@
         <v>601003</v>
       </c>
       <c r="C68" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+      <c r="M68" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="s">
         <v>1227</v>
-      </c>
-      <c r="D68" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F68" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G68" t="s">
-        <v>1188</v>
-      </c>
-      <c r="H68" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" t="b">
-        <v>1</v>
-      </c>
-      <c r="M68" t="b">
-        <v>1</v>
-      </c>
-      <c r="N68" t="b">
-        <v>0</v>
-      </c>
-      <c r="O68" t="s">
-        <v>1228</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -19768,43 +19962,43 @@
         <v>601004</v>
       </c>
       <c r="C69" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="M69" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
         <v>1229</v>
-      </c>
-      <c r="D69" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F69" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G69" t="s">
-        <v>1192</v>
-      </c>
-      <c r="H69" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="b">
-        <v>0</v>
-      </c>
-      <c r="L69" t="b">
-        <v>1</v>
-      </c>
-      <c r="M69" t="b">
-        <v>1</v>
-      </c>
-      <c r="N69" t="b">
-        <v>0</v>
-      </c>
-      <c r="O69" t="s">
-        <v>1230</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
@@ -19824,43 +20018,43 @@
         <v>601005</v>
       </c>
       <c r="C70" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
         <v>1231</v>
-      </c>
-      <c r="D70" t="s">
-        <v>1176</v>
-      </c>
-      <c r="E70" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F70" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G70" t="s">
-        <v>1178</v>
-      </c>
-      <c r="H70" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" t="b">
-        <v>1</v>
-      </c>
-      <c r="M70" t="b">
-        <v>1</v>
-      </c>
-      <c r="N70" t="b">
-        <v>0</v>
-      </c>
-      <c r="O70" t="s">
-        <v>1232</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -19880,43 +20074,43 @@
         <v>601006</v>
       </c>
       <c r="C71" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="b">
+        <v>1</v>
+      </c>
+      <c r="M71" t="b">
+        <v>1</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
         <v>1233</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E71" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F71" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G71" t="s">
-        <v>1192</v>
-      </c>
-      <c r="H71" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" t="b">
-        <v>1</v>
-      </c>
-      <c r="M71" t="b">
-        <v>1</v>
-      </c>
-      <c r="N71" t="b">
-        <v>0</v>
-      </c>
-      <c r="O71" t="s">
-        <v>1234</v>
       </c>
       <c r="P71" t="b">
         <v>0</v>
@@ -19936,43 +20130,43 @@
         <v>601007</v>
       </c>
       <c r="C72" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E72" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="s">
         <v>1235</v>
-      </c>
-      <c r="D72" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E72" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F72" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G72" t="s">
-        <v>1192</v>
-      </c>
-      <c r="H72" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" t="b">
-        <v>1</v>
-      </c>
-      <c r="M72" t="b">
-        <v>1</v>
-      </c>
-      <c r="N72" t="b">
-        <v>0</v>
-      </c>
-      <c r="O72" t="s">
-        <v>1236</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -19989,7 +20183,7 @@
         <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C73" t="s">
         <v>10</v>
@@ -20048,43 +20242,43 @@
         <v>700001</v>
       </c>
       <c r="C74" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D74" t="s">
         <v>1238</v>
-      </c>
-      <c r="D74" t="s">
-        <v>1239</v>
       </c>
       <c r="E74" t="s">
         <v>686</v>
       </c>
       <c r="F74" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G74" t="s">
         <v>1240</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
+        <v>10</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
         <v>1241</v>
-      </c>
-      <c r="H74" t="s">
-        <v>10</v>
-      </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" t="b">
-        <v>1</v>
-      </c>
-      <c r="M74" t="b">
-        <v>1</v>
-      </c>
-      <c r="N74" t="b">
-        <v>0</v>
-      </c>
-      <c r="O74" t="s">
-        <v>1242</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -20104,43 +20298,43 @@
         <v>700002</v>
       </c>
       <c r="C75" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D75" t="s">
         <v>1243</v>
-      </c>
-      <c r="D75" t="s">
-        <v>1244</v>
       </c>
       <c r="E75" t="s">
         <v>686</v>
       </c>
       <c r="F75" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G75" t="s">
         <v>1245</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
+        <v>10</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
         <v>1246</v>
-      </c>
-      <c r="H75" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" t="b">
-        <v>1</v>
-      </c>
-      <c r="M75" t="b">
-        <v>1</v>
-      </c>
-      <c r="N75" t="b">
-        <v>0</v>
-      </c>
-      <c r="O75" t="s">
-        <v>1247</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -20160,43 +20354,43 @@
         <v>700004</v>
       </c>
       <c r="C76" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D76" t="s">
         <v>1248</v>
-      </c>
-      <c r="D76" t="s">
-        <v>1249</v>
       </c>
       <c r="E76" t="s">
         <v>686</v>
       </c>
       <c r="F76" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G76" t="s">
         <v>1250</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>10</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
         <v>1251</v>
-      </c>
-      <c r="H76" t="s">
-        <v>10</v>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" t="b">
-        <v>1</v>
-      </c>
-      <c r="M76" t="b">
-        <v>1</v>
-      </c>
-      <c r="N76" t="b">
-        <v>0</v>
-      </c>
-      <c r="O76" t="s">
-        <v>1252</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -20216,20 +20410,20 @@
         <v>700005</v>
       </c>
       <c r="C77" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D77" t="s">
         <v>1253</v>
-      </c>
-      <c r="D77" t="s">
-        <v>1254</v>
       </c>
       <c r="E77" t="s">
         <v>686</v>
       </c>
       <c r="F77" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G77" t="s">
         <v>1255</v>
       </c>
-      <c r="G77" t="s">
-        <v>1256</v>
-      </c>
       <c r="H77" t="s">
         <v>10</v>
       </c>
@@ -20252,7 +20446,7 @@
         <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -20272,20 +20466,20 @@
         <v>700007</v>
       </c>
       <c r="C78" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D78" t="s">
         <v>1257</v>
-      </c>
-      <c r="D78" t="s">
-        <v>1258</v>
       </c>
       <c r="E78" t="s">
         <v>686</v>
       </c>
       <c r="F78" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G78" t="s">
         <v>1259</v>
       </c>
-      <c r="G78" t="s">
-        <v>1260</v>
-      </c>
       <c r="H78" t="s">
         <v>10</v>
       </c>
@@ -20308,7 +20502,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -20328,20 +20522,20 @@
         <v>700008</v>
       </c>
       <c r="C79" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D79" t="s">
         <v>1261</v>
-      </c>
-      <c r="D79" t="s">
-        <v>1262</v>
       </c>
       <c r="E79" t="s">
         <v>686</v>
       </c>
       <c r="F79" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G79" t="s">
         <v>1263</v>
       </c>
-      <c r="G79" t="s">
-        <v>1264</v>
-      </c>
       <c r="H79" t="s">
         <v>10</v>
       </c>
@@ -20364,7 +20558,7 @@
         <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -20384,20 +20578,20 @@
         <v>700010</v>
       </c>
       <c r="C80" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D80" t="s">
         <v>1265</v>
-      </c>
-      <c r="D80" t="s">
-        <v>1266</v>
       </c>
       <c r="E80" t="s">
         <v>686</v>
       </c>
       <c r="F80" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G80" t="s">
         <v>1267</v>
       </c>
-      <c r="G80" t="s">
-        <v>1268</v>
-      </c>
       <c r="H80" t="s">
         <v>10</v>
       </c>
@@ -20420,7 +20614,7 @@
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -20440,20 +20634,20 @@
         <v>700011</v>
       </c>
       <c r="C81" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D81" t="s">
         <v>1269</v>
-      </c>
-      <c r="D81" t="s">
-        <v>1270</v>
       </c>
       <c r="E81" t="s">
         <v>686</v>
       </c>
       <c r="F81" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G81" t="s">
         <v>1271</v>
       </c>
-      <c r="G81" t="s">
-        <v>1272</v>
-      </c>
       <c r="H81" t="s">
         <v>10</v>
       </c>
@@ -20476,7 +20670,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -20493,7 +20687,7 @@
         <v>36</v>
       </c>
       <c r="B82" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -20501,43 +20695,43 @@
         <v>700101</v>
       </c>
       <c r="C83" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D83" t="s">
         <v>1274</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1275</v>
       </c>
       <c r="E83" t="s">
         <v>686</v>
       </c>
       <c r="F83" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G83" t="s">
         <v>1276</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
+        <v>10</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M83" t="b">
+        <v>1</v>
+      </c>
+      <c r="N83" t="b">
+        <v>0</v>
+      </c>
+      <c r="O83" t="s">
         <v>1277</v>
-      </c>
-      <c r="H83" t="s">
-        <v>10</v>
-      </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" t="b">
-        <v>1</v>
-      </c>
-      <c r="M83" t="b">
-        <v>1</v>
-      </c>
-      <c r="N83" t="b">
-        <v>0</v>
-      </c>
-      <c r="O83" t="s">
-        <v>1278</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -20554,43 +20748,43 @@
         <v>700102</v>
       </c>
       <c r="C84" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D84" t="s">
         <v>1279</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1280</v>
       </c>
       <c r="E84" t="s">
         <v>686</v>
       </c>
       <c r="F84" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G84" t="s">
         <v>1281</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
+        <v>10</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="b">
+        <v>1</v>
+      </c>
+      <c r="M84" t="b">
+        <v>1</v>
+      </c>
+      <c r="N84" t="b">
+        <v>0</v>
+      </c>
+      <c r="O84" t="s">
         <v>1282</v>
-      </c>
-      <c r="H84" t="s">
-        <v>10</v>
-      </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="b">
-        <v>0</v>
-      </c>
-      <c r="L84" t="b">
-        <v>1</v>
-      </c>
-      <c r="M84" t="b">
-        <v>1</v>
-      </c>
-      <c r="N84" t="b">
-        <v>0</v>
-      </c>
-      <c r="O84" t="s">
-        <v>1283</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -20607,20 +20801,20 @@
         <v>700104</v>
       </c>
       <c r="C85" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D85" t="s">
         <v>1284</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1285</v>
       </c>
       <c r="E85" t="s">
         <v>686</v>
       </c>
       <c r="F85" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G85" t="s">
         <v>1286</v>
       </c>
-      <c r="G85" t="s">
-        <v>1287</v>
-      </c>
       <c r="H85" t="s">
         <v>10</v>
       </c>
@@ -20643,7 +20837,7 @@
         <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -20660,20 +20854,20 @@
         <v>700105</v>
       </c>
       <c r="C86" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D86" t="s">
         <v>1288</v>
-      </c>
-      <c r="D86" t="s">
-        <v>1289</v>
       </c>
       <c r="E86" t="s">
         <v>686</v>
       </c>
       <c r="F86" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G86" t="s">
         <v>1290</v>
       </c>
-      <c r="G86" t="s">
-        <v>1291</v>
-      </c>
       <c r="H86" t="s">
         <v>10</v>
       </c>
@@ -20696,7 +20890,7 @@
         <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -20713,20 +20907,20 @@
         <v>700107</v>
       </c>
       <c r="C87" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D87" t="s">
         <v>1292</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1293</v>
       </c>
       <c r="E87" t="s">
         <v>686</v>
       </c>
       <c r="F87" t="s">
+        <v>1293</v>
+      </c>
+      <c r="G87" t="s">
         <v>1294</v>
       </c>
-      <c r="G87" t="s">
-        <v>1295</v>
-      </c>
       <c r="H87" t="s">
         <v>10</v>
       </c>
@@ -20749,7 +20943,7 @@
         <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -20766,20 +20960,20 @@
         <v>700108</v>
       </c>
       <c r="C88" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D88" t="s">
         <v>1296</v>
-      </c>
-      <c r="D88" t="s">
-        <v>1297</v>
       </c>
       <c r="E88" t="s">
         <v>686</v>
       </c>
       <c r="F88" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G88" t="s">
         <v>1298</v>
       </c>
-      <c r="G88" t="s">
-        <v>1299</v>
-      </c>
       <c r="H88" t="s">
         <v>10</v>
       </c>
@@ -20802,7 +20996,7 @@
         <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -20819,20 +21013,20 @@
         <v>700110</v>
       </c>
       <c r="C89" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D89" t="s">
         <v>1300</v>
-      </c>
-      <c r="D89" t="s">
-        <v>1301</v>
       </c>
       <c r="E89" t="s">
         <v>686</v>
       </c>
       <c r="F89" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G89" t="s">
         <v>1302</v>
       </c>
-      <c r="G89" t="s">
-        <v>1303</v>
-      </c>
       <c r="H89" t="s">
         <v>10</v>
       </c>
@@ -20855,7 +21049,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -20872,20 +21066,20 @@
         <v>700111</v>
       </c>
       <c r="C90" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D90" t="s">
         <v>1304</v>
-      </c>
-      <c r="D90" t="s">
-        <v>1305</v>
       </c>
       <c r="E90" t="s">
         <v>686</v>
       </c>
       <c r="F90" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G90" t="s">
         <v>1306</v>
       </c>
-      <c r="G90" t="s">
-        <v>1307</v>
-      </c>
       <c r="H90" t="s">
         <v>10</v>
       </c>
@@ -20908,7 +21102,7 @@
         <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -20925,7 +21119,7 @@
         <v>36</v>
       </c>
       <c r="B91" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C91" t="s">
         <v>10</v>
@@ -20984,19 +21178,19 @@
         <v>701001</v>
       </c>
       <c r="C92" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D92" t="s">
         <v>1309</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1310</v>
       </c>
       <c r="E92" t="s">
         <v>686</v>
       </c>
       <c r="F92" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="G92" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H92" t="s">
         <v>10</v>
@@ -21020,7 +21214,7 @@
         <v>0</v>
       </c>
       <c r="O92" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -21037,7 +21231,7 @@
         <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -21045,20 +21239,20 @@
         <v>701101</v>
       </c>
       <c r="C94" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D94" t="s">
         <v>1313</v>
-      </c>
-      <c r="D94" t="s">
-        <v>1314</v>
       </c>
       <c r="E94" t="s">
         <v>686</v>
       </c>
       <c r="F94" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G94" t="s">
         <v>1315</v>
       </c>
-      <c r="G94" t="s">
-        <v>1316</v>
-      </c>
       <c r="H94" t="s">
         <v>10</v>
       </c>
@@ -21081,7 +21275,7 @@
         <v>0</v>
       </c>
       <c r="O94" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -21280,7 +21474,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{a6eac399-f71f-463f-899b-fb921f68190c}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{8119da8b-0e1e-439c-ae37-ce9416df91ee}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21294,7 +21488,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{a62d283c-bb65-443d-bf4e-c3383600f037}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{366580fa-cabb-4c51-96d3-0f5f34987cb6}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21308,7 +21502,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{2463f772-ab79-4f72-81a8-0e00c714116a}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{93a8ba2f-e042-4942-bb21-ba7fa24ae5fb}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21322,7 +21516,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{43c51112-4cf1-4aa0-a3bb-e1e59bd36fc9}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{abde639c-8488-4995-ab43-5d4e2456ed14}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21336,7 +21530,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{eec386cb-1931-4745-9e3e-a6e55099625f}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{ec17ee6e-33a0-466b-a9a4-012c433a0150}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21350,7 +21544,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{4dedf94b-e664-4ef4-91a9-6d725eeda781}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{93274468-ca86-4bb3-be9c-8a56c1848d71}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21364,7 +21558,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{2ab3034f-8228-43e9-b3eb-088e27d06b2f}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{ab6ef531-8d21-4a38-a2c4-3b35a181641d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21378,7 +21572,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{25d83a26-9799-44a2-8b9e-8e48de1e8775}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{321250a0-2d6c-4448-b92d-276f46936537}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21392,7 +21586,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{b36c3e8b-cf5d-482d-9f16-89be018da138}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{1cbb9fec-4201-4c2a-b0e7-7ed26a0b68b3}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21431,19 +21625,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D1" t="s">
         <v>1317</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>1318</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>1319</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -21500,13 +21694,13 @@
         <v>622</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>1321</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>1322</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>1323</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>661</v>
@@ -21529,13 +21723,13 @@
         <v>199999</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>662</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="6" ht="52.2" spans="1:7">
@@ -21552,13 +21746,13 @@
         <v>299999</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" t="s">
         <v>1327</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="7" ht="87" spans="1:7">
@@ -21575,13 +21769,13 @@
         <v>229999</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>1329</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>1330</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="8" ht="84" customHeight="1" spans="1:7">
@@ -21595,13 +21789,13 @@
         <v>209999</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>1332</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="5" t="s">
         <v>1333</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="9" ht="65" customHeight="1" spans="1:7">
@@ -21618,13 +21812,13 @@
         <v>299999</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" t="s">
         <v>1336</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="10" ht="69.6" spans="1:7">
@@ -21641,13 +21835,13 @@
         <v>399999</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>1338</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="9" t="s">
         <v>1339</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="11" ht="67" customHeight="1" spans="1:7">
@@ -21661,13 +21855,13 @@
         <v>399999</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>1342</v>
-      </c>
       <c r="G11" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="12" ht="34.8" spans="1:7">
@@ -21684,13 +21878,13 @@
         <v>301999</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>1343</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="9" t="s">
         <v>1344</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:7">
@@ -21704,13 +21898,13 @@
         <v>301999</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>1346</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>1347</v>
-      </c>
       <c r="G13" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="14" ht="34.8" spans="1:7">
@@ -21727,13 +21921,13 @@
         <v>302999</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>1348</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" t="s">
         <v>1349</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="15" ht="34.8" spans="1:7">
@@ -21750,13 +21944,13 @@
         <v>399999</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>1351</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" t="s">
         <v>1352</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="16" ht="87" spans="1:7">
@@ -21773,13 +21967,13 @@
         <v>499999</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>1354</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" t="s">
         <v>1355</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="17" ht="52.2" spans="1:7">
@@ -21796,13 +21990,13 @@
         <v>409999</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>1357</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" t="s">
         <v>1358</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="18" ht="52.2" spans="1:7">
@@ -21819,13 +22013,13 @@
         <v>499999</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>1360</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" t="s">
         <v>1361</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="19" ht="52.2" spans="1:7">
@@ -21842,13 +22036,13 @@
         <v>599999</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>1363</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" t="s">
         <v>1364</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="20" ht="52.2" spans="1:7">
@@ -21862,13 +22056,13 @@
         <v>500999</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>1366</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" t="s">
         <v>1367</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="21" ht="34.8" spans="1:7">
@@ -21885,13 +22079,13 @@
         <v>501999</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" t="s">
         <v>1370</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="22" ht="34.8" spans="1:7">
@@ -21908,13 +22102,13 @@
         <v>502999</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" t="s">
         <v>1373</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="23" ht="34.8" spans="1:7">
@@ -21931,13 +22125,13 @@
         <v>599999</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" t="s">
         <v>1376</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1377</v>
       </c>
     </row>
     <row r="24" ht="87" spans="1:7">
@@ -21954,13 +22148,13 @@
         <v>699999</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>1378</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" t="s">
         <v>1379</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="25" ht="34.8" spans="1:7">
@@ -21977,13 +22171,13 @@
         <v>601999</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" t="s">
         <v>1382</v>
-      </c>
-      <c r="G25" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="26" ht="34.8" spans="1:7">
@@ -22000,13 +22194,13 @@
         <v>602999</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>1384</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" t="s">
         <v>1385</v>
-      </c>
-      <c r="G26" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="27" ht="34.8" spans="1:7">
@@ -22023,13 +22217,13 @@
         <v>603999</v>
       </c>
       <c r="E27" s="6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" t="s">
         <v>1388</v>
-      </c>
-      <c r="G27" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="28" ht="34.8" spans="1:7">
@@ -22046,13 +22240,13 @@
         <v>699999</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>1390</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" t="s">
         <v>1391</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="29" ht="34.8" spans="1:7">
@@ -22069,13 +22263,13 @@
         <v>799999</v>
       </c>
       <c r="E29" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" t="s">
         <v>1394</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="30" ht="52.2" spans="1:7">
@@ -22092,13 +22286,13 @@
         <v>709999</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>1396</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" t="s">
         <v>1397</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="31" ht="34.8" spans="1:7">
@@ -22115,13 +22309,13 @@
         <v>700999</v>
       </c>
       <c r="E31" s="13" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F31" s="11" t="s">
         <v>1399</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="G31" s="9" t="s">
         <v>1400</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="32" ht="52.2" spans="1:7">
@@ -22135,13 +22329,13 @@
         <v>700999</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" t="s">
         <v>1403</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="33" ht="34.8" spans="1:7">
@@ -22155,13 +22349,13 @@
         <v>700099</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>1405</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" t="s">
         <v>1406</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="34" ht="34.8" spans="1:7">
@@ -22175,13 +22369,13 @@
         <v>700999</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>1408</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" t="s">
         <v>1409</v>
-      </c>
-      <c r="G34" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="35" ht="34.8" spans="1:7">
@@ -22198,13 +22392,13 @@
         <v>701999</v>
       </c>
       <c r="E35" s="13" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F35" s="11" t="s">
         <v>1411</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="G35" s="9" t="s">
         <v>1412</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>1413</v>
       </c>
     </row>
     <row r="36" ht="71" customHeight="1" spans="1:7">
@@ -22218,13 +22412,13 @@
         <v>701999</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>1414</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="G36" t="s">
         <v>1415</v>
-      </c>
-      <c r="G36" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="37" ht="71" customHeight="1" spans="1:7">
@@ -22238,13 +22432,13 @@
         <v>701099</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" t="s">
         <v>1418</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="38" ht="71" customHeight="1" spans="1:7">
@@ -22258,13 +22452,13 @@
         <v>701999</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G38" t="s">
         <v>1420</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>1412</v>
-      </c>
-      <c r="G38" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="39" ht="34.8" spans="1:7">
@@ -22281,13 +22475,13 @@
         <v>709999</v>
       </c>
       <c r="E39" s="6" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>1422</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="G39" t="s">
         <v>1423</v>
-      </c>
-      <c r="G39" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="40" ht="34.8" spans="1:7">
@@ -22304,13 +22498,13 @@
         <v>799999</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>1425</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="G40" t="s">
         <v>1426</v>
-      </c>
-      <c r="G40" t="s">
-        <v>1427</v>
       </c>
     </row>
     <row r="41" ht="34.8" spans="1:7">
@@ -22327,10 +22521,10 @@
         <v>999999</v>
       </c>
       <c r="E41" s="6" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>1428</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>1429</v>
       </c>
       <c r="G41" t="s">
         <v>694</v>
@@ -22350,13 +22544,13 @@
         <v>99999</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" t="s">
         <v>1431</v>
-      </c>
-      <c r="G42" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -35891,7 +36085,7 @@
       </c>
       <c r="E15" t="str">
         <f>LOOKUP(B15,Item!B:B,Item!H:H)</f>
-        <v>史诗</v>
+        <v>传说</v>
       </c>
       <c r="F15">
         <v>0.9</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="11"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -294,7 +294,7 @@
     <t>v1\Shiba\Red\</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1001.png</t>
+    <t>v3\ItemIcon\Dog_1001.png</t>
   </si>
   <si>
     <t>Item</t>
@@ -315,7 +315,7 @@
     <t>v1\Shiba\Black\</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1002.png</t>
+    <t>v3\ItemIcon\Dog_1002.png</t>
   </si>
   <si>
     <t>Cream Shiba Inu</t>
@@ -330,7 +330,7 @@
     <t>v1\Shiba\Cream\</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1003.png</t>
+    <t>v3\ItemIcon\Dog_1003.png</t>
   </si>
   <si>
     <t>Sesame Shiba Inu</t>
@@ -345,7 +345,7 @@
     <t>v1\Shiba\Sesame\</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1004.png</t>
+    <t>v3\ItemIcon\Dog_1004.png</t>
   </si>
   <si>
     <t>Skinny Red Shiba Inu</t>
@@ -354,7 +354,7 @@
     <t>瘦赤柴</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1005.png</t>
+    <t>v3\ItemIcon\Dog_1005.png</t>
   </si>
   <si>
     <t>Unshaven Red Shiba Inu</t>
@@ -363,7 +363,7 @@
     <t>胡渣赤柴</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1006.png</t>
+    <t>v3\ItemIcon\Dog_1006.png</t>
   </si>
   <si>
     <t>Sharp-faced Black and Tan Shiba Inu</t>
@@ -372,13 +372,13 @@
     <t>瘦黑柴</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1007.png</t>
+    <t>v3\ItemIcon\Dog_1007.png</t>
   </si>
   <si>
     <t>胡渣黑柴</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1008.png</t>
+    <t>v3\ItemIcon\Dog_1008.png</t>
   </si>
   <si>
     <t>Skinny Cream Shiba Inu</t>
@@ -387,7 +387,7 @@
     <t>瘦白柴</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1009.png</t>
+    <t>v3\ItemIcon\Dog_1009.png</t>
   </si>
   <si>
     <t>Unshaven Cream Shiba Inu</t>
@@ -396,7 +396,7 @@
     <t>胡渣白柴</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1010.png</t>
+    <t>v3\ItemIcon\Dog_1010.png</t>
   </si>
   <si>
     <t>Sharp-faced Sesame Shiba Inu</t>
@@ -405,7 +405,7 @@
     <t>瘦胡麻柴</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1011.png</t>
+    <t>v3\ItemIcon\Dog_1011.png</t>
   </si>
   <si>
     <t>Unshaven Sesame Shiba Inu</t>
@@ -417,7 +417,7 @@
     <t>神话</t>
   </si>
   <si>
-    <t>v0\ItemIcon\Dog_1012.png</t>
+    <t>v3\ItemIcon\Dog_1012.png</t>
   </si>
   <si>
     <t>Green Beret</t>
@@ -21474,7 +21474,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{8119da8b-0e1e-439c-ae37-ce9416df91ee}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{ee4764c1-079b-469a-8c3f-129650bbd66c}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21488,7 +21488,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{366580fa-cabb-4c51-96d3-0f5f34987cb6}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{59866497-0a92-4294-a344-76b940b87ea9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21502,7 +21502,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{93a8ba2f-e042-4942-bb21-ba7fa24ae5fb}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{76e6fbce-5ed3-4f73-a4ea-a885e8a35bf2}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21516,7 +21516,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{abde639c-8488-4995-ab43-5d4e2456ed14}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{e62e5605-788c-4350-8433-6400ca0c41b3}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21530,7 +21530,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{ec17ee6e-33a0-466b-a9a4-012c433a0150}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{ffd0f33f-e6ab-454e-93c9-925bb51a8a83}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21544,7 +21544,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{93274468-ca86-4bb3-be9c-8a56c1848d71}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{b1eae7bc-9de2-445d-8781-d9d2576af5b5}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21558,7 +21558,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{ab6ef531-8d21-4a38-a2c4-3b35a181641d}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{055c6280-ec0a-404b-a0da-2f8c83ac8019}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21572,7 +21572,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{321250a0-2d6c-4448-b92d-276f46936537}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{f90ff12e-e19f-4456-a46b-ff380d193711}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21586,7 +21586,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{1cbb9fec-4201-4c2a-b0e7-7ed26a0b68b3}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{59d54686-3969-42d3-b833-73f308ba0d3e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -432,10 +432,10 @@
     <t>优秀</t>
   </si>
   <si>
-    <t>v1\Headwear\Beret_Green.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_Beret_Green.png</t>
+    <t>v2\Headwear\Beret_Green.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_Beret_Green.png</t>
   </si>
   <si>
     <t>Red Beret</t>
@@ -444,10 +444,10 @@
     <t>红色贝雷帽</t>
   </si>
   <si>
-    <t>v1\Headwear\Beret_Red.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_Beret_Red.png</t>
+    <t>v2\Headwear\Beret_Red.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_Beret_Red.png</t>
   </si>
   <si>
     <t>Gray Fedora Hat</t>
@@ -456,10 +456,10 @@
     <t>灰色软呢帽</t>
   </si>
   <si>
-    <t>v1\Headwear\FedoraHat_Gray.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_FedoraHat_Gray.png</t>
+    <t>v2\Headwear\FedoraHat_Gray.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_FedoraHat_Gray.png</t>
   </si>
   <si>
     <t>Maroon Fedora Hat</t>
@@ -468,10 +468,10 @@
     <t>栗色软呢帽</t>
   </si>
   <si>
-    <t>v1\Headwear\FedoraHat_Maroon.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_FedoraHat_Maroon.png</t>
+    <t>v2\Headwear\FedoraHat_Maroon.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_FedoraHat_Maroon.png</t>
   </si>
   <si>
     <t>Halo</t>
@@ -480,10 +480,10 @@
     <t>光环</t>
   </si>
   <si>
-    <t>v1\Headwear\Hole.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_Hole.png</t>
+    <t>v2\Headwear\Hole.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_Hole.png</t>
   </si>
   <si>
     <t>Lucky Hat</t>
@@ -492,10 +492,10 @@
     <t>幸运帽</t>
   </si>
   <si>
-    <t>v1\Headwear\LuckyHat.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_LuckyHat.png</t>
+    <t>v2\Headwear\LuckyHat.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_LuckyHat.png</t>
   </si>
   <si>
     <t>Black Magic Hat</t>
@@ -504,10 +504,10 @@
     <t>黑色魔术帽</t>
   </si>
   <si>
-    <t>v1\Headwear\MagicHat_Black.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_MagicHat_Black.png</t>
+    <t>v2\Headwear\MagicHat_Black.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_MagicHat_Black.png</t>
   </si>
   <si>
     <t>White Magic Hat</t>
@@ -516,10 +516,10 @@
     <t>白色魔术帽</t>
   </si>
   <si>
-    <t>v1\Headwear\MagicHat_White.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_MagicHat_White.png</t>
+    <t>v2\Headwear\MagicHat_White.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_MagicHat_White.png</t>
   </si>
   <si>
     <t>Beige Sun Hat</t>
@@ -528,10 +528,10 @@
     <t>米色太阳帽</t>
   </si>
   <si>
-    <t>v1\Headwear\SunHat_Beige.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_SunHat_Beige.png</t>
+    <t>v2\Headwear\SunHat_Beige.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_SunHat_Beige.png</t>
   </si>
   <si>
     <t>Blue Sun Hat</t>
@@ -540,10 +540,10 @@
     <t>蓝色太阳帽</t>
   </si>
   <si>
-    <t>v1\Headwear\SunHat_Blue.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_SunHat_Blue.png</t>
+    <t>v2\Headwear\SunHat_Blue.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_SunHat_Blue.png</t>
   </si>
   <si>
     <t>Red Tyrolean Hat</t>
@@ -552,10 +552,10 @@
     <t>红色蒂罗尔帽</t>
   </si>
   <si>
-    <t>v1\Headwear\TyroleanHat_Red.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_TyroleanHat_Red.png</t>
+    <t>v2\Headwear\TyroleanHat_Red.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_TyroleanHat_Red.png</t>
   </si>
   <si>
     <t>Green Tyrolean Hat</t>
@@ -564,10 +564,10 @@
     <t>绿色蒂罗尔帽</t>
   </si>
   <si>
-    <t>v1\Headwear\TyroleanHat_Green.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Headwear_TyroleanHat_Green.png</t>
+    <t>v2\Headwear\TyroleanHat_Green.png</t>
+  </si>
+  <si>
+    <t>v2\ItemIcon\Headwear_TyroleanHat_Green.png</t>
   </si>
   <si>
     <t>3001-3005墓碑</t>
@@ -21474,7 +21474,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{ee4764c1-079b-469a-8c3f-129650bbd66c}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{1dc8a2f6-b6d2-456a-8aaf-48e606b75800}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21488,7 +21488,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{59866497-0a92-4294-a344-76b940b87ea9}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{818b94c5-a25e-4153-b617-3b21ba7429f1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21502,7 +21502,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{76e6fbce-5ed3-4f73-a4ea-a885e8a35bf2}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{b6f57e99-7375-451c-af75-8f6941424913}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21516,7 +21516,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{e62e5605-788c-4350-8433-6400ca0c41b3}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{93788a8d-a32a-4d09-961f-9514a50c8765}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21530,7 +21530,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{ffd0f33f-e6ab-454e-93c9-925bb51a8a83}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{7cfc27ea-0032-4efb-b530-93c7e5fc0bc9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21544,7 +21544,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{b1eae7bc-9de2-445d-8781-d9d2576af5b5}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{ffa221b3-3491-41d5-a24b-c3f6f27d2fe0}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21558,7 +21558,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{055c6280-ec0a-404b-a0da-2f8c83ac8019}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{cffd2324-9e43-4f14-883b-38373b07649b}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21572,7 +21572,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{f90ff12e-e19f-4456-a46b-ff380d193711}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{278cafbb-3cb0-41dc-a587-d2663b1f214d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21586,7 +21586,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{59d54686-3969-42d3-b833-73f308ba0d3e}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{9a40c835-53da-4391-936a-01f6ce4f6ce3}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -405,10 +405,10 @@
     <t>v3\ItemIcon\Dog_1010.png</t>
   </si>
   <si>
-    <t>Aristocrat Sesame Shiba</t>
-  </si>
-  <si>
-    <t>贵族麻柴</t>
+    <t>Top Student Sesame Shiba</t>
+  </si>
+  <si>
+    <t>学霸胡麻柴</t>
   </si>
   <si>
     <t>v3\ItemIcon\Dog_1011.png</t>
@@ -21963,7 +21963,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{7a784120-b7c4-436f-b30c-225f609a5032}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{aaf3771a-7f76-4477-a35b-9447542ef7ac}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21977,7 +21977,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{95cb84a2-1805-4725-84e5-a5c8f86dfa68}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{d8a2df56-cd7e-4c5c-8257-ac3d356fd27a}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21991,7 +21991,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{39fd40ff-35ed-485b-8e93-f432f2229e1f}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{a187bc1c-24bf-4152-87dc-ca1b3c1e0d8f}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22005,7 +22005,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{ce2e8023-1d85-44b0-bd53-5408ac354057}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{213d560a-0322-4daf-878a-29ac6f0bf215}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22019,7 +22019,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{6189f173-a112-48b7-9ed3-099579e51cc8}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{11352dc5-3dd0-415b-a0d0-c6e9dfdd9b38}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22033,7 +22033,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{c5d7d49a-0381-451d-a0a4-d632cfd98672}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{6daf80c6-961e-45e7-80aa-5cfa558f18a4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22047,7 +22047,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{8be2aafc-185b-4744-bfa5-ac00df808cc7}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{1d834d4c-7982-4d8c-9008-f2397498abea}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22061,7 +22061,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{37e2e6d0-d342-4708-ade7-8d56c2d2ac4a}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{1dc8e610-ef8b-4258-bc1c-94f813337c5b}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22075,7 +22075,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{a69d968f-402b-45f4-b70a-4ab8d0964ad2}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{7c2731cb-6998-4c81-9c58-86cf7f08e8b4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -27467,6 +27467,7 @@
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
     <col min="6" max="6" width="11.0833333333333" style="17" customWidth="1"/>
+    <col min="7" max="7" width="28.4166666666667" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -35926,13 +35927,13 @@
     <row r="361" spans="2:7">
       <c r="B361" s="19">
         <f t="shared" si="5"/>
-        <v>200301012</v>
+        <v>200301008</v>
       </c>
       <c r="C361">
         <v>2003</v>
       </c>
       <c r="D361">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="E361">
         <v>100</v>
@@ -35947,13 +35948,13 @@
     <row r="362" spans="2:7">
       <c r="B362" s="19">
         <f t="shared" si="5"/>
-        <v>200301008</v>
+        <v>200301011</v>
       </c>
       <c r="C362">
         <v>2003</v>
       </c>
       <c r="D362">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E362">
         <v>100</v>
@@ -35968,13 +35969,13 @@
     <row r="363" spans="2:7">
       <c r="B363" s="19">
         <f t="shared" si="5"/>
-        <v>200301010</v>
+        <v>200301013</v>
       </c>
       <c r="C363">
         <v>2003</v>
       </c>
       <c r="D363">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="E363">
         <v>100</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -327,45 +327,48 @@
     <t>胖白柴</t>
   </si>
   <si>
+    <t>优秀</t>
+  </si>
+  <si>
+    <t>v3\Shiba\Cream\</t>
+  </si>
+  <si>
+    <t>v3\ItemIcon\Dog_1003.png</t>
+  </si>
+  <si>
+    <t>Chubby Sesame Shiba</t>
+  </si>
+  <si>
+    <t>胖胡麻柴</t>
+  </si>
+  <si>
+    <t>v3\Shiba\Sesame\</t>
+  </si>
+  <si>
+    <t>v3\ItemIcon\Dog_1004.png</t>
+  </si>
+  <si>
+    <t>Chubby Red Shiba</t>
+  </si>
+  <si>
+    <t>胖赤柴</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>v3\ItemIcon\Dog_1005.png</t>
+  </si>
+  <si>
+    <t>Arcade Gamer Red Shiba</t>
+  </si>
+  <si>
+    <t>电玩赤柴</t>
+  </si>
+  <si>
     <t>传说</t>
   </si>
   <si>
-    <t>v3\Shiba\Cream\</t>
-  </si>
-  <si>
-    <t>v3\ItemIcon\Dog_1003.png</t>
-  </si>
-  <si>
-    <t>Chubby Sesame Shiba</t>
-  </si>
-  <si>
-    <t>胖胡麻柴</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>v3\Shiba\Sesame\</t>
-  </si>
-  <si>
-    <t>v3\ItemIcon\Dog_1004.png</t>
-  </si>
-  <si>
-    <t>Chubby Red Shiba</t>
-  </si>
-  <si>
-    <t>胖赤柴</t>
-  </si>
-  <si>
-    <t>v3\ItemIcon\Dog_1005.png</t>
-  </si>
-  <si>
-    <t>Arcade Gamer Red Shiba</t>
-  </si>
-  <si>
-    <t>电玩赤柴</t>
-  </si>
-  <si>
     <t>v3\ItemIcon\Dog_1006.png</t>
   </si>
   <si>
@@ -411,6 +414,9 @@
     <t>学霸胡麻柴</t>
   </si>
   <si>
+    <t>神话</t>
+  </si>
+  <si>
     <t>v3\ItemIcon\Dog_1011.png</t>
   </si>
   <si>
@@ -420,9 +426,6 @@
     <t>绅士赤柴</t>
   </si>
   <si>
-    <t>神话</t>
-  </si>
-  <si>
     <t>v3\ItemIcon\Dog_1012.png</t>
   </si>
   <si>
@@ -658,9 +661,6 @@
   </si>
   <si>
     <t>Headwear</t>
-  </si>
-  <si>
-    <t>优秀</t>
   </si>
   <si>
     <t>v2\Headwear\Beret_Green.png</t>
@@ -6679,7 +6679,7 @@
         <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I8">
         <v>200</v>
@@ -6694,10 +6694,10 @@
         <v>11</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="P8">
         <v>1004</v>
@@ -6729,16 +6729,16 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
         <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -6797,7 +6797,7 @@
         <v>79</v>
       </c>
       <c r="H10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -6815,7 +6815,7 @@
         <v>82</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P10">
         <v>1006</v>
@@ -6847,16 +6847,16 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -6874,7 +6874,7 @@
         <v>89</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P11">
         <v>1007</v>
@@ -6906,16 +6906,16 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
       </c>
       <c r="H12" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -6933,7 +6933,7 @@
         <v>94</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P12">
         <v>1008</v>
@@ -6965,16 +6965,16 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -6992,7 +6992,7 @@
         <v>89</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P13">
         <v>1009</v>
@@ -7024,16 +7024,16 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
         <v>79</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -7051,7 +7051,7 @@
         <v>94</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P14">
         <v>1010</v>
@@ -7083,16 +7083,16 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
         <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -7107,10 +7107,10 @@
         <v>11</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P15">
         <v>1011</v>
@@ -7142,16 +7142,16 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
         <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -7169,7 +7169,7 @@
         <v>82</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P16">
         <v>1012</v>
@@ -7201,16 +7201,16 @@
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
         <v>79</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -7225,7 +7225,7 @@
         <v>82</v>
       </c>
       <c r="O17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P17">
         <v>1013</v>
@@ -7257,16 +7257,16 @@
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
         <v>79</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -7281,7 +7281,7 @@
         <v>89</v>
       </c>
       <c r="O18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P18">
         <v>1014</v>
@@ -7313,16 +7313,16 @@
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
         <v>79</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -7337,7 +7337,7 @@
         <v>94</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P19">
         <v>1015</v>
@@ -7369,16 +7369,16 @@
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -7390,10 +7390,10 @@
         <v>88</v>
       </c>
       <c r="N20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P20">
         <v>1016</v>
@@ -7425,16 +7425,16 @@
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
         <v>79</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -7449,7 +7449,7 @@
         <v>82</v>
       </c>
       <c r="O21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P21">
         <v>1017</v>
@@ -7481,16 +7481,16 @@
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -7505,7 +7505,7 @@
         <v>89</v>
       </c>
       <c r="O22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P22">
         <v>1018</v>
@@ -7537,16 +7537,16 @@
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
         <v>79</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -7561,7 +7561,7 @@
         <v>94</v>
       </c>
       <c r="O23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P23">
         <v>1019</v>
@@ -7593,16 +7593,16 @@
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E24" t="s">
         <v>79</v>
       </c>
       <c r="H24" s="27" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -7614,10 +7614,10 @@
         <v>88</v>
       </c>
       <c r="N24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P24">
         <v>1020</v>
@@ -7649,16 +7649,16 @@
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E25" t="s">
         <v>79</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -7673,7 +7673,7 @@
         <v>89</v>
       </c>
       <c r="O25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P25">
         <v>1021</v>
@@ -7705,16 +7705,16 @@
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E26" t="s">
         <v>79</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -7729,7 +7729,7 @@
         <v>94</v>
       </c>
       <c r="O26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P26">
         <v>1022</v>
@@ -7761,16 +7761,16 @@
         <v>1023</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E27" t="s">
         <v>79</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -7785,7 +7785,7 @@
         <v>82</v>
       </c>
       <c r="O27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P27">
         <v>1023</v>
@@ -7817,16 +7817,16 @@
         <v>1024</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E28" t="s">
         <v>79</v>
       </c>
       <c r="H28" s="27" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -7841,7 +7841,7 @@
         <v>89</v>
       </c>
       <c r="O28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P28">
         <v>1024</v>
@@ -7873,16 +7873,16 @@
         <v>1025</v>
       </c>
       <c r="C29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
         <v>79</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -7897,7 +7897,7 @@
         <v>94</v>
       </c>
       <c r="O29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P29">
         <v>1025</v>
@@ -7929,16 +7929,16 @@
         <v>1026</v>
       </c>
       <c r="C30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E30" t="s">
         <v>79</v>
       </c>
       <c r="H30" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I30">
         <v>100</v>
@@ -7950,10 +7950,10 @@
         <v>88</v>
       </c>
       <c r="N30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P30">
         <v>1026</v>
@@ -7985,16 +7985,16 @@
         <v>1027</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E31" t="s">
         <v>79</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I31">
         <v>100</v>
@@ -8009,7 +8009,7 @@
         <v>94</v>
       </c>
       <c r="O31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P31">
         <v>1027</v>
@@ -8041,16 +8041,16 @@
         <v>1028</v>
       </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E32" t="s">
         <v>79</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -8065,7 +8065,7 @@
         <v>82</v>
       </c>
       <c r="O32" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P32">
         <v>1028</v>
@@ -8097,16 +8097,16 @@
         <v>1029</v>
       </c>
       <c r="C33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E33" t="s">
         <v>79</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -8121,7 +8121,7 @@
         <v>94</v>
       </c>
       <c r="O33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P33">
         <v>1029</v>
@@ -8153,16 +8153,16 @@
         <v>1030</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E34" t="s">
         <v>79</v>
       </c>
       <c r="H34" s="27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I34">
         <v>100</v>
@@ -8174,10 +8174,10 @@
         <v>88</v>
       </c>
       <c r="N34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P34">
         <v>1030</v>
@@ -8209,16 +8209,16 @@
         <v>1031</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E35" t="s">
         <v>79</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I35">
         <v>100</v>
@@ -8233,7 +8233,7 @@
         <v>82</v>
       </c>
       <c r="O35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P35">
         <v>1031</v>
@@ -8265,16 +8265,16 @@
         <v>1032</v>
       </c>
       <c r="C36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E36" t="s">
         <v>79</v>
       </c>
       <c r="H36" s="27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I36">
         <v>100</v>
@@ -8289,7 +8289,7 @@
         <v>89</v>
       </c>
       <c r="O36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P36">
         <v>1032</v>
@@ -8321,16 +8321,16 @@
         <v>1033</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E37" t="s">
         <v>79</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I37">
         <v>100</v>
@@ -8342,10 +8342,10 @@
         <v>88</v>
       </c>
       <c r="N37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P37">
         <v>1033</v>
@@ -8377,16 +8377,16 @@
         <v>1034</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E38" t="s">
         <v>79</v>
       </c>
       <c r="H38" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I38">
         <v>100</v>
@@ -8401,7 +8401,7 @@
         <v>82</v>
       </c>
       <c r="O38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P38">
         <v>1034</v>
@@ -8433,16 +8433,16 @@
         <v>1035</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
         <v>79</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I39">
         <v>100</v>
@@ -8457,7 +8457,7 @@
         <v>89</v>
       </c>
       <c r="O39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P39">
         <v>1035</v>
@@ -8489,16 +8489,16 @@
         <v>1036</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E40" t="s">
         <v>79</v>
       </c>
       <c r="H40" s="27" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I40">
         <v>100</v>
@@ -8513,7 +8513,7 @@
         <v>94</v>
       </c>
       <c r="O40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P40">
         <v>1036</v>
@@ -8545,16 +8545,16 @@
         <v>1037</v>
       </c>
       <c r="C41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E41" t="s">
         <v>79</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I41">
         <v>100</v>
@@ -8566,10 +8566,10 @@
         <v>88</v>
       </c>
       <c r="N41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P41">
         <v>1037</v>
@@ -8609,16 +8609,16 @@
         <v>2001</v>
       </c>
       <c r="C43" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D43" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H43" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I43">
         <v>300</v>
@@ -8671,7 +8671,7 @@
         <v>208</v>
       </c>
       <c r="E44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H44" t="s">
         <v>87</v>
@@ -8727,10 +8727,10 @@
         <v>212</v>
       </c>
       <c r="E45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H45" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I45">
         <v>300</v>
@@ -8783,7 +8783,7 @@
         <v>216</v>
       </c>
       <c r="E46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H46" t="s">
         <v>87</v>
@@ -8839,10 +8839,10 @@
         <v>220</v>
       </c>
       <c r="E47" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H47" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I47">
         <v>300</v>
@@ -8895,7 +8895,7 @@
         <v>224</v>
       </c>
       <c r="E48" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
@@ -8960,10 +8960,10 @@
         <v>228</v>
       </c>
       <c r="E49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H49" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I49">
         <v>300</v>
@@ -9016,10 +9016,10 @@
         <v>232</v>
       </c>
       <c r="E50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H50" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I50">
         <v>300</v>
@@ -9072,10 +9072,10 @@
         <v>236</v>
       </c>
       <c r="E51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H51" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I51">
         <v>300</v>
@@ -9128,10 +9128,10 @@
         <v>240</v>
       </c>
       <c r="E52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H52" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I52">
         <v>300</v>
@@ -9187,7 +9187,7 @@
         <v>244</v>
       </c>
       <c r="E53" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
@@ -9273,7 +9273,7 @@
         <v>248</v>
       </c>
       <c r="E54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
@@ -9282,7 +9282,7 @@
         <v>11</v>
       </c>
       <c r="H54" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I54">
         <v>300</v>
@@ -9356,10 +9356,10 @@
         <v>252</v>
       </c>
       <c r="E55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H55" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I55">
         <v>100</v>
@@ -9412,10 +9412,10 @@
         <v>256</v>
       </c>
       <c r="E56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H56" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I56">
         <v>100</v>
@@ -9468,10 +9468,10 @@
         <v>260</v>
       </c>
       <c r="E57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H57" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I57">
         <v>100</v>
@@ -9524,10 +9524,10 @@
         <v>264</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I58">
         <v>100</v>
@@ -9580,10 +9580,10 @@
         <v>268</v>
       </c>
       <c r="E59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I59">
         <v>100</v>
@@ -9636,10 +9636,10 @@
         <v>272</v>
       </c>
       <c r="E60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I60">
         <v>100</v>
@@ -9692,10 +9692,10 @@
         <v>276</v>
       </c>
       <c r="E61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H61" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I61">
         <v>100</v>
@@ -9748,10 +9748,10 @@
         <v>280</v>
       </c>
       <c r="E62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H62" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I62">
         <v>100</v>
@@ -9804,10 +9804,10 @@
         <v>284</v>
       </c>
       <c r="E63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H63" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I63">
         <v>100</v>
@@ -9860,7 +9860,7 @@
         <v>288</v>
       </c>
       <c r="E64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H64" t="s">
         <v>87</v>
@@ -9916,10 +9916,10 @@
         <v>292</v>
       </c>
       <c r="E65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H65" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I65">
         <v>100</v>
@@ -9972,10 +9972,10 @@
         <v>296</v>
       </c>
       <c r="E66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H66" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I66">
         <v>100</v>
@@ -10028,10 +10028,10 @@
         <v>300</v>
       </c>
       <c r="E67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H67" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I67">
         <v>200</v>
@@ -10084,7 +10084,7 @@
         <v>304</v>
       </c>
       <c r="E68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H68" t="s">
         <v>87</v>
@@ -10140,7 +10140,7 @@
         <v>308</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H69" t="s">
         <v>87</v>
@@ -10196,10 +10196,10 @@
         <v>312</v>
       </c>
       <c r="E70" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H70" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I70">
         <v>100</v>
@@ -10252,7 +10252,7 @@
         <v>316</v>
       </c>
       <c r="E71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H71" t="s">
         <v>87</v>
@@ -10308,10 +10308,10 @@
         <v>320</v>
       </c>
       <c r="E72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H72" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I72">
         <v>100</v>
@@ -10364,7 +10364,7 @@
         <v>324</v>
       </c>
       <c r="E73" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H73" t="s">
         <v>87</v>
@@ -10420,10 +10420,10 @@
         <v>328</v>
       </c>
       <c r="E74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H74" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I74">
         <v>100</v>
@@ -10476,10 +10476,10 @@
         <v>332</v>
       </c>
       <c r="E75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H75" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I75">
         <v>100</v>
@@ -10538,7 +10538,7 @@
         <v>338</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I76" s="9">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>370</v>
       </c>
       <c r="H83" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I83">
         <v>300</v>
@@ -11010,7 +11010,7 @@
         <v>370</v>
       </c>
       <c r="H84" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I84">
         <v>300</v>
@@ -11122,7 +11122,7 @@
         <v>370</v>
       </c>
       <c r="H86" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I86">
         <v>300</v>
@@ -11178,7 +11178,7 @@
         <v>370</v>
       </c>
       <c r="H87" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I87">
         <v>300</v>
@@ -11234,7 +11234,7 @@
         <v>370</v>
       </c>
       <c r="H88" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I88">
         <v>300</v>
@@ -11346,7 +11346,7 @@
         <v>370</v>
       </c>
       <c r="H90" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I90">
         <v>300</v>
@@ -11474,7 +11474,7 @@
         <v>11</v>
       </c>
       <c r="H92" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I92">
         <v>300</v>
@@ -11539,7 +11539,7 @@
         <v>11</v>
       </c>
       <c r="H93" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I93">
         <v>300</v>
@@ -11734,7 +11734,7 @@
         <v>11</v>
       </c>
       <c r="H96" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I96">
         <v>300</v>
@@ -11799,7 +11799,7 @@
         <v>11</v>
       </c>
       <c r="H97" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I97">
         <v>300</v>
@@ -11864,7 +11864,7 @@
         <v>11</v>
       </c>
       <c r="H98" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I98">
         <v>300</v>
@@ -11929,7 +11929,7 @@
         <v>11</v>
       </c>
       <c r="H99" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I99">
         <v>300</v>
@@ -11994,7 +11994,7 @@
         <v>11</v>
       </c>
       <c r="H100" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I100">
         <v>300</v>
@@ -12059,7 +12059,7 @@
         <v>11</v>
       </c>
       <c r="H101" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I101">
         <v>300</v>
@@ -12118,7 +12118,7 @@
         <v>448</v>
       </c>
       <c r="H102" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I102">
         <v>300</v>
@@ -12174,7 +12174,7 @@
         <v>448</v>
       </c>
       <c r="H103" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I103">
         <v>300</v>
@@ -12230,7 +12230,7 @@
         <v>448</v>
       </c>
       <c r="H104" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I104">
         <v>300</v>
@@ -12455,7 +12455,7 @@
         <v>448</v>
       </c>
       <c r="H108" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I108">
         <v>300</v>
@@ -12647,7 +12647,7 @@
         <v>11</v>
       </c>
       <c r="H111" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I111">
         <v>300</v>
@@ -12777,7 +12777,7 @@
         <v>11</v>
       </c>
       <c r="H113" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I113">
         <v>300</v>
@@ -12907,7 +12907,7 @@
         <v>11</v>
       </c>
       <c r="H115" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I115">
         <v>300</v>
@@ -12972,7 +12972,7 @@
         <v>11</v>
       </c>
       <c r="H116" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I116">
         <v>300</v>
@@ -13102,7 +13102,7 @@
         <v>11</v>
       </c>
       <c r="H118" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I118">
         <v>300</v>
@@ -13161,7 +13161,7 @@
         <v>448</v>
       </c>
       <c r="H119" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I119">
         <v>300</v>
@@ -13226,7 +13226,7 @@
         <v>11</v>
       </c>
       <c r="H120" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I120">
         <v>300</v>
@@ -13439,7 +13439,7 @@
         <v>11</v>
       </c>
       <c r="H123" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I123">
         <v>300</v>
@@ -13504,7 +13504,7 @@
         <v>11</v>
       </c>
       <c r="H124" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I124">
         <v>300</v>
@@ -13569,7 +13569,7 @@
         <v>11</v>
       </c>
       <c r="H125" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="I125">
         <v>300</v>
@@ -13634,7 +13634,7 @@
         <v>11</v>
       </c>
       <c r="H126" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="I126">
         <v>300</v>
@@ -13693,7 +13693,7 @@
         <v>525</v>
       </c>
       <c r="H127" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I127">
         <v>300</v>
@@ -13749,7 +13749,7 @@
         <v>525</v>
       </c>
       <c r="H128" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I128">
         <v>300</v>
@@ -13805,7 +13805,7 @@
         <v>525</v>
       </c>
       <c r="H129" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I129">
         <v>300</v>
@@ -13956,7 +13956,7 @@
         <v>11</v>
       </c>
       <c r="H131" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="I131">
         <v>300</v>
@@ -14033,7 +14033,7 @@
         <v>570</v>
       </c>
       <c r="H132" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I132">
         <v>200</v>
@@ -14225,7 +14225,7 @@
         <v>9009</v>
       </c>
       <c r="H135" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I135">
         <v>200</v>
@@ -14485,7 +14485,7 @@
         <v>9009</v>
       </c>
       <c r="H139" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I139">
         <v>200</v>
@@ -14544,7 +14544,7 @@
         <v>570</v>
       </c>
       <c r="H140" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I140">
         <v>200</v>
@@ -14609,7 +14609,7 @@
         <v>9009</v>
       </c>
       <c r="H141" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I141">
         <v>200</v>
@@ -14671,7 +14671,7 @@
         <v>9009</v>
       </c>
       <c r="H142" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I142">
         <v>200</v>
@@ -14978,7 +14978,7 @@
         <v>11</v>
       </c>
       <c r="H147" s="20" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I147">
         <v>300</v>
@@ -15097,7 +15097,7 @@
         <v>644</v>
       </c>
       <c r="E149" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H149" s="20" t="s">
         <v>640</v>
@@ -15216,7 +15216,7 @@
         <v>652</v>
       </c>
       <c r="E151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H151" t="s">
         <v>640</v>
@@ -15273,7 +15273,7 @@
         <v>654</v>
       </c>
       <c r="D152" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E152" t="s">
         <v>79</v>
@@ -15298,7 +15298,7 @@
         <v>82</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P152">
         <v>1012</v>
@@ -15481,7 +15481,7 @@
         <v>985</v>
       </c>
       <c r="D5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -15687,7 +15687,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -21963,7 +21963,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{aaf3771a-7f76-4477-a35b-9447542ef7ac}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{066ffaa5-508e-47bc-841e-91485e2aa6e9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21977,7 +21977,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{d8a2df56-cd7e-4c5c-8257-ac3d356fd27a}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{e91f3930-9ccb-43fb-9b2a-b52da20af275}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21991,7 +21991,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{a187bc1c-24bf-4152-87dc-ca1b3c1e0d8f}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{1e06d02e-9559-4220-afee-53722061add1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22005,7 +22005,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{213d560a-0322-4daf-878a-29ac6f0bf215}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{7804de6e-0968-4d54-93f3-3ccc103ea2b4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22019,7 +22019,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{11352dc5-3dd0-415b-a0d0-c6e9dfdd9b38}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{5f90ae70-5bed-44da-82d6-41ef7aa144e6}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22033,7 +22033,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{6daf80c6-961e-45e7-80aa-5cfa558f18a4}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{90e69ca2-db4a-4adc-ac12-bb6b58bf3fdc}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22047,7 +22047,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{1d834d4c-7982-4d8c-9008-f2397498abea}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{4b4b9acc-cdd3-4179-8860-88a9683ce10a}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22061,7 +22061,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{1dc8e610-ef8b-4258-bc1c-94f813337c5b}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{3ebeaf7b-075e-417b-b341-a569b9363efd}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22075,7 +22075,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{7c2731cb-6998-4c81-9c58-86cf7f08e8b4}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{2fa4b0df-d749-47d8-9ed6-d369dc194885}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -23126,7 +23126,7 @@
         <v>657</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16" t="s">
@@ -23150,7 +23150,7 @@
     </row>
     <row r="3" spans="1:21">
       <c r="B3" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>662</v>
@@ -23159,7 +23159,7 @@
         <v>663</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16" t="s">
@@ -23192,7 +23192,7 @@
         <v>670</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16" t="s">
@@ -23258,7 +23258,7 @@
         <v>684</v>
       </c>
       <c r="F6" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16" t="s">
@@ -26586,7 +26586,7 @@
         <v>1001</v>
       </c>
       <c r="D6" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="E6">
         <v>6700</v>
@@ -26628,7 +26628,7 @@
         <v>1001</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" s="20">
         <v>900</v>
@@ -26649,7 +26649,7 @@
         <v>1001</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E9" s="20">
         <v>180</v>
@@ -26670,7 +26670,7 @@
         <v>1001</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E10">
         <v>20</v>
@@ -26721,7 +26721,7 @@
         <v>1002</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="E13">
         <v>3700</v>
@@ -26766,7 +26766,7 @@
         <v>1002</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E15">
         <v>1700</v>
@@ -26787,7 +26787,7 @@
         <v>1002</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E16">
         <v>380</v>
@@ -26808,7 +26808,7 @@
         <v>1002</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E17">
         <v>20</v>
@@ -26862,7 +26862,7 @@
         <v>2001</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="E20">
         <v>3000</v>
@@ -26910,7 +26910,7 @@
         <v>2001</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E22">
         <v>1700</v>
@@ -26934,7 +26934,7 @@
         <v>2001</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E23">
         <v>380</v>
@@ -26958,7 +26958,7 @@
         <v>2001</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -27015,7 +27015,7 @@
         <v>2002</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="E27">
         <v>3700</v>
@@ -27063,7 +27063,7 @@
         <v>2002</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E29">
         <v>1700</v>
@@ -27087,7 +27087,7 @@
         <v>2002</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -27111,7 +27111,7 @@
         <v>2002</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -27168,7 +27168,7 @@
         <v>2003</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -27216,7 +27216,7 @@
         <v>2003</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E36">
         <v>1000</v>
@@ -27240,7 +27240,7 @@
         <v>2003</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E37">
         <v>1000</v>
@@ -27264,7 +27264,7 @@
         <v>2003</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E38">
         <v>2000</v>
@@ -27346,7 +27346,7 @@
         <v>4001</v>
       </c>
       <c r="D43" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="E43">
         <v>6700</v>
@@ -27388,7 +27388,7 @@
         <v>4001</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E45" s="20">
         <v>900</v>
@@ -27409,7 +27409,7 @@
         <v>4001</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E46" s="20">
         <v>180</v>
@@ -27430,7 +27430,7 @@
         <v>4001</v>
       </c>
       <c r="D47" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E47">
         <v>20</v>
@@ -27571,7 +27571,6 @@
         <v>11</v>
       </c>
       <c r="B5" s="19">
-        <f>C5*100000+D5</f>
         <v>100101002</v>
       </c>
       <c r="C5">
@@ -27581,7 +27580,7 @@
         <v>1002</v>
       </c>
       <c r="E5">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F5" s="17" t="b">
         <v>1</v>
@@ -27595,7 +27594,6 @@
         <v>11</v>
       </c>
       <c r="B6" s="19">
-        <f t="shared" ref="B6:B69" si="0">C6*100000+D6</f>
         <v>100101003</v>
       </c>
       <c r="C6">
@@ -27605,7 +27603,7 @@
         <v>1003</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="F6" s="17" t="b">
         <v>1</v>
@@ -27619,7 +27617,6 @@
         <v>11</v>
       </c>
       <c r="B7" s="19">
-        <f t="shared" si="0"/>
         <v>100101004</v>
       </c>
       <c r="C7">
@@ -27629,7 +27626,7 @@
         <v>1004</v>
       </c>
       <c r="E7">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="F7" s="17" t="b">
         <v>1</v>
@@ -27643,7 +27640,6 @@
         <v>11</v>
       </c>
       <c r="B8" s="19">
-        <f t="shared" si="0"/>
         <v>100101005</v>
       </c>
       <c r="C8">
@@ -27653,7 +27649,7 @@
         <v>1005</v>
       </c>
       <c r="E8" s="20">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="F8" s="17" t="b">
         <v>1</v>
@@ -27667,7 +27663,6 @@
         <v>11</v>
       </c>
       <c r="B9" s="19">
-        <f t="shared" si="0"/>
         <v>100101006</v>
       </c>
       <c r="C9">
@@ -27677,7 +27672,7 @@
         <v>1006</v>
       </c>
       <c r="E9" s="20">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F9" s="17" t="b">
         <v>1</v>
@@ -27691,7 +27686,6 @@
         <v>11</v>
       </c>
       <c r="B10" s="19">
-        <f t="shared" si="0"/>
         <v>100101007</v>
       </c>
       <c r="C10">
@@ -27701,7 +27695,7 @@
         <v>1007</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F10" s="17" t="b">
         <v>1</v>
@@ -27715,7 +27709,6 @@
         <v>11</v>
       </c>
       <c r="B11" s="19">
-        <f t="shared" si="0"/>
         <v>100101008</v>
       </c>
       <c r="C11">
@@ -27725,7 +27718,7 @@
         <v>1008</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F11" s="17" t="b">
         <v>1</v>
@@ -27739,7 +27732,6 @@
         <v>11</v>
       </c>
       <c r="B12" s="19">
-        <f t="shared" si="0"/>
         <v>100101009</v>
       </c>
       <c r="C12">
@@ -27749,7 +27741,7 @@
         <v>1009</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F12" s="17" t="b">
         <v>1</v>
@@ -27763,7 +27755,6 @@
         <v>11</v>
       </c>
       <c r="B13" s="19">
-        <f t="shared" si="0"/>
         <v>100101010</v>
       </c>
       <c r="C13">
@@ -27773,7 +27764,7 @@
         <v>1010</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F13" s="17" t="b">
         <v>1</v>
@@ -27787,7 +27778,6 @@
         <v>11</v>
       </c>
       <c r="B14" s="19">
-        <f t="shared" si="0"/>
         <v>100101011</v>
       </c>
       <c r="C14">
@@ -27797,7 +27787,7 @@
         <v>1011</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F14" s="17" t="b">
         <v>1</v>
@@ -27811,7 +27801,6 @@
         <v>11</v>
       </c>
       <c r="B15" s="19">
-        <f t="shared" si="0"/>
         <v>100101012</v>
       </c>
       <c r="C15">
@@ -27821,7 +27810,7 @@
         <v>1012</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F15" s="17" t="b">
         <v>1</v>
@@ -27832,7 +27821,6 @@
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="19">
-        <f t="shared" si="0"/>
         <v>100101013</v>
       </c>
       <c r="C16">
@@ -27842,7 +27830,7 @@
         <v>1013</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F16" s="17" t="b">
         <v>1</v>
@@ -27853,7 +27841,6 @@
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="19">
-        <f t="shared" si="0"/>
         <v>100101014</v>
       </c>
       <c r="C17">
@@ -27863,7 +27850,7 @@
         <v>1014</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F17" s="17" t="b">
         <v>1</v>
@@ -27874,7 +27861,6 @@
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="19">
-        <f t="shared" si="0"/>
         <v>100101015</v>
       </c>
       <c r="C18">
@@ -27884,7 +27870,7 @@
         <v>1015</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F18" s="17" t="b">
         <v>1</v>
@@ -27895,7 +27881,6 @@
     </row>
     <row r="19" spans="2:7">
       <c r="B19" s="19">
-        <f t="shared" si="0"/>
         <v>100101016</v>
       </c>
       <c r="C19">
@@ -27905,7 +27890,7 @@
         <v>1016</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F19" s="17" t="b">
         <v>1</v>
@@ -27916,7 +27901,6 @@
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="19">
-        <f t="shared" si="0"/>
         <v>100101017</v>
       </c>
       <c r="C20">
@@ -27926,7 +27910,7 @@
         <v>1017</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F20" s="17" t="b">
         <v>1</v>
@@ -27937,7 +27921,6 @@
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="19">
-        <f t="shared" si="0"/>
         <v>100101018</v>
       </c>
       <c r="C21">
@@ -27947,7 +27930,7 @@
         <v>1018</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F21" s="17" t="b">
         <v>1</v>
@@ -27958,7 +27941,6 @@
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="19">
-        <f t="shared" si="0"/>
         <v>100101019</v>
       </c>
       <c r="C22">
@@ -27968,7 +27950,7 @@
         <v>1019</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F22" s="17" t="b">
         <v>1</v>
@@ -27979,7 +27961,6 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="19">
-        <f t="shared" si="0"/>
         <v>100101020</v>
       </c>
       <c r="C23">
@@ -27989,7 +27970,7 @@
         <v>1020</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F23" s="17" t="b">
         <v>1</v>
@@ -28000,7 +27981,6 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="19">
-        <f t="shared" si="0"/>
         <v>100101021</v>
       </c>
       <c r="C24">
@@ -28010,7 +27990,7 @@
         <v>1021</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="17" t="b">
         <v>1</v>
@@ -28021,7 +28001,6 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="19">
-        <f t="shared" si="0"/>
         <v>100101022</v>
       </c>
       <c r="C25">
@@ -28031,7 +28010,7 @@
         <v>1022</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F25" s="17" t="b">
         <v>1</v>
@@ -28042,7 +28021,6 @@
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="19">
-        <f t="shared" si="0"/>
         <v>100101023</v>
       </c>
       <c r="C26">
@@ -28052,7 +28030,7 @@
         <v>1023</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F26" s="17" t="b">
         <v>1</v>
@@ -28063,7 +28041,6 @@
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="19">
-        <f t="shared" si="0"/>
         <v>100101024</v>
       </c>
       <c r="C27">
@@ -28073,7 +28050,7 @@
         <v>1024</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F27" s="17" t="b">
         <v>1</v>
@@ -28084,7 +28061,6 @@
     </row>
     <row r="28" spans="2:7">
       <c r="B28" s="19">
-        <f t="shared" si="0"/>
         <v>100101025</v>
       </c>
       <c r="C28">
@@ -28094,7 +28070,7 @@
         <v>1025</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F28" s="17" t="b">
         <v>1</v>
@@ -28105,7 +28081,6 @@
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="19">
-        <f t="shared" si="0"/>
         <v>100101026</v>
       </c>
       <c r="C29">
@@ -28115,7 +28090,7 @@
         <v>1026</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F29" s="17" t="b">
         <v>1</v>
@@ -28126,7 +28101,6 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="19">
-        <f t="shared" si="0"/>
         <v>100101027</v>
       </c>
       <c r="C30">
@@ -28136,7 +28110,7 @@
         <v>1027</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F30" s="17" t="b">
         <v>1</v>
@@ -28147,7 +28121,6 @@
     </row>
     <row r="31" spans="2:7">
       <c r="B31" s="19">
-        <f t="shared" si="0"/>
         <v>100101028</v>
       </c>
       <c r="C31">
@@ -28157,7 +28130,7 @@
         <v>1028</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F31" s="17" t="b">
         <v>1</v>
@@ -28168,7 +28141,6 @@
     </row>
     <row r="32" spans="2:7">
       <c r="B32" s="19">
-        <f t="shared" si="0"/>
         <v>100101029</v>
       </c>
       <c r="C32">
@@ -28178,7 +28150,7 @@
         <v>1029</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F32" s="17" t="b">
         <v>1</v>
@@ -28189,7 +28161,6 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="19">
-        <f t="shared" si="0"/>
         <v>100101030</v>
       </c>
       <c r="C33">
@@ -28199,7 +28170,7 @@
         <v>1030</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F33" s="17" t="b">
         <v>1</v>
@@ -28210,7 +28181,6 @@
     </row>
     <row r="34" spans="1:7">
       <c r="B34" s="19">
-        <f t="shared" si="0"/>
         <v>100101031</v>
       </c>
       <c r="C34">
@@ -28220,7 +28190,7 @@
         <v>1031</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F34" s="17" t="b">
         <v>1</v>
@@ -28231,7 +28201,6 @@
     </row>
     <row r="35" spans="1:7">
       <c r="B35" s="19">
-        <f t="shared" si="0"/>
         <v>100101032</v>
       </c>
       <c r="C35">
@@ -28241,7 +28210,7 @@
         <v>1032</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F35" s="17" t="b">
         <v>1</v>
@@ -28252,7 +28221,6 @@
     </row>
     <row r="36" spans="1:7">
       <c r="B36" s="19">
-        <f t="shared" si="0"/>
         <v>100101033</v>
       </c>
       <c r="C36">
@@ -28262,7 +28230,7 @@
         <v>1033</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F36" s="17" t="b">
         <v>1</v>
@@ -28273,7 +28241,6 @@
     </row>
     <row r="37" spans="1:7">
       <c r="B37" s="19">
-        <f t="shared" si="0"/>
         <v>100101034</v>
       </c>
       <c r="C37">
@@ -28283,7 +28250,7 @@
         <v>1034</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F37" s="17" t="b">
         <v>1</v>
@@ -28294,7 +28261,6 @@
     </row>
     <row r="38" spans="1:7">
       <c r="B38" s="19">
-        <f t="shared" si="0"/>
         <v>100101035</v>
       </c>
       <c r="C38">
@@ -28304,7 +28270,7 @@
         <v>1035</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F38" s="17" t="b">
         <v>1</v>
@@ -28315,7 +28281,6 @@
     </row>
     <row r="39" spans="1:7">
       <c r="B39" s="19">
-        <f t="shared" si="0"/>
         <v>100101036</v>
       </c>
       <c r="C39">
@@ -28325,7 +28290,7 @@
         <v>1036</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F39" s="17" t="b">
         <v>1</v>
@@ -28336,7 +28301,6 @@
     </row>
     <row r="40" spans="1:7">
       <c r="B40" s="19">
-        <f t="shared" si="0"/>
         <v>100101037</v>
       </c>
       <c r="C40">
@@ -28346,7 +28310,7 @@
         <v>1037</v>
       </c>
       <c r="E40">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F40" s="17" t="b">
         <v>1</v>
@@ -28360,7 +28324,6 @@
         <v>11</v>
       </c>
       <c r="B41" s="19">
-        <f t="shared" si="0"/>
         <v>100102001</v>
       </c>
       <c r="C41">
@@ -28384,7 +28347,6 @@
         <v>11</v>
       </c>
       <c r="B42" s="19">
-        <f t="shared" si="0"/>
         <v>100102002</v>
       </c>
       <c r="C42">
@@ -28408,7 +28370,6 @@
         <v>11</v>
       </c>
       <c r="B43" s="19">
-        <f t="shared" si="0"/>
         <v>100102003</v>
       </c>
       <c r="C43">
@@ -28432,7 +28393,6 @@
         <v>11</v>
       </c>
       <c r="B44" s="19">
-        <f t="shared" si="0"/>
         <v>100102004</v>
       </c>
       <c r="C44">
@@ -28456,7 +28416,6 @@
         <v>11</v>
       </c>
       <c r="B45" s="19">
-        <f t="shared" si="0"/>
         <v>100102005</v>
       </c>
       <c r="C45">
@@ -28480,7 +28439,6 @@
         <v>11</v>
       </c>
       <c r="B46" s="19">
-        <f t="shared" si="0"/>
         <v>100102006</v>
       </c>
       <c r="C46">
@@ -28504,7 +28462,6 @@
         <v>11</v>
       </c>
       <c r="B47" s="19">
-        <f t="shared" si="0"/>
         <v>100102007</v>
       </c>
       <c r="C47">
@@ -28528,7 +28485,6 @@
         <v>11</v>
       </c>
       <c r="B48" s="19">
-        <f t="shared" si="0"/>
         <v>100102008</v>
       </c>
       <c r="C48">
@@ -28552,7 +28508,6 @@
         <v>11</v>
       </c>
       <c r="B49" s="19">
-        <f t="shared" si="0"/>
         <v>100102009</v>
       </c>
       <c r="C49">
@@ -28576,7 +28531,6 @@
         <v>11</v>
       </c>
       <c r="B50" s="19">
-        <f t="shared" si="0"/>
         <v>100102010</v>
       </c>
       <c r="C50">
@@ -28600,7 +28554,6 @@
         <v>11</v>
       </c>
       <c r="B51" s="19">
-        <f t="shared" si="0"/>
         <v>100102011</v>
       </c>
       <c r="C51">
@@ -28624,7 +28577,6 @@
         <v>11</v>
       </c>
       <c r="B52" s="19">
-        <f t="shared" si="0"/>
         <v>100102012</v>
       </c>
       <c r="C52">
@@ -28648,7 +28600,6 @@
         <v>11</v>
       </c>
       <c r="B53" s="19">
-        <f t="shared" si="0"/>
         <v>100102013</v>
       </c>
       <c r="C53">
@@ -28672,7 +28623,6 @@
         <v>11</v>
       </c>
       <c r="B54" s="19">
-        <f t="shared" si="0"/>
         <v>100102014</v>
       </c>
       <c r="C54">
@@ -28696,7 +28646,6 @@
         <v>11</v>
       </c>
       <c r="B55" s="19">
-        <f t="shared" si="0"/>
         <v>100102015</v>
       </c>
       <c r="C55">
@@ -28720,7 +28669,6 @@
         <v>11</v>
       </c>
       <c r="B56" s="19">
-        <f t="shared" si="0"/>
         <v>100102016</v>
       </c>
       <c r="C56">
@@ -28744,7 +28692,6 @@
         <v>11</v>
       </c>
       <c r="B57" s="19">
-        <f t="shared" si="0"/>
         <v>100102017</v>
       </c>
       <c r="C57">
@@ -28768,7 +28715,6 @@
         <v>11</v>
       </c>
       <c r="B58" s="19">
-        <f t="shared" si="0"/>
         <v>100102018</v>
       </c>
       <c r="C58">
@@ -28792,7 +28738,6 @@
         <v>11</v>
       </c>
       <c r="B59" s="19">
-        <f t="shared" si="0"/>
         <v>100102019</v>
       </c>
       <c r="C59">
@@ -28816,7 +28761,6 @@
         <v>11</v>
       </c>
       <c r="B60" s="19">
-        <f t="shared" si="0"/>
         <v>100102020</v>
       </c>
       <c r="C60">
@@ -28840,7 +28784,6 @@
         <v>11</v>
       </c>
       <c r="B61" s="19">
-        <f t="shared" si="0"/>
         <v>100102021</v>
       </c>
       <c r="C61">
@@ -28864,7 +28807,6 @@
         <v>11</v>
       </c>
       <c r="B62" s="19">
-        <f t="shared" si="0"/>
         <v>100102022</v>
       </c>
       <c r="C62">
@@ -28888,7 +28830,6 @@
         <v>11</v>
       </c>
       <c r="B63" s="19">
-        <f t="shared" si="0"/>
         <v>100102023</v>
       </c>
       <c r="C63">
@@ -28912,7 +28853,6 @@
         <v>11</v>
       </c>
       <c r="B64" s="19">
-        <f t="shared" si="0"/>
         <v>100102024</v>
       </c>
       <c r="C64">
@@ -28936,7 +28876,6 @@
         <v>11</v>
       </c>
       <c r="B65" s="19">
-        <f t="shared" si="0"/>
         <v>100102025</v>
       </c>
       <c r="C65">
@@ -28960,7 +28899,6 @@
         <v>11</v>
       </c>
       <c r="B66" s="19">
-        <f t="shared" si="0"/>
         <v>100102026</v>
       </c>
       <c r="C66">
@@ -28984,7 +28922,6 @@
         <v>11</v>
       </c>
       <c r="B67" s="19">
-        <f t="shared" si="0"/>
         <v>100102027</v>
       </c>
       <c r="C67">
@@ -29008,7 +28945,6 @@
         <v>11</v>
       </c>
       <c r="B68" s="19">
-        <f t="shared" si="0"/>
         <v>100102028</v>
       </c>
       <c r="C68">
@@ -29032,7 +28968,6 @@
         <v>11</v>
       </c>
       <c r="B69" s="19">
-        <f t="shared" si="0"/>
         <v>100102029</v>
       </c>
       <c r="C69">
@@ -29056,7 +28991,7 @@
         <v>11</v>
       </c>
       <c r="B70" s="19">
-        <f t="shared" ref="B70:B133" si="1">C70*100000+D70</f>
+        <f t="shared" ref="B70:B133" si="0">C70*100000+D70</f>
         <v>100102030</v>
       </c>
       <c r="C70">
@@ -29080,7 +29015,7 @@
         <v>11</v>
       </c>
       <c r="B71" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100102031</v>
       </c>
       <c r="C71">
@@ -29104,7 +29039,7 @@
         <v>11</v>
       </c>
       <c r="B72" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100102032</v>
       </c>
       <c r="C72">
@@ -29128,7 +29063,7 @@
         <v>11</v>
       </c>
       <c r="B73" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100102033</v>
       </c>
       <c r="C73">
@@ -29152,7 +29087,7 @@
         <v>11</v>
       </c>
       <c r="B74" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105001</v>
       </c>
       <c r="C74">
@@ -29176,7 +29111,7 @@
         <v>11</v>
       </c>
       <c r="B75" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105002</v>
       </c>
       <c r="C75">
@@ -29200,7 +29135,7 @@
         <v>11</v>
       </c>
       <c r="B76" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105003</v>
       </c>
       <c r="C76">
@@ -29224,7 +29159,7 @@
         <v>11</v>
       </c>
       <c r="B77" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105004</v>
       </c>
       <c r="C77">
@@ -29248,7 +29183,7 @@
         <v>11</v>
       </c>
       <c r="B78" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105005</v>
       </c>
       <c r="C78">
@@ -29272,7 +29207,7 @@
         <v>11</v>
       </c>
       <c r="B79" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105006</v>
       </c>
       <c r="C79">
@@ -29296,7 +29231,7 @@
         <v>11</v>
       </c>
       <c r="B80" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105007</v>
       </c>
       <c r="C80">
@@ -29320,7 +29255,7 @@
         <v>11</v>
       </c>
       <c r="B81" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100105008</v>
       </c>
       <c r="C81">
@@ -29344,7 +29279,7 @@
         <v>11</v>
       </c>
       <c r="B82" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106002</v>
       </c>
       <c r="C82">
@@ -29368,7 +29303,7 @@
         <v>11</v>
       </c>
       <c r="B83" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106003</v>
       </c>
       <c r="C83">
@@ -29392,7 +29327,7 @@
         <v>11</v>
       </c>
       <c r="B84" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106004</v>
       </c>
       <c r="C84">
@@ -29416,7 +29351,7 @@
         <v>11</v>
       </c>
       <c r="B85" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106005</v>
       </c>
       <c r="C85">
@@ -29440,7 +29375,7 @@
         <v>11</v>
       </c>
       <c r="B86" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106006</v>
       </c>
       <c r="C86">
@@ -29464,7 +29399,7 @@
         <v>11</v>
       </c>
       <c r="B87" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106007</v>
       </c>
       <c r="C87">
@@ -29488,7 +29423,7 @@
         <v>11</v>
       </c>
       <c r="B88" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106008</v>
       </c>
       <c r="C88">
@@ -29512,7 +29447,7 @@
         <v>11</v>
       </c>
       <c r="B89" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106009</v>
       </c>
       <c r="C89">
@@ -29536,7 +29471,7 @@
         <v>11</v>
       </c>
       <c r="B90" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106010</v>
       </c>
       <c r="C90">
@@ -29560,7 +29495,7 @@
         <v>11</v>
       </c>
       <c r="B91" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100106011</v>
       </c>
       <c r="C91">
@@ -29584,7 +29519,7 @@
         <v>11</v>
       </c>
       <c r="B92" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107001</v>
       </c>
       <c r="C92">
@@ -29608,7 +29543,7 @@
         <v>11</v>
       </c>
       <c r="B93" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107002</v>
       </c>
       <c r="C93">
@@ -29632,7 +29567,7 @@
         <v>11</v>
       </c>
       <c r="B94" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107003</v>
       </c>
       <c r="C94">
@@ -29656,7 +29591,7 @@
         <v>11</v>
       </c>
       <c r="B95" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107005</v>
       </c>
       <c r="C95">
@@ -29680,7 +29615,7 @@
         <v>11</v>
       </c>
       <c r="B96" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107006</v>
       </c>
       <c r="C96">
@@ -29704,7 +29639,7 @@
         <v>11</v>
       </c>
       <c r="B97" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107007</v>
       </c>
       <c r="C97">
@@ -29728,7 +29663,7 @@
         <v>11</v>
       </c>
       <c r="B98" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107008</v>
       </c>
       <c r="C98">
@@ -29752,7 +29687,7 @@
         <v>11</v>
       </c>
       <c r="B99" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107009</v>
       </c>
       <c r="C99">
@@ -29776,7 +29711,7 @@
         <v>11</v>
       </c>
       <c r="B100" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107010</v>
       </c>
       <c r="C100">
@@ -29800,7 +29735,7 @@
         <v>11</v>
       </c>
       <c r="B101" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107011</v>
       </c>
       <c r="C101">
@@ -29824,7 +29759,7 @@
         <v>11</v>
       </c>
       <c r="B102" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107012</v>
       </c>
       <c r="C102">
@@ -29848,7 +29783,7 @@
         <v>11</v>
       </c>
       <c r="B103" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107013</v>
       </c>
       <c r="C103">
@@ -29872,7 +29807,7 @@
         <v>11</v>
       </c>
       <c r="B104" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107014</v>
       </c>
       <c r="C104">
@@ -29896,7 +29831,7 @@
         <v>11</v>
       </c>
       <c r="B105" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107015</v>
       </c>
       <c r="C105">
@@ -29920,7 +29855,7 @@
         <v>11</v>
       </c>
       <c r="B106" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107016</v>
       </c>
       <c r="C106">
@@ -29944,7 +29879,7 @@
         <v>11</v>
       </c>
       <c r="B107" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107017</v>
       </c>
       <c r="C107">
@@ -29968,7 +29903,7 @@
         <v>11</v>
       </c>
       <c r="B108" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107018</v>
       </c>
       <c r="C108">
@@ -29992,7 +29927,7 @@
         <v>11</v>
       </c>
       <c r="B109" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100107019</v>
       </c>
       <c r="C109">
@@ -30016,7 +29951,7 @@
         <v>11</v>
       </c>
       <c r="B110" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108001</v>
       </c>
       <c r="C110">
@@ -30040,7 +29975,7 @@
         <v>11</v>
       </c>
       <c r="B111" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108003</v>
       </c>
       <c r="C111">
@@ -30064,7 +29999,7 @@
         <v>11</v>
       </c>
       <c r="B112" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108004</v>
       </c>
       <c r="C112">
@@ -30088,7 +30023,7 @@
         <v>11</v>
       </c>
       <c r="B113" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108005</v>
       </c>
       <c r="C113">
@@ -30112,7 +30047,7 @@
         <v>11</v>
       </c>
       <c r="B114" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108007</v>
       </c>
       <c r="C114">
@@ -30136,7 +30071,7 @@
         <v>11</v>
       </c>
       <c r="B115" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108008</v>
       </c>
       <c r="C115">
@@ -30160,7 +30095,7 @@
         <v>11</v>
       </c>
       <c r="B116" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108009</v>
       </c>
       <c r="C116">
@@ -30184,7 +30119,7 @@
         <v>11</v>
       </c>
       <c r="B117" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108010</v>
       </c>
       <c r="C117">
@@ -30208,7 +30143,7 @@
         <v>11</v>
       </c>
       <c r="B118" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108011</v>
       </c>
       <c r="C118">
@@ -30232,7 +30167,7 @@
         <v>11</v>
       </c>
       <c r="B119" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100108012</v>
       </c>
       <c r="C119">
@@ -30256,7 +30191,6 @@
         <v>11</v>
       </c>
       <c r="B120" s="19">
-        <f t="shared" si="1"/>
         <v>100108013</v>
       </c>
       <c r="C120">
@@ -30266,7 +30200,7 @@
         <v>8013</v>
       </c>
       <c r="E120">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F120" s="17" t="b">
         <v>1</v>
@@ -30280,7 +30214,6 @@
         <v>11</v>
       </c>
       <c r="B121" s="19">
-        <f t="shared" si="1"/>
         <v>100112001</v>
       </c>
       <c r="C121">
@@ -30290,7 +30223,7 @@
         <v>12001</v>
       </c>
       <c r="E121">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F121" s="17" t="b">
         <v>1</v>
@@ -30304,7 +30237,6 @@
         <v>11</v>
       </c>
       <c r="B122" s="19">
-        <f t="shared" si="1"/>
         <v>100112002</v>
       </c>
       <c r="C122">
@@ -30314,7 +30246,7 @@
         <v>12002</v>
       </c>
       <c r="E122">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F122" s="17" t="b">
         <v>1</v>
@@ -30328,7 +30260,7 @@
         <v>11</v>
       </c>
       <c r="B123" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201002</v>
       </c>
       <c r="C123">
@@ -30352,7 +30284,7 @@
         <v>11</v>
       </c>
       <c r="B124" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201003</v>
       </c>
       <c r="C124">
@@ -30376,7 +30308,7 @@
         <v>11</v>
       </c>
       <c r="B125" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201004</v>
       </c>
       <c r="C125">
@@ -30400,7 +30332,7 @@
         <v>11</v>
       </c>
       <c r="B126" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201005</v>
       </c>
       <c r="C126">
@@ -30424,7 +30356,7 @@
         <v>11</v>
       </c>
       <c r="B127" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201006</v>
       </c>
       <c r="C127">
@@ -30448,7 +30380,7 @@
         <v>11</v>
       </c>
       <c r="B128" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201007</v>
       </c>
       <c r="C128">
@@ -30472,7 +30404,7 @@
         <v>11</v>
       </c>
       <c r="B129" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201008</v>
       </c>
       <c r="C129">
@@ -30496,7 +30428,7 @@
         <v>11</v>
       </c>
       <c r="B130" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201009</v>
       </c>
       <c r="C130">
@@ -30520,7 +30452,7 @@
         <v>11</v>
       </c>
       <c r="B131" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201010</v>
       </c>
       <c r="C131">
@@ -30544,7 +30476,7 @@
         <v>11</v>
       </c>
       <c r="B132" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201011</v>
       </c>
       <c r="C132">
@@ -30568,7 +30500,7 @@
         <v>11</v>
       </c>
       <c r="B133" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100201012</v>
       </c>
       <c r="C133">
@@ -30589,7 +30521,7 @@
     </row>
     <row r="134" spans="1:7">
       <c r="B134" s="19">
-        <f t="shared" ref="B134:B197" si="2">C134*100000+D134</f>
+        <f t="shared" ref="B134:B197" si="1">C134*100000+D134</f>
         <v>100201013</v>
       </c>
       <c r="C134">
@@ -30610,7 +30542,7 @@
     </row>
     <row r="135" spans="1:7">
       <c r="B135" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201014</v>
       </c>
       <c r="C135">
@@ -30631,7 +30563,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="B136" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201015</v>
       </c>
       <c r="C136">
@@ -30652,7 +30584,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="B137" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201016</v>
       </c>
       <c r="C137">
@@ -30673,7 +30605,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="B138" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201017</v>
       </c>
       <c r="C138">
@@ -30694,7 +30626,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="B139" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201018</v>
       </c>
       <c r="C139">
@@ -30715,7 +30647,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="B140" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201019</v>
       </c>
       <c r="C140">
@@ -30736,7 +30668,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="B141" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201020</v>
       </c>
       <c r="C141">
@@ -30757,7 +30689,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="B142" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201021</v>
       </c>
       <c r="C142">
@@ -30778,7 +30710,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="B143" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201022</v>
       </c>
       <c r="C143">
@@ -30799,7 +30731,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="B144" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201023</v>
       </c>
       <c r="C144">
@@ -30820,7 +30752,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="B145" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201024</v>
       </c>
       <c r="C145">
@@ -30841,7 +30773,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="B146" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201025</v>
       </c>
       <c r="C146">
@@ -30862,7 +30794,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="B147" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201026</v>
       </c>
       <c r="C147">
@@ -30883,7 +30815,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="B148" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201027</v>
       </c>
       <c r="C148">
@@ -30904,7 +30836,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="B149" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201028</v>
       </c>
       <c r="C149">
@@ -30925,7 +30857,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="B150" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201029</v>
       </c>
       <c r="C150">
@@ -30946,7 +30878,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="B151" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201030</v>
       </c>
       <c r="C151">
@@ -30967,7 +30899,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="B152" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201031</v>
       </c>
       <c r="C152">
@@ -30988,7 +30920,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="B153" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201032</v>
       </c>
       <c r="C153">
@@ -31009,7 +30941,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="B154" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201033</v>
       </c>
       <c r="C154">
@@ -31030,7 +30962,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="B155" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201034</v>
       </c>
       <c r="C155">
@@ -31051,7 +30983,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="B156" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201035</v>
       </c>
       <c r="C156">
@@ -31072,7 +31004,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="B157" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201036</v>
       </c>
       <c r="C157">
@@ -31093,7 +31025,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="B158" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100201037</v>
       </c>
       <c r="C158">
@@ -31117,7 +31049,7 @@
         <v>11</v>
       </c>
       <c r="B159" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202001</v>
       </c>
       <c r="C159">
@@ -31141,7 +31073,7 @@
         <v>11</v>
       </c>
       <c r="B160" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202002</v>
       </c>
       <c r="C160">
@@ -31165,7 +31097,7 @@
         <v>11</v>
       </c>
       <c r="B161" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202003</v>
       </c>
       <c r="C161">
@@ -31189,7 +31121,7 @@
         <v>11</v>
       </c>
       <c r="B162" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202004</v>
       </c>
       <c r="C162">
@@ -31213,7 +31145,7 @@
         <v>11</v>
       </c>
       <c r="B163" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202005</v>
       </c>
       <c r="C163">
@@ -31237,7 +31169,7 @@
         <v>11</v>
       </c>
       <c r="B164" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202006</v>
       </c>
       <c r="C164">
@@ -31261,7 +31193,7 @@
         <v>11</v>
       </c>
       <c r="B165" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202007</v>
       </c>
       <c r="C165">
@@ -31285,7 +31217,7 @@
         <v>11</v>
       </c>
       <c r="B166" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202008</v>
       </c>
       <c r="C166">
@@ -31309,7 +31241,7 @@
         <v>11</v>
       </c>
       <c r="B167" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202009</v>
       </c>
       <c r="C167">
@@ -31333,7 +31265,7 @@
         <v>11</v>
       </c>
       <c r="B168" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202010</v>
       </c>
       <c r="C168">
@@ -31357,7 +31289,7 @@
         <v>11</v>
       </c>
       <c r="B169" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202011</v>
       </c>
       <c r="C169">
@@ -31381,7 +31313,7 @@
         <v>11</v>
       </c>
       <c r="B170" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202012</v>
       </c>
       <c r="C170">
@@ -31405,7 +31337,7 @@
         <v>11</v>
       </c>
       <c r="B171" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202013</v>
       </c>
       <c r="C171">
@@ -31429,7 +31361,7 @@
         <v>11</v>
       </c>
       <c r="B172" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202014</v>
       </c>
       <c r="C172">
@@ -31453,7 +31385,7 @@
         <v>11</v>
       </c>
       <c r="B173" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202015</v>
       </c>
       <c r="C173">
@@ -31477,7 +31409,7 @@
         <v>11</v>
       </c>
       <c r="B174" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202016</v>
       </c>
       <c r="C174">
@@ -31501,7 +31433,7 @@
         <v>11</v>
       </c>
       <c r="B175" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202017</v>
       </c>
       <c r="C175">
@@ -31525,7 +31457,7 @@
         <v>11</v>
       </c>
       <c r="B176" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202018</v>
       </c>
       <c r="C176">
@@ -31549,7 +31481,7 @@
         <v>11</v>
       </c>
       <c r="B177" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202019</v>
       </c>
       <c r="C177">
@@ -31573,7 +31505,7 @@
         <v>11</v>
       </c>
       <c r="B178" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202020</v>
       </c>
       <c r="C178">
@@ -31597,7 +31529,7 @@
         <v>11</v>
       </c>
       <c r="B179" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202021</v>
       </c>
       <c r="C179">
@@ -31621,7 +31553,7 @@
         <v>11</v>
       </c>
       <c r="B180" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202022</v>
       </c>
       <c r="C180">
@@ -31645,7 +31577,7 @@
         <v>11</v>
       </c>
       <c r="B181" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202023</v>
       </c>
       <c r="C181">
@@ -31669,7 +31601,7 @@
         <v>11</v>
       </c>
       <c r="B182" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202024</v>
       </c>
       <c r="C182">
@@ -31693,7 +31625,7 @@
         <v>11</v>
       </c>
       <c r="B183" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202025</v>
       </c>
       <c r="C183">
@@ -31717,7 +31649,7 @@
         <v>11</v>
       </c>
       <c r="B184" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202026</v>
       </c>
       <c r="C184">
@@ -31741,7 +31673,7 @@
         <v>11</v>
       </c>
       <c r="B185" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202027</v>
       </c>
       <c r="C185">
@@ -31765,7 +31697,7 @@
         <v>11</v>
       </c>
       <c r="B186" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202028</v>
       </c>
       <c r="C186">
@@ -31789,7 +31721,7 @@
         <v>11</v>
       </c>
       <c r="B187" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202029</v>
       </c>
       <c r="C187">
@@ -31813,7 +31745,7 @@
         <v>11</v>
       </c>
       <c r="B188" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202030</v>
       </c>
       <c r="C188">
@@ -31837,7 +31769,7 @@
         <v>11</v>
       </c>
       <c r="B189" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202031</v>
       </c>
       <c r="C189">
@@ -31861,7 +31793,7 @@
         <v>11</v>
       </c>
       <c r="B190" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202032</v>
       </c>
       <c r="C190">
@@ -31885,7 +31817,7 @@
         <v>11</v>
       </c>
       <c r="B191" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100202033</v>
       </c>
       <c r="C191">
@@ -31909,7 +31841,7 @@
         <v>11</v>
       </c>
       <c r="B192" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100205001</v>
       </c>
       <c r="C192">
@@ -31933,7 +31865,7 @@
         <v>11</v>
       </c>
       <c r="B193" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100205002</v>
       </c>
       <c r="C193">
@@ -31957,7 +31889,7 @@
         <v>11</v>
       </c>
       <c r="B194" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100205003</v>
       </c>
       <c r="C194">
@@ -31981,7 +31913,7 @@
         <v>11</v>
       </c>
       <c r="B195" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100205004</v>
       </c>
       <c r="C195">
@@ -32005,7 +31937,7 @@
         <v>11</v>
       </c>
       <c r="B196" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100205005</v>
       </c>
       <c r="C196">
@@ -32029,7 +31961,7 @@
         <v>11</v>
       </c>
       <c r="B197" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100205006</v>
       </c>
       <c r="C197">
@@ -32053,7 +31985,7 @@
         <v>11</v>
       </c>
       <c r="B198" s="19">
-        <f t="shared" ref="B198:B261" si="3">C198*100000+D198</f>
+        <f t="shared" ref="B198:B261" si="2">C198*100000+D198</f>
         <v>100205007</v>
       </c>
       <c r="C198">
@@ -32077,7 +32009,7 @@
         <v>11</v>
       </c>
       <c r="B199" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100205008</v>
       </c>
       <c r="C199">
@@ -32101,7 +32033,7 @@
         <v>11</v>
       </c>
       <c r="B200" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206002</v>
       </c>
       <c r="C200">
@@ -32125,7 +32057,7 @@
         <v>11</v>
       </c>
       <c r="B201" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206003</v>
       </c>
       <c r="C201">
@@ -32149,7 +32081,7 @@
         <v>11</v>
       </c>
       <c r="B202" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206004</v>
       </c>
       <c r="C202">
@@ -32173,7 +32105,7 @@
         <v>11</v>
       </c>
       <c r="B203" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206005</v>
       </c>
       <c r="C203">
@@ -32197,7 +32129,7 @@
         <v>11</v>
       </c>
       <c r="B204" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206006</v>
       </c>
       <c r="C204">
@@ -32221,7 +32153,7 @@
         <v>11</v>
       </c>
       <c r="B205" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206007</v>
       </c>
       <c r="C205">
@@ -32245,7 +32177,7 @@
         <v>11</v>
       </c>
       <c r="B206" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206008</v>
       </c>
       <c r="C206">
@@ -32269,7 +32201,7 @@
         <v>11</v>
       </c>
       <c r="B207" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206009</v>
       </c>
       <c r="C207">
@@ -32293,7 +32225,7 @@
         <v>11</v>
       </c>
       <c r="B208" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206010</v>
       </c>
       <c r="C208">
@@ -32317,7 +32249,7 @@
         <v>11</v>
       </c>
       <c r="B209" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100206011</v>
       </c>
       <c r="C209">
@@ -32341,7 +32273,7 @@
         <v>11</v>
       </c>
       <c r="B210" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207001</v>
       </c>
       <c r="C210">
@@ -32365,7 +32297,7 @@
         <v>11</v>
       </c>
       <c r="B211" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207002</v>
       </c>
       <c r="C211">
@@ -32389,7 +32321,7 @@
         <v>11</v>
       </c>
       <c r="B212" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207003</v>
       </c>
       <c r="C212">
@@ -32413,7 +32345,7 @@
         <v>11</v>
       </c>
       <c r="B213" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207005</v>
       </c>
       <c r="C213">
@@ -32437,7 +32369,7 @@
         <v>11</v>
       </c>
       <c r="B214" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207006</v>
       </c>
       <c r="C214">
@@ -32461,7 +32393,7 @@
         <v>11</v>
       </c>
       <c r="B215" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207007</v>
       </c>
       <c r="C215">
@@ -32485,7 +32417,7 @@
         <v>11</v>
       </c>
       <c r="B216" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207008</v>
       </c>
       <c r="C216">
@@ -32509,7 +32441,7 @@
         <v>11</v>
       </c>
       <c r="B217" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207009</v>
       </c>
       <c r="C217">
@@ -32533,7 +32465,7 @@
         <v>11</v>
       </c>
       <c r="B218" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207010</v>
       </c>
       <c r="C218">
@@ -32557,7 +32489,7 @@
         <v>11</v>
       </c>
       <c r="B219" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207011</v>
       </c>
       <c r="C219">
@@ -32581,7 +32513,7 @@
         <v>11</v>
       </c>
       <c r="B220" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207012</v>
       </c>
       <c r="C220">
@@ -32605,7 +32537,7 @@
         <v>11</v>
       </c>
       <c r="B221" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207013</v>
       </c>
       <c r="C221">
@@ -32629,7 +32561,7 @@
         <v>11</v>
       </c>
       <c r="B222" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207014</v>
       </c>
       <c r="C222">
@@ -32653,7 +32585,7 @@
         <v>11</v>
       </c>
       <c r="B223" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207015</v>
       </c>
       <c r="C223">
@@ -32677,7 +32609,7 @@
         <v>11</v>
       </c>
       <c r="B224" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207016</v>
       </c>
       <c r="C224">
@@ -32701,7 +32633,7 @@
         <v>11</v>
       </c>
       <c r="B225" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207017</v>
       </c>
       <c r="C225">
@@ -32725,7 +32657,7 @@
         <v>11</v>
       </c>
       <c r="B226" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207018</v>
       </c>
       <c r="C226">
@@ -32749,7 +32681,7 @@
         <v>11</v>
       </c>
       <c r="B227" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100207019</v>
       </c>
       <c r="C227">
@@ -32773,7 +32705,7 @@
         <v>11</v>
       </c>
       <c r="B228" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208001</v>
       </c>
       <c r="C228">
@@ -32797,7 +32729,7 @@
         <v>11</v>
       </c>
       <c r="B229" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208003</v>
       </c>
       <c r="C229">
@@ -32821,7 +32753,7 @@
         <v>11</v>
       </c>
       <c r="B230" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208004</v>
       </c>
       <c r="C230">
@@ -32845,7 +32777,7 @@
         <v>11</v>
       </c>
       <c r="B231" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208005</v>
       </c>
       <c r="C231">
@@ -32869,7 +32801,7 @@
         <v>11</v>
       </c>
       <c r="B232" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208007</v>
       </c>
       <c r="C232">
@@ -32893,7 +32825,7 @@
         <v>11</v>
       </c>
       <c r="B233" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208008</v>
       </c>
       <c r="C233">
@@ -32917,7 +32849,7 @@
         <v>11</v>
       </c>
       <c r="B234" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208009</v>
       </c>
       <c r="C234">
@@ -32941,7 +32873,7 @@
         <v>11</v>
       </c>
       <c r="B235" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208010</v>
       </c>
       <c r="C235">
@@ -32965,7 +32897,7 @@
         <v>11</v>
       </c>
       <c r="B236" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208011</v>
       </c>
       <c r="C236">
@@ -32989,7 +32921,7 @@
         <v>11</v>
       </c>
       <c r="B237" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208012</v>
       </c>
       <c r="C237">
@@ -33013,7 +32945,7 @@
         <v>11</v>
       </c>
       <c r="B238" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100208013</v>
       </c>
       <c r="C238">
@@ -33037,7 +32969,7 @@
         <v>11</v>
       </c>
       <c r="B239" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100212001</v>
       </c>
       <c r="C239">
@@ -33061,7 +32993,7 @@
         <v>11</v>
       </c>
       <c r="B240" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>100212002</v>
       </c>
       <c r="C240">
@@ -33085,7 +33017,7 @@
         <v>11</v>
       </c>
       <c r="B241" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109001</v>
       </c>
       <c r="C241">
@@ -33109,7 +33041,7 @@
         <v>11</v>
       </c>
       <c r="B242" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109002</v>
       </c>
       <c r="C242">
@@ -33133,7 +33065,7 @@
         <v>11</v>
       </c>
       <c r="B243" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109003</v>
       </c>
       <c r="C243">
@@ -33157,7 +33089,7 @@
         <v>11</v>
       </c>
       <c r="B244" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109004</v>
       </c>
       <c r="C244">
@@ -33181,7 +33113,7 @@
         <v>11</v>
       </c>
       <c r="B245" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109005</v>
       </c>
       <c r="C245">
@@ -33205,7 +33137,7 @@
         <v>11</v>
       </c>
       <c r="B246" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109006</v>
       </c>
       <c r="C246">
@@ -33229,7 +33161,7 @@
         <v>11</v>
       </c>
       <c r="B247" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109007</v>
       </c>
       <c r="C247">
@@ -33253,7 +33185,7 @@
         <v>11</v>
       </c>
       <c r="B248" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109008</v>
       </c>
       <c r="C248">
@@ -33277,7 +33209,7 @@
         <v>11</v>
       </c>
       <c r="B249" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109009</v>
       </c>
       <c r="C249">
@@ -33301,7 +33233,7 @@
         <v>11</v>
       </c>
       <c r="B250" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109010</v>
       </c>
       <c r="C250">
@@ -33325,7 +33257,7 @@
         <v>11</v>
       </c>
       <c r="B251" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>200109011</v>
       </c>
       <c r="C251">
@@ -33349,7 +33281,7 @@
         <v>11</v>
       </c>
       <c r="B252" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>300151001</v>
       </c>
       <c r="C252">
@@ -33373,7 +33305,7 @@
         <v>11</v>
       </c>
       <c r="B253" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>300152001</v>
       </c>
       <c r="C253">
@@ -33397,7 +33329,7 @@
         <v>11</v>
       </c>
       <c r="B254" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>300191012</v>
       </c>
       <c r="C254">
@@ -33421,7 +33353,7 @@
         <v>11</v>
       </c>
       <c r="B255" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>300192005</v>
       </c>
       <c r="C255">
@@ -33445,7 +33377,7 @@
         <v>11</v>
       </c>
       <c r="B256" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>400101002</v>
       </c>
       <c r="C256">
@@ -33469,7 +33401,7 @@
         <v>11</v>
       </c>
       <c r="B257" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>400101003</v>
       </c>
       <c r="C257">
@@ -33493,7 +33425,7 @@
         <v>11</v>
       </c>
       <c r="B258" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>400101004</v>
       </c>
       <c r="C258">
@@ -33517,7 +33449,7 @@
         <v>11</v>
       </c>
       <c r="B259" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>400101005</v>
       </c>
       <c r="C259">
@@ -33541,7 +33473,7 @@
         <v>11</v>
       </c>
       <c r="B260" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>400101006</v>
       </c>
       <c r="C260">
@@ -33565,7 +33497,7 @@
         <v>11</v>
       </c>
       <c r="B261" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>400101007</v>
       </c>
       <c r="C261">
@@ -33589,7 +33521,7 @@
         <v>11</v>
       </c>
       <c r="B262" s="19">
-        <f t="shared" ref="B262:B325" si="4">C262*100000+D262</f>
+        <f t="shared" ref="B262:B325" si="3">C262*100000+D262</f>
         <v>400101008</v>
       </c>
       <c r="C262">
@@ -33613,7 +33545,7 @@
         <v>11</v>
       </c>
       <c r="B263" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400101009</v>
       </c>
       <c r="C263">
@@ -33637,7 +33569,7 @@
         <v>11</v>
       </c>
       <c r="B264" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400101010</v>
       </c>
       <c r="C264">
@@ -33661,7 +33593,7 @@
         <v>11</v>
       </c>
       <c r="B265" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400101011</v>
       </c>
       <c r="C265">
@@ -33685,7 +33617,7 @@
         <v>11</v>
       </c>
       <c r="B266" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400101012</v>
       </c>
       <c r="C266">
@@ -33709,7 +33641,7 @@
         <v>11</v>
       </c>
       <c r="B267" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102001</v>
       </c>
       <c r="C267">
@@ -33733,7 +33665,7 @@
         <v>11</v>
       </c>
       <c r="B268" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102002</v>
       </c>
       <c r="C268">
@@ -33757,7 +33689,7 @@
         <v>11</v>
       </c>
       <c r="B269" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102003</v>
       </c>
       <c r="C269">
@@ -33781,7 +33713,7 @@
         <v>11</v>
       </c>
       <c r="B270" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102004</v>
       </c>
       <c r="C270">
@@ -33805,7 +33737,7 @@
         <v>11</v>
       </c>
       <c r="B271" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102005</v>
       </c>
       <c r="C271">
@@ -33829,7 +33761,7 @@
         <v>11</v>
       </c>
       <c r="B272" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102006</v>
       </c>
       <c r="C272">
@@ -33853,7 +33785,7 @@
         <v>11</v>
       </c>
       <c r="B273" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102007</v>
       </c>
       <c r="C273">
@@ -33877,7 +33809,7 @@
         <v>11</v>
       </c>
       <c r="B274" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102008</v>
       </c>
       <c r="C274">
@@ -33901,7 +33833,7 @@
         <v>11</v>
       </c>
       <c r="B275" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102009</v>
       </c>
       <c r="C275">
@@ -33925,7 +33857,7 @@
         <v>11</v>
       </c>
       <c r="B276" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102010</v>
       </c>
       <c r="C276">
@@ -33949,7 +33881,7 @@
         <v>11</v>
       </c>
       <c r="B277" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102011</v>
       </c>
       <c r="C277">
@@ -33973,7 +33905,7 @@
         <v>11</v>
       </c>
       <c r="B278" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102012</v>
       </c>
       <c r="C278">
@@ -33997,7 +33929,7 @@
         <v>11</v>
       </c>
       <c r="B279" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102013</v>
       </c>
       <c r="C279">
@@ -34021,7 +33953,7 @@
         <v>11</v>
       </c>
       <c r="B280" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102014</v>
       </c>
       <c r="C280">
@@ -34045,7 +33977,7 @@
         <v>11</v>
       </c>
       <c r="B281" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102015</v>
       </c>
       <c r="C281">
@@ -34069,7 +34001,7 @@
         <v>11</v>
       </c>
       <c r="B282" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102016</v>
       </c>
       <c r="C282">
@@ -34093,7 +34025,7 @@
         <v>11</v>
       </c>
       <c r="B283" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102017</v>
       </c>
       <c r="C283">
@@ -34117,7 +34049,7 @@
         <v>11</v>
       </c>
       <c r="B284" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102018</v>
       </c>
       <c r="C284">
@@ -34141,7 +34073,7 @@
         <v>11</v>
       </c>
       <c r="B285" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102019</v>
       </c>
       <c r="C285">
@@ -34165,7 +34097,7 @@
         <v>11</v>
       </c>
       <c r="B286" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102020</v>
       </c>
       <c r="C286">
@@ -34189,7 +34121,7 @@
         <v>11</v>
       </c>
       <c r="B287" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102021</v>
       </c>
       <c r="C287">
@@ -34213,7 +34145,7 @@
         <v>11</v>
       </c>
       <c r="B288" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102022</v>
       </c>
       <c r="C288">
@@ -34237,7 +34169,7 @@
         <v>11</v>
       </c>
       <c r="B289" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102023</v>
       </c>
       <c r="C289">
@@ -34261,7 +34193,7 @@
         <v>11</v>
       </c>
       <c r="B290" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102024</v>
       </c>
       <c r="C290">
@@ -34285,7 +34217,7 @@
         <v>11</v>
       </c>
       <c r="B291" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102025</v>
       </c>
       <c r="C291">
@@ -34309,7 +34241,7 @@
         <v>11</v>
       </c>
       <c r="B292" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102026</v>
       </c>
       <c r="C292">
@@ -34333,7 +34265,7 @@
         <v>11</v>
       </c>
       <c r="B293" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102027</v>
       </c>
       <c r="C293">
@@ -34357,7 +34289,7 @@
         <v>11</v>
       </c>
       <c r="B294" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102028</v>
       </c>
       <c r="C294">
@@ -34381,7 +34313,7 @@
         <v>11</v>
       </c>
       <c r="B295" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102029</v>
       </c>
       <c r="C295">
@@ -34405,7 +34337,7 @@
         <v>11</v>
       </c>
       <c r="B296" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102030</v>
       </c>
       <c r="C296">
@@ -34429,7 +34361,7 @@
         <v>11</v>
       </c>
       <c r="B297" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102031</v>
       </c>
       <c r="C297">
@@ -34453,7 +34385,7 @@
         <v>11</v>
       </c>
       <c r="B298" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102032</v>
       </c>
       <c r="C298">
@@ -34477,7 +34409,7 @@
         <v>11</v>
       </c>
       <c r="B299" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400102033</v>
       </c>
       <c r="C299">
@@ -34501,7 +34433,7 @@
         <v>11</v>
       </c>
       <c r="B300" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105001</v>
       </c>
       <c r="C300">
@@ -34525,7 +34457,7 @@
         <v>11</v>
       </c>
       <c r="B301" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105002</v>
       </c>
       <c r="C301">
@@ -34549,7 +34481,7 @@
         <v>11</v>
       </c>
       <c r="B302" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105003</v>
       </c>
       <c r="C302">
@@ -34573,7 +34505,7 @@
         <v>11</v>
       </c>
       <c r="B303" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105004</v>
       </c>
       <c r="C303">
@@ -34597,7 +34529,7 @@
         <v>11</v>
       </c>
       <c r="B304" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105005</v>
       </c>
       <c r="C304">
@@ -34621,7 +34553,7 @@
         <v>11</v>
       </c>
       <c r="B305" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105006</v>
       </c>
       <c r="C305">
@@ -34645,7 +34577,7 @@
         <v>11</v>
       </c>
       <c r="B306" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105007</v>
       </c>
       <c r="C306">
@@ -34669,7 +34601,7 @@
         <v>11</v>
       </c>
       <c r="B307" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400105008</v>
       </c>
       <c r="C307">
@@ -34693,7 +34625,7 @@
         <v>11</v>
       </c>
       <c r="B308" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106002</v>
       </c>
       <c r="C308">
@@ -34717,7 +34649,7 @@
         <v>11</v>
       </c>
       <c r="B309" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106003</v>
       </c>
       <c r="C309">
@@ -34741,7 +34673,7 @@
         <v>11</v>
       </c>
       <c r="B310" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106004</v>
       </c>
       <c r="C310">
@@ -34765,7 +34697,7 @@
         <v>11</v>
       </c>
       <c r="B311" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106005</v>
       </c>
       <c r="C311">
@@ -34789,7 +34721,7 @@
         <v>11</v>
       </c>
       <c r="B312" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106006</v>
       </c>
       <c r="C312">
@@ -34813,7 +34745,7 @@
         <v>11</v>
       </c>
       <c r="B313" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106007</v>
       </c>
       <c r="C313">
@@ -34837,7 +34769,7 @@
         <v>11</v>
       </c>
       <c r="B314" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106008</v>
       </c>
       <c r="C314">
@@ -34861,7 +34793,7 @@
         <v>11</v>
       </c>
       <c r="B315" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106009</v>
       </c>
       <c r="C315">
@@ -34885,7 +34817,7 @@
         <v>11</v>
       </c>
       <c r="B316" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106010</v>
       </c>
       <c r="C316">
@@ -34909,7 +34841,7 @@
         <v>11</v>
       </c>
       <c r="B317" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400106011</v>
       </c>
       <c r="C317">
@@ -34933,7 +34865,7 @@
         <v>11</v>
       </c>
       <c r="B318" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107001</v>
       </c>
       <c r="C318">
@@ -34957,7 +34889,7 @@
         <v>11</v>
       </c>
       <c r="B319" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107002</v>
       </c>
       <c r="C319">
@@ -34981,7 +34913,7 @@
         <v>11</v>
       </c>
       <c r="B320" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107003</v>
       </c>
       <c r="C320">
@@ -35005,7 +34937,7 @@
         <v>11</v>
       </c>
       <c r="B321" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107005</v>
       </c>
       <c r="C321">
@@ -35029,7 +34961,7 @@
         <v>11</v>
       </c>
       <c r="B322" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107006</v>
       </c>
       <c r="C322">
@@ -35053,7 +34985,7 @@
         <v>11</v>
       </c>
       <c r="B323" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107007</v>
       </c>
       <c r="C323">
@@ -35077,7 +35009,7 @@
         <v>11</v>
       </c>
       <c r="B324" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107008</v>
       </c>
       <c r="C324">
@@ -35101,7 +35033,7 @@
         <v>11</v>
       </c>
       <c r="B325" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>400107009</v>
       </c>
       <c r="C325">
@@ -35125,7 +35057,7 @@
         <v>11</v>
       </c>
       <c r="B326" s="19">
-        <f t="shared" ref="B326:B363" si="5">C326*100000+D326</f>
+        <f t="shared" ref="B326:B363" si="4">C326*100000+D326</f>
         <v>400107010</v>
       </c>
       <c r="C326">
@@ -35149,7 +35081,7 @@
         <v>11</v>
       </c>
       <c r="B327" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107011</v>
       </c>
       <c r="C327">
@@ -35173,7 +35105,7 @@
         <v>11</v>
       </c>
       <c r="B328" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107012</v>
       </c>
       <c r="C328">
@@ -35197,7 +35129,7 @@
         <v>11</v>
       </c>
       <c r="B329" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107013</v>
       </c>
       <c r="C329">
@@ -35221,7 +35153,7 @@
         <v>11</v>
       </c>
       <c r="B330" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107014</v>
       </c>
       <c r="C330">
@@ -35245,7 +35177,7 @@
         <v>11</v>
       </c>
       <c r="B331" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107015</v>
       </c>
       <c r="C331">
@@ -35269,7 +35201,7 @@
         <v>11</v>
       </c>
       <c r="B332" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107016</v>
       </c>
       <c r="C332">
@@ -35293,7 +35225,7 @@
         <v>11</v>
       </c>
       <c r="B333" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107017</v>
       </c>
       <c r="C333">
@@ -35317,7 +35249,7 @@
         <v>11</v>
       </c>
       <c r="B334" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107018</v>
       </c>
       <c r="C334">
@@ -35341,7 +35273,7 @@
         <v>11</v>
       </c>
       <c r="B335" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400107019</v>
       </c>
       <c r="C335">
@@ -35365,7 +35297,7 @@
         <v>11</v>
       </c>
       <c r="B336" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108001</v>
       </c>
       <c r="C336">
@@ -35389,7 +35321,7 @@
         <v>11</v>
       </c>
       <c r="B337" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108003</v>
       </c>
       <c r="C337">
@@ -35413,7 +35345,7 @@
         <v>11</v>
       </c>
       <c r="B338" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108004</v>
       </c>
       <c r="C338">
@@ -35437,7 +35369,7 @@
         <v>11</v>
       </c>
       <c r="B339" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108005</v>
       </c>
       <c r="C339">
@@ -35461,7 +35393,7 @@
         <v>11</v>
       </c>
       <c r="B340" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108007</v>
       </c>
       <c r="C340">
@@ -35485,7 +35417,7 @@
         <v>11</v>
       </c>
       <c r="B341" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108008</v>
       </c>
       <c r="C341">
@@ -35509,7 +35441,7 @@
         <v>11</v>
       </c>
       <c r="B342" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108009</v>
       </c>
       <c r="C342">
@@ -35533,7 +35465,7 @@
         <v>11</v>
       </c>
       <c r="B343" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108010</v>
       </c>
       <c r="C343">
@@ -35557,7 +35489,7 @@
         <v>11</v>
       </c>
       <c r="B344" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108011</v>
       </c>
       <c r="C344">
@@ -35581,7 +35513,7 @@
         <v>11</v>
       </c>
       <c r="B345" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108012</v>
       </c>
       <c r="C345">
@@ -35605,7 +35537,7 @@
         <v>11</v>
       </c>
       <c r="B346" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400108013</v>
       </c>
       <c r="C346">
@@ -35629,7 +35561,7 @@
         <v>11</v>
       </c>
       <c r="B347" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400112001</v>
       </c>
       <c r="C347">
@@ -35653,7 +35585,7 @@
         <v>11</v>
       </c>
       <c r="B348" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>400112002</v>
       </c>
       <c r="C348">
@@ -35674,7 +35606,7 @@
     </row>
     <row r="349" spans="1:7">
       <c r="B349" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200202003</v>
       </c>
       <c r="C349">
@@ -35695,7 +35627,7 @@
     </row>
     <row r="350" spans="1:7">
       <c r="B350" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200202009</v>
       </c>
       <c r="C350">
@@ -35716,7 +35648,7 @@
     </row>
     <row r="351" spans="1:7">
       <c r="B351" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200202013</v>
       </c>
       <c r="C351">
@@ -35737,7 +35669,7 @@
     </row>
     <row r="352" spans="1:7">
       <c r="B352" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200202022</v>
       </c>
       <c r="C352">
@@ -35758,7 +35690,7 @@
     </row>
     <row r="353" spans="2:7">
       <c r="B353" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200202029</v>
       </c>
       <c r="C353">
@@ -35779,7 +35711,7 @@
     </row>
     <row r="354" spans="2:7">
       <c r="B354" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200202032</v>
       </c>
       <c r="C354">
@@ -35800,7 +35732,7 @@
     </row>
     <row r="355" spans="2:7">
       <c r="B355" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200205004</v>
       </c>
       <c r="C355">
@@ -35821,7 +35753,7 @@
     </row>
     <row r="356" spans="2:7">
       <c r="B356" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200206006</v>
       </c>
       <c r="C356">
@@ -35842,7 +35774,7 @@
     </row>
     <row r="357" spans="2:7">
       <c r="B357" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200208005</v>
       </c>
       <c r="C357">
@@ -35863,7 +35795,7 @@
     </row>
     <row r="358" spans="2:7">
       <c r="B358" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200206008</v>
       </c>
       <c r="C358">
@@ -35884,7 +35816,7 @@
     </row>
     <row r="359" spans="2:7">
       <c r="B359" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200207008</v>
       </c>
       <c r="C359">
@@ -35905,7 +35837,7 @@
     </row>
     <row r="360" spans="2:7">
       <c r="B360" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200208012</v>
       </c>
       <c r="C360">
@@ -35926,7 +35858,7 @@
     </row>
     <row r="361" spans="2:7">
       <c r="B361" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200301008</v>
       </c>
       <c r="C361">
@@ -35947,7 +35879,6 @@
     </row>
     <row r="362" spans="2:7">
       <c r="B362" s="19">
-        <f t="shared" si="5"/>
         <v>200301011</v>
       </c>
       <c r="C362">
@@ -35968,7 +35899,6 @@
     </row>
     <row r="363" spans="2:7">
       <c r="B363" s="19">
-        <f t="shared" si="5"/>
         <v>200301013</v>
       </c>
       <c r="C363">
@@ -36214,7 +36144,7 @@
         <v>100501</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="D7">
         <v>45</v>
@@ -36229,7 +36159,7 @@
         <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -36246,7 +36176,7 @@
         <v>100502</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="D8">
         <v>45</v>
@@ -36258,10 +36188,10 @@
         <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -36278,7 +36208,7 @@
         <v>100503</v>
       </c>
       <c r="C9" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -36287,13 +36217,13 @@
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="H9" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -36354,7 +36284,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s">
         <v>87</v>
@@ -36383,10 +36313,10 @@
         <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s">
         <v>87</v>
@@ -36415,7 +36345,7 @@
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s">
         <v>87</v>
@@ -36441,7 +36371,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="F14" t="s">
         <v>87</v>
@@ -36499,7 +36429,7 @@
         <v>100701</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D16">
         <v>65</v>
@@ -36508,13 +36438,13 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s">
         <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -36531,7 +36461,7 @@
         <v>100702</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D17">
         <v>15</v>
@@ -36546,7 +36476,7 @@
         <v>87</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -36566,7 +36496,7 @@
         <v>100703</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D18">
         <v>15</v>
@@ -36575,13 +36505,13 @@
         <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -36601,22 +36531,22 @@
         <v>100704</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
         <v>87</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -36665,7 +36595,7 @@
         <v>100801</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D21">
         <v>37</v>
@@ -36677,10 +36607,10 @@
         <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -36700,7 +36630,7 @@
         <v>100802</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D22">
         <v>55</v>
@@ -36709,13 +36639,13 @@
         <v>80</v>
       </c>
       <c r="F22" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
@@ -36735,7 +36665,7 @@
         <v>100803</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -36744,13 +36674,13 @@
         <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H23" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -36767,22 +36697,22 @@
         <v>100804</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s">
         <v>87</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H24" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
@@ -36831,7 +36761,7 @@
         <v>100901</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -36840,13 +36770,13 @@
         <v>87</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G26" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
@@ -36863,7 +36793,7 @@
         <v>100902</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D27">
         <v>25</v>
@@ -36875,10 +36805,10 @@
         <v>87</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
@@ -36898,7 +36828,7 @@
         <v>100903</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28">
         <v>25</v>
@@ -36907,13 +36837,13 @@
         <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -36933,7 +36863,7 @@
         <v>100904</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D29">
         <v>25</v>
@@ -36945,10 +36875,10 @@
         <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
@@ -37291,7 +37221,7 @@
         <v>657</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
         <v>936</v>
@@ -37314,7 +37244,7 @@
         <v>663</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
         <v>940</v>
@@ -37337,7 +37267,7 @@
         <v>670</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>943</v>
@@ -37383,7 +37313,7 @@
         <v>684</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>949</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4170" uniqueCount="1508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4179" uniqueCount="1508">
   <si>
     <t>##var</t>
   </si>
@@ -2546,6 +2546,9 @@
     <t>暂不使用，作为低位保留段。</t>
   </si>
   <si>
+    <t>BuildChannelMask</t>
+  </si>
+  <si>
     <t>BoxType</t>
   </si>
   <si>
@@ -2574,6 +2577,9 @@
   </si>
   <si>
     <t>IsEnabled</t>
+  </si>
+  <si>
+    <t>EBuildChannelMask</t>
   </si>
   <si>
     <t>EBlindBoxType</t>
@@ -2628,6 +2634,9 @@
     <t>奖励盒名称</t>
   </si>
   <si>
+    <t>适用构建渠道</t>
+  </si>
+  <si>
     <t>奖励盒类型</t>
   </si>
   <si>
@@ -2658,6 +2667,9 @@
     <t>标准盲盒</t>
   </si>
   <si>
+    <t>Playtest|Release</t>
+  </si>
+  <si>
     <t>装扮盲盒</t>
   </si>
   <si>
@@ -2685,6 +2697,9 @@
     <t>DEMO本地普通盲盒</t>
   </si>
   <si>
+    <t>Demo</t>
+  </si>
+  <si>
     <t>ExcludeDrawnInThisBox</t>
   </si>
   <si>
@@ -2694,6 +2709,9 @@
     <t>测试活动盲盒</t>
   </si>
   <si>
+    <t>Playtest</t>
+  </si>
+  <si>
     <t>活动盲盒</t>
   </si>
   <si>
@@ -2754,9 +2772,6 @@
     <t>SteamCompletionReceiptItemDefId</t>
   </si>
   <si>
-    <t>EBuildChannelMask</t>
-  </si>
-  <si>
     <t>首轮奖励序列中，当前 Schedule 完成后进入的下一条 BlindBoxSchedule.Id；末条首轮 Schedule 填 0，循环 Schedule 填 0；所有启用的首轮 Schedule 必须组成无环、无分叉的单链，顺序不再根据 StartSeconds 或数字 ID 推断。</t>
   </si>
   <si>
@@ -2848,12 +2863,6 @@
   </si>
   <si>
     <t>Steam完成回执DefID</t>
-  </si>
-  <si>
-    <t>Playtest|Release</t>
-  </si>
-  <si>
-    <t>Demo</t>
   </si>
   <si>
     <t>Rarity</t>
@@ -3206,9 +3215,6 @@
   </si>
   <si>
     <t>IsPinned</t>
-  </si>
-  <si>
-    <t>BuildChannelMask</t>
   </si>
   <si>
     <t>TooltipKey</t>
@@ -3331,9 +3337,6 @@
     <t>启用</t>
   </si>
   <si>
-    <t>适用构建渠道</t>
-  </si>
-  <si>
     <t>提示文本Key</t>
   </si>
   <si>
@@ -3443,9 +3446,6 @@
   </si>
   <si>
     <t>Test01</t>
-  </si>
-  <si>
-    <t>Playtest</t>
   </si>
   <si>
     <t>Test</t>
@@ -15434,10 +15434,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="D1" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -15454,7 +15454,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -15471,10 +15471,10 @@
         <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E3" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -15496,7 +15496,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D5" t="s">
         <v>204</v>
@@ -15513,7 +15513,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D6" t="s">
         <v>338</v>
@@ -15527,7 +15527,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="D7" t="s">
         <v>525</v>
@@ -15551,7 +15551,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D10" t="s">
         <v>403</v>
@@ -15658,10 +15658,10 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -15686,10 +15686,10 @@
         <v>53</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D3" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15851,58 +15851,58 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D1" t="s">
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="F1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G1" t="s">
-        <v>994</v>
+        <v>774</v>
       </c>
       <c r="H1" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="I1" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="J1" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K1" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="L1" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="M1" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="N1" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="O1" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="P1" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="Q1" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="R1" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="S1" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="T1" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -15925,7 +15925,7 @@
         <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>843</v>
+        <v>785</v>
       </c>
       <c r="H2" t="s">
         <v>29</v>
@@ -15943,10 +15943,10 @@
         <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="N2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -15972,61 +15972,61 @@
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -16034,64 +16034,64 @@
         <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C4" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D4" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="E4" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="F4" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="G4" t="s">
-        <v>1034</v>
+        <v>803</v>
       </c>
       <c r="H4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="I4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="K4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="L4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="M4" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="N4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="O4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="P4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="Q4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="R4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="S4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="T4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="U4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -16099,7 +16099,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -16111,25 +16111,25 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="I5" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="J5" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K5" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="L5" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="M5" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N5" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O5">
         <v>92005</v>
@@ -16141,7 +16141,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -16149,7 +16149,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -16161,25 +16161,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="I6" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="J6" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K6" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="L6" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M6" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N6" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -16191,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -16199,7 +16199,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -16211,25 +16211,25 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="I7" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J7" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K7" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="L7" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="M7" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -16241,7 +16241,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -16249,7 +16249,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -16261,25 +16261,25 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J8" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K8" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L8" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M8" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N8" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O8">
         <v>91012</v>
@@ -16291,7 +16291,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:21">
@@ -16299,7 +16299,7 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -16311,25 +16311,25 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="I9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="J9" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K9" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="L9" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="M9" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N9" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O9">
         <v>92005</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:21">
@@ -16349,7 +16349,7 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D10">
         <v>80</v>
@@ -16361,28 +16361,28 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="H10" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="I10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="J10" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K10" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="L10" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M10" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N10" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -16405,7 +16405,7 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -16417,28 +16417,28 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="H11" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="I11" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J11" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K11" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="L11" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="M11" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N11" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -16461,7 +16461,7 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -16473,25 +16473,25 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I12" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J12" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K12" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L12" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M12" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N12" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -16503,7 +16503,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:21">
@@ -16511,7 +16511,7 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D13">
         <v>60</v>
@@ -16523,28 +16523,28 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="H13" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="I13" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="J13" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K13" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="L13" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="M13" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N13" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O13">
         <v>52001</v>
@@ -16567,7 +16567,7 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D14">
         <v>120</v>
@@ -16579,25 +16579,25 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I14" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J14" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K14" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L14" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M14" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N14" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:21">
@@ -16617,7 +16617,7 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D15">
         <v>120</v>
@@ -16629,28 +16629,28 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="H15" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I15" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J15" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K15" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L15" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M15" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N15" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O15">
         <v>51001</v>
@@ -16673,7 +16673,7 @@
         <v>410001</v>
       </c>
       <c r="C16" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D16">
         <v>2000</v>
@@ -16685,7 +16685,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="H16" t="s">
         <v>1073</v>
@@ -16694,19 +16694,19 @@
         <v>1074</v>
       </c>
       <c r="J16" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K16" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L16" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M16" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N16" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O16">
         <v>51001</v>
@@ -16741,7 +16741,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="H17" t="s">
         <v>1073</v>
@@ -16750,19 +16750,19 @@
         <v>1074</v>
       </c>
       <c r="J17" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K17" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L17" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M17" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N17" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O17">
         <v>51001</v>
@@ -16797,7 +16797,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="H18" t="s">
         <v>1073</v>
@@ -16806,19 +16806,19 @@
         <v>1074</v>
       </c>
       <c r="J18" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K18" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L18" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M18" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N18" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O18">
         <v>51001</v>
@@ -16853,7 +16853,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>1072</v>
+        <v>828</v>
       </c>
       <c r="H19" t="s">
         <v>1073</v>
@@ -16862,19 +16862,19 @@
         <v>1074</v>
       </c>
       <c r="J19" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K19" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L19" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M19" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N19" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O19">
         <v>51001</v>
@@ -16897,7 +16897,7 @@
         <v>2001</v>
       </c>
       <c r="C20" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D20">
         <v>30</v>
@@ -16909,28 +16909,28 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="H20" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="I20" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="J20" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K20" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="L20" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="M20" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N20" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O20">
         <v>9001</v>
@@ -16947,7 +16947,7 @@
         <v>2002</v>
       </c>
       <c r="C21" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D21">
         <v>10</v>
@@ -16959,28 +16959,28 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="H21" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="I21" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="J21" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K21" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="L21" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M21" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N21" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O21">
         <v>9001</v>
@@ -16997,7 +16997,7 @@
         <v>2003</v>
       </c>
       <c r="C22" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D22">
         <v>20</v>
@@ -17009,28 +17009,28 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="H22" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="I22" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J22" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K22" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="L22" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="M22" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N22" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O22">
         <v>9001</v>
@@ -17047,7 +17047,7 @@
         <v>2004</v>
       </c>
       <c r="C23" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D23">
         <v>40</v>
@@ -17059,28 +17059,28 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="H23" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I23" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J23" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K23" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="L23" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M23" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N23" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="O23">
         <v>9001</v>
@@ -17147,7 +17147,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E1" t="s">
         <v>1078</v>
@@ -17183,7 +17183,7 @@
         <v>1087</v>
       </c>
       <c r="P1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="Q1" t="s">
         <v>1088</v>
@@ -17306,7 +17306,7 @@
         <v>1105</v>
       </c>
       <c r="C4" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D4" t="s">
         <v>1106</v>
@@ -17345,7 +17345,7 @@
         <v>1114</v>
       </c>
       <c r="P4" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="Q4" t="s">
         <v>1115</v>
@@ -21981,7 +21981,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{ae5f587b-e675-4cff-bc87-53a6e2e4bfa9}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{0a4b7713-0fd5-47b5-ba07-6aa0ec5707d4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21995,7 +21995,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{8289e015-7ea0-4ae1-b2e9-fdcf407df41b}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{60023efd-9649-403f-86a3-50632cf3e2c9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22009,7 +22009,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{ad2e2a2b-40f5-4f50-8d41-b30a0cc57210}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{c202a918-d989-4da6-8a32-8dcbe53f516b}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22023,7 +22023,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{936bee49-47da-434d-84ea-0b510a264857}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{75179a25-0841-4c07-bacc-2375d39e186d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22037,7 +22037,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{9eaeffdb-c5ec-485f-8a3f-985004881d58}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{79e0b37b-515a-4324-a260-43d2c87e6702}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22051,7 +22051,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{275e5a97-6b52-441d-bdfc-db8479c45625}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{840efd7c-dd5c-47a3-a9ca-7a33e7ab2af1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22065,7 +22065,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{720221e9-3d08-418d-b6fe-0d6e0df55695}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{7f4dfed4-b326-40cd-b0c6-39fc32071eed}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22079,7 +22079,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{1a351250-5fee-4a06-a5c6-18abb998b691}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{aa830b10-4c24-45f9-b0ab-6af4c301fb19}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22093,7 +22093,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{41fde5ed-d9f5-4bd7-af7b-4de1d180d4ce}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{bcf10269-9dc1-4fbe-a24e-fee794e76ded}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -23864,27 +23864,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="35.25" customWidth="1"/>
-    <col min="4" max="4" width="14.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="21.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="22.8333333333333" customWidth="1"/>
-    <col min="7" max="7" width="8.75" customWidth="1"/>
-    <col min="8" max="8" width="19.1666666666667" customWidth="1"/>
-    <col min="9" max="9" width="12.25" customWidth="1"/>
-    <col min="10" max="10" width="16.75" customWidth="1"/>
-    <col min="11" max="11" width="36.75" customWidth="1"/>
-    <col min="12" max="12" width="25.1666666666667" customWidth="1"/>
-    <col min="13" max="13" width="8.83333333333333" customWidth="1"/>
-    <col min="14" max="14" width="23" customWidth="1"/>
-    <col min="15" max="15" width="28.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="14.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="21.0833333333333" customWidth="1"/>
+    <col min="7" max="7" width="22.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="8.75" customWidth="1"/>
+    <col min="9" max="9" width="19.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.25" customWidth="1"/>
+    <col min="11" max="11" width="16.75" customWidth="1"/>
+    <col min="12" max="12" width="36.75" customWidth="1"/>
+    <col min="13" max="13" width="25.1666666666667" customWidth="1"/>
+    <col min="14" max="14" width="8.83333333333333" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="16" width="28.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -23924,8 +23925,11 @@
       <c r="M1" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -23936,392 +23940,416 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G2" t="s">
+        <v>788</v>
+      </c>
+      <c r="H2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
-        <v>787</v>
-      </c>
       <c r="I2" t="s">
+        <v>789</v>
+      </c>
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s">
-        <v>788</v>
-      </c>
       <c r="K2" t="s">
+        <v>790</v>
+      </c>
+      <c r="L2" t="s">
         <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
       </c>
       <c r="M2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>11</v>
+        <v>796</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>795</v>
+        <v>11</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>797</v>
-      </c>
       <c r="M3" s="2" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="4" s="5" customFormat="1" spans="1:13">
+        <v>799</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" s="5" customFormat="1" spans="1:14">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>808</v>
-      </c>
       <c r="M4" s="5" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>811</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>810</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>811</v>
+        <v>813</v>
+      </c>
+      <c r="D5" t="s">
+        <v>814</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="G5">
+        <v>816</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="H5">
         <v>1000</v>
       </c>
-      <c r="H5" t="s">
-        <v>814</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
+      <c r="I5" t="s">
+        <v>818</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
-      <c r="K5" t="s">
-        <v>815</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5" t="s">
+        <v>819</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>820</v>
+      </c>
+      <c r="D6" t="s">
+        <v>814</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="F6" s="16" t="s">
         <v>816</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="G6" s="16" t="s">
         <v>817</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>812</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="G6">
+      <c r="H6">
         <v>1000</v>
       </c>
-      <c r="H6" t="s">
-        <v>814</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
+      <c r="I6" t="s">
+        <v>818</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>815</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6" t="s">
+        <v>819</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7">
         <v>2001</v>
       </c>
       <c r="C7" t="s">
+        <v>822</v>
+      </c>
+      <c r="D7" t="s">
+        <v>814</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>822</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="H7">
+        <v>1000</v>
+      </c>
+      <c r="I7" t="s">
         <v>818</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>818</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>812</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="G7">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="s">
-        <v>814</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
-      <c r="K7" t="s">
-        <v>815</v>
-      </c>
-      <c r="L7" t="b">
-        <v>0</v>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7" t="s">
+        <v>819</v>
       </c>
       <c r="M7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8">
         <v>2002</v>
       </c>
       <c r="C8" t="s">
-        <v>819</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>811</v>
+        <v>823</v>
+      </c>
+      <c r="D8" t="s">
+        <v>824</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="G8">
+        <v>825</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="H8">
         <v>1000</v>
       </c>
-      <c r="H8" t="s">
-        <v>814</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
+      <c r="I8" t="s">
+        <v>818</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
-      <c r="K8" t="s">
-        <v>815</v>
-      </c>
-      <c r="L8" t="b">
-        <v>0</v>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>819</v>
       </c>
       <c r="M8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9">
         <v>2003</v>
       </c>
       <c r="C9" t="s">
-        <v>821</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>811</v>
+        <v>826</v>
+      </c>
+      <c r="D9" t="s">
+        <v>824</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="G9">
+        <v>825</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="H9">
         <v>1000</v>
       </c>
-      <c r="H9" t="s">
-        <v>814</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
+      <c r="I9" t="s">
+        <v>818</v>
       </c>
       <c r="J9">
         <v>3</v>
       </c>
-      <c r="K9" t="s">
-        <v>815</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>819</v>
       </c>
       <c r="M9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="B10">
         <v>3001</v>
       </c>
       <c r="C10" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="D10" t="s">
-        <v>823</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>812</v>
+        <v>828</v>
+      </c>
+      <c r="E10" t="s">
+        <v>829</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>824</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>825</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
+        <v>816</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>831</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>3</v>
       </c>
-      <c r="K10" t="s">
-        <v>815</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
+      <c r="L10" t="s">
+        <v>819</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="B11">
         <v>4001</v>
       </c>
       <c r="C11" t="s">
-        <v>826</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>825</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
+        <v>816</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>831</v>
       </c>
       <c r="J11">
         <v>3</v>
       </c>
-      <c r="K11" t="s">
-        <v>827</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="6:6">
-      <c r="F17" s="16"/>
-    </row>
-    <row r="18" spans="6:6">
-      <c r="F18" s="16"/>
-    </row>
-    <row r="19" spans="6:6">
-      <c r="F19" s="16"/>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11" t="s">
+        <v>833</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7">
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" spans="7:7">
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24364,55 +24392,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D1" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="E1" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="F1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="G1" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="H1" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="I1" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="J1" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="N1" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="O1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P1" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="Q1" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="R1" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="S1" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="T1" t="s">
         <v>11</v>
       </c>
       <c r="U1" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="V1" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -24429,7 +24457,7 @@
         <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>843</v>
+        <v>785</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -24482,59 +24510,59 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="T3" s="2"/>
       <c r="U3" s="2" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -24542,61 +24570,61 @@
         <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C4" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="D4" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="F4" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="G4" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="H4" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="I4" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="J4" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="K4" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="L4" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="M4" s="21">
         <v>10</v>
       </c>
       <c r="N4" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="O4" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="P4" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="Q4" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="R4" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="S4" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="U4" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="V4" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -24610,7 +24638,7 @@
         <v>1000</v>
       </c>
       <c r="E5" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F5">
         <v>1001</v>
@@ -24676,7 +24704,7 @@
         <v>2000</v>
       </c>
       <c r="E6" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F6">
         <v>1002</v>
@@ -24742,7 +24770,7 @@
         <v>3000</v>
       </c>
       <c r="E7" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F7">
         <v>2001</v>
@@ -24805,7 +24833,7 @@
         <v>4000</v>
       </c>
       <c r="E8" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F8">
         <v>1001</v>
@@ -24871,7 +24899,7 @@
         <v>5000</v>
       </c>
       <c r="E9" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F9">
         <v>1002</v>
@@ -24937,7 +24965,7 @@
         <v>6000</v>
       </c>
       <c r="E10" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F10">
         <v>2001</v>
@@ -25000,7 +25028,7 @@
         <v>7000</v>
       </c>
       <c r="E11" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F11">
         <v>1001</v>
@@ -25066,7 +25094,7 @@
         <v>8000</v>
       </c>
       <c r="E12" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F12">
         <v>1002</v>
@@ -25132,7 +25160,7 @@
         <v>9000</v>
       </c>
       <c r="E13" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F13">
         <v>2001</v>
@@ -25195,7 +25223,7 @@
         <v>10000</v>
       </c>
       <c r="E14" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F14">
         <v>1001</v>
@@ -25261,7 +25289,7 @@
         <v>11000</v>
       </c>
       <c r="E15" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F15">
         <v>1002</v>
@@ -25327,7 +25355,7 @@
         <v>12000</v>
       </c>
       <c r="E16" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F16">
         <v>2001</v>
@@ -25431,7 +25459,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>875</v>
+        <v>814</v>
       </c>
       <c r="F18">
         <v>1001</v>
@@ -25492,7 +25520,7 @@
         <v>1000</v>
       </c>
       <c r="E20" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F20">
         <v>2002</v>
@@ -25558,7 +25586,7 @@
         <v>2000</v>
       </c>
       <c r="E21" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F21">
         <v>2002</v>
@@ -25624,7 +25652,7 @@
         <v>3000</v>
       </c>
       <c r="E22" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F22">
         <v>2003</v>
@@ -25690,7 +25718,7 @@
         <v>4000</v>
       </c>
       <c r="E23" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F23">
         <v>2002</v>
@@ -25756,7 +25784,7 @@
         <v>5000</v>
       </c>
       <c r="E24" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F24">
         <v>2002</v>
@@ -25822,7 +25850,7 @@
         <v>6000</v>
       </c>
       <c r="E25" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F25">
         <v>2002</v>
@@ -25888,7 +25916,7 @@
         <v>7000</v>
       </c>
       <c r="E26" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F26">
         <v>2002</v>
@@ -25954,7 +25982,7 @@
         <v>8000</v>
       </c>
       <c r="E27" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F27">
         <v>2003</v>
@@ -26020,7 +26048,7 @@
         <v>9000</v>
       </c>
       <c r="E28" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F28">
         <v>2002</v>
@@ -26086,7 +26114,7 @@
         <v>10000</v>
       </c>
       <c r="E29" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F29">
         <v>2002</v>
@@ -26152,7 +26180,7 @@
         <v>11000</v>
       </c>
       <c r="E30" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F30">
         <v>2002</v>
@@ -26218,7 +26246,7 @@
         <v>12000</v>
       </c>
       <c r="E31" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F31">
         <v>2002</v>
@@ -26284,7 +26312,7 @@
         <v>13000</v>
       </c>
       <c r="E32" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F32">
         <v>2002</v>
@@ -26350,7 +26378,7 @@
         <v>14000</v>
       </c>
       <c r="E33" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F33">
         <v>2003</v>
@@ -26416,7 +26444,7 @@
         <v>15000</v>
       </c>
       <c r="E34" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="F34">
         <v>2002</v>
@@ -26499,16 +26527,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="D1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="G1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -26536,20 +26564,20 @@
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -26560,19 +26588,19 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D4" t="s">
         <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="G4" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="H4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -26752,7 +26780,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -27324,7 +27352,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -27353,7 +27381,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -27497,16 +27525,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="D1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G1" t="s">
         <v>11</v>
@@ -27540,19 +27568,19 @@
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>11</v>
@@ -27566,22 +27594,22 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D4" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E4" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="G4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="H4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -27604,7 +27632,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -27627,7 +27655,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -27650,7 +27678,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -27673,7 +27701,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -27696,7 +27724,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -27719,7 +27747,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -27742,7 +27770,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -27765,7 +27793,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -27788,7 +27816,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -27811,7 +27839,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -27834,7 +27862,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -27854,7 +27882,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -27874,7 +27902,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -27894,7 +27922,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -27914,7 +27942,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="20" spans="2:7">
@@ -27934,7 +27962,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -27954,7 +27982,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -27974,7 +28002,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -27994,7 +28022,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -28014,7 +28042,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -28034,7 +28062,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -28054,7 +28082,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -28074,7 +28102,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -28094,7 +28122,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -28114,7 +28142,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -28134,7 +28162,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -28154,7 +28182,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="32" spans="2:7">
@@ -28174,7 +28202,7 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -28194,7 +28222,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -28214,7 +28242,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -28234,7 +28262,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -28254,7 +28282,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -28274,7 +28302,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -28294,7 +28322,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -28314,7 +28342,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -28334,7 +28362,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -28357,7 +28385,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -28380,7 +28408,7 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -28403,7 +28431,7 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -28426,7 +28454,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -28449,7 +28477,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -28472,7 +28500,7 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -28495,7 +28523,7 @@
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -28518,7 +28546,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -28541,7 +28569,7 @@
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -28564,7 +28592,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -28587,7 +28615,7 @@
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -28610,7 +28638,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -28633,7 +28661,7 @@
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -28656,7 +28684,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -28679,7 +28707,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -28702,7 +28730,7 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -28725,7 +28753,7 @@
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -28748,7 +28776,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -28771,7 +28799,7 @@
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -28794,7 +28822,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -28817,7 +28845,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -28840,7 +28868,7 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -28863,7 +28891,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -28886,7 +28914,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -28909,7 +28937,7 @@
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -28932,7 +28960,7 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -28955,7 +28983,7 @@
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -28978,7 +29006,7 @@
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -29001,7 +29029,7 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -29025,7 +29053,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -29049,7 +29077,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -29073,7 +29101,7 @@
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -29097,7 +29125,7 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -29121,7 +29149,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -29145,7 +29173,7 @@
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -29169,7 +29197,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -29193,7 +29221,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -29217,7 +29245,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -29241,7 +29269,7 @@
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -29265,7 +29293,7 @@
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -29289,7 +29317,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -29313,7 +29341,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -29337,7 +29365,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -29361,7 +29389,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -29385,7 +29413,7 @@
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -29409,7 +29437,7 @@
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -29433,7 +29461,7 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -29457,7 +29485,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -29481,7 +29509,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -29505,7 +29533,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -29529,7 +29557,7 @@
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -29553,7 +29581,7 @@
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -29577,7 +29605,7 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -29601,7 +29629,7 @@
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -29625,7 +29653,7 @@
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -29649,7 +29677,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -29673,7 +29701,7 @@
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -29697,7 +29725,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -29721,7 +29749,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -29745,7 +29773,7 @@
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -29769,7 +29797,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -29793,7 +29821,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -29817,7 +29845,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -29841,7 +29869,7 @@
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -29865,7 +29893,7 @@
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -29889,7 +29917,7 @@
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -29913,7 +29941,7 @@
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -29937,7 +29965,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -29961,7 +29989,7 @@
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -29985,7 +30013,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -30009,7 +30037,7 @@
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -30033,7 +30061,7 @@
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -30057,7 +30085,7 @@
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -30081,7 +30109,7 @@
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -30105,7 +30133,7 @@
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -30129,7 +30157,7 @@
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -30153,7 +30181,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -30177,7 +30205,7 @@
         <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -30201,7 +30229,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -30224,7 +30252,7 @@
         <v>1</v>
       </c>
       <c r="G120" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -30247,7 +30275,7 @@
         <v>1</v>
       </c>
       <c r="G121" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -30270,7 +30298,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -30294,7 +30322,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -30318,7 +30346,7 @@
         <v>1</v>
       </c>
       <c r="G124" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -30342,7 +30370,7 @@
         <v>1</v>
       </c>
       <c r="G125" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -30366,7 +30394,7 @@
         <v>1</v>
       </c>
       <c r="G126" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -30390,7 +30418,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -30414,7 +30442,7 @@
         <v>1</v>
       </c>
       <c r="G128" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -30438,7 +30466,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -30462,7 +30490,7 @@
         <v>1</v>
       </c>
       <c r="G130" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -30486,7 +30514,7 @@
         <v>1</v>
       </c>
       <c r="G131" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -30510,7 +30538,7 @@
         <v>1</v>
       </c>
       <c r="G132" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -30534,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="G133" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -30555,7 +30583,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -30576,7 +30604,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -30597,7 +30625,7 @@
         <v>1</v>
       </c>
       <c r="G136" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -30618,7 +30646,7 @@
         <v>1</v>
       </c>
       <c r="G137" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -30639,7 +30667,7 @@
         <v>1</v>
       </c>
       <c r="G138" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -30660,7 +30688,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -30681,7 +30709,7 @@
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -30702,7 +30730,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -30723,7 +30751,7 @@
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -30744,7 +30772,7 @@
         <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -30765,7 +30793,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -30786,7 +30814,7 @@
         <v>1</v>
       </c>
       <c r="G145" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -30807,7 +30835,7 @@
         <v>1</v>
       </c>
       <c r="G146" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -30828,7 +30856,7 @@
         <v>1</v>
       </c>
       <c r="G147" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -30849,7 +30877,7 @@
         <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -30870,7 +30898,7 @@
         <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -30891,7 +30919,7 @@
         <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -30912,7 +30940,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -30933,7 +30961,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -30954,7 +30982,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -30975,7 +31003,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -30996,7 +31024,7 @@
         <v>1</v>
       </c>
       <c r="G155" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -31017,7 +31045,7 @@
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -31038,7 +31066,7 @@
         <v>1</v>
       </c>
       <c r="G157" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -31059,7 +31087,7 @@
         <v>1</v>
       </c>
       <c r="G158" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -31083,7 +31111,7 @@
         <v>1</v>
       </c>
       <c r="G159" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -31107,7 +31135,7 @@
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -31131,7 +31159,7 @@
         <v>1</v>
       </c>
       <c r="G161" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -31155,7 +31183,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -31179,7 +31207,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -31203,7 +31231,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -31227,7 +31255,7 @@
         <v>1</v>
       </c>
       <c r="G165" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -31251,7 +31279,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -31275,7 +31303,7 @@
         <v>1</v>
       </c>
       <c r="G167" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -31299,7 +31327,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -31323,7 +31351,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -31347,7 +31375,7 @@
         <v>1</v>
       </c>
       <c r="G170" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -31371,7 +31399,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -31395,7 +31423,7 @@
         <v>1</v>
       </c>
       <c r="G172" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -31419,7 +31447,7 @@
         <v>1</v>
       </c>
       <c r="G173" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -31443,7 +31471,7 @@
         <v>1</v>
       </c>
       <c r="G174" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -31467,7 +31495,7 @@
         <v>1</v>
       </c>
       <c r="G175" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -31491,7 +31519,7 @@
         <v>1</v>
       </c>
       <c r="G176" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -31515,7 +31543,7 @@
         <v>1</v>
       </c>
       <c r="G177" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -31539,7 +31567,7 @@
         <v>1</v>
       </c>
       <c r="G178" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -31563,7 +31591,7 @@
         <v>1</v>
       </c>
       <c r="G179" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -31587,7 +31615,7 @@
         <v>1</v>
       </c>
       <c r="G180" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -31611,7 +31639,7 @@
         <v>1</v>
       </c>
       <c r="G181" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -31635,7 +31663,7 @@
         <v>1</v>
       </c>
       <c r="G182" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -31659,7 +31687,7 @@
         <v>1</v>
       </c>
       <c r="G183" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -31683,7 +31711,7 @@
         <v>1</v>
       </c>
       <c r="G184" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -31707,7 +31735,7 @@
         <v>1</v>
       </c>
       <c r="G185" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -31731,7 +31759,7 @@
         <v>1</v>
       </c>
       <c r="G186" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -31755,7 +31783,7 @@
         <v>1</v>
       </c>
       <c r="G187" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -31779,7 +31807,7 @@
         <v>1</v>
       </c>
       <c r="G188" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -31803,7 +31831,7 @@
         <v>1</v>
       </c>
       <c r="G189" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -31827,7 +31855,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -31851,7 +31879,7 @@
         <v>1</v>
       </c>
       <c r="G191" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -31875,7 +31903,7 @@
         <v>1</v>
       </c>
       <c r="G192" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -31899,7 +31927,7 @@
         <v>1</v>
       </c>
       <c r="G193" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -31923,7 +31951,7 @@
         <v>1</v>
       </c>
       <c r="G194" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -31947,7 +31975,7 @@
         <v>1</v>
       </c>
       <c r="G195" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -31971,7 +31999,7 @@
         <v>1</v>
       </c>
       <c r="G196" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -31995,7 +32023,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -32019,7 +32047,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -32043,7 +32071,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -32067,7 +32095,7 @@
         <v>1</v>
       </c>
       <c r="G200" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -32091,7 +32119,7 @@
         <v>1</v>
       </c>
       <c r="G201" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -32115,7 +32143,7 @@
         <v>1</v>
       </c>
       <c r="G202" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -32139,7 +32167,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -32163,7 +32191,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -32187,7 +32215,7 @@
         <v>1</v>
       </c>
       <c r="G205" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -32211,7 +32239,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -32235,7 +32263,7 @@
         <v>1</v>
       </c>
       <c r="G207" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -32259,7 +32287,7 @@
         <v>1</v>
       </c>
       <c r="G208" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -32283,7 +32311,7 @@
         <v>1</v>
       </c>
       <c r="G209" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -32307,7 +32335,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -32331,7 +32359,7 @@
         <v>1</v>
       </c>
       <c r="G211" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -32355,7 +32383,7 @@
         <v>1</v>
       </c>
       <c r="G212" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -32379,7 +32407,7 @@
         <v>1</v>
       </c>
       <c r="G213" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -32403,7 +32431,7 @@
         <v>1</v>
       </c>
       <c r="G214" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -32427,7 +32455,7 @@
         <v>1</v>
       </c>
       <c r="G215" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -32451,7 +32479,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -32475,7 +32503,7 @@
         <v>1</v>
       </c>
       <c r="G217" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -32499,7 +32527,7 @@
         <v>1</v>
       </c>
       <c r="G218" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -32523,7 +32551,7 @@
         <v>1</v>
       </c>
       <c r="G219" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -32547,7 +32575,7 @@
         <v>1</v>
       </c>
       <c r="G220" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -32571,7 +32599,7 @@
         <v>1</v>
       </c>
       <c r="G221" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -32595,7 +32623,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -32619,7 +32647,7 @@
         <v>1</v>
       </c>
       <c r="G223" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -32643,7 +32671,7 @@
         <v>1</v>
       </c>
       <c r="G224" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -32667,7 +32695,7 @@
         <v>1</v>
       </c>
       <c r="G225" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -32691,7 +32719,7 @@
         <v>1</v>
       </c>
       <c r="G226" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -32715,7 +32743,7 @@
         <v>1</v>
       </c>
       <c r="G227" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -32739,7 +32767,7 @@
         <v>1</v>
       </c>
       <c r="G228" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -32763,7 +32791,7 @@
         <v>1</v>
       </c>
       <c r="G229" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -32787,7 +32815,7 @@
         <v>1</v>
       </c>
       <c r="G230" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -32811,7 +32839,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -32835,7 +32863,7 @@
         <v>1</v>
       </c>
       <c r="G232" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -32859,7 +32887,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -32883,7 +32911,7 @@
         <v>1</v>
       </c>
       <c r="G234" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -32907,7 +32935,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -32931,7 +32959,7 @@
         <v>1</v>
       </c>
       <c r="G236" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -32955,7 +32983,7 @@
         <v>1</v>
       </c>
       <c r="G237" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -32979,7 +33007,7 @@
         <v>1</v>
       </c>
       <c r="G238" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -33003,7 +33031,7 @@
         <v>1</v>
       </c>
       <c r="G239" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -33027,7 +33055,7 @@
         <v>1</v>
       </c>
       <c r="G240" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -33051,7 +33079,7 @@
         <v>1</v>
       </c>
       <c r="G241" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -33075,7 +33103,7 @@
         <v>1</v>
       </c>
       <c r="G242" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -33099,7 +33127,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -33123,7 +33151,7 @@
         <v>1</v>
       </c>
       <c r="G244" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -33147,7 +33175,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -33171,7 +33199,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -33195,7 +33223,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -33219,7 +33247,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -33243,7 +33271,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -33267,7 +33295,7 @@
         <v>1</v>
       </c>
       <c r="G250" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -33291,7 +33319,7 @@
         <v>1</v>
       </c>
       <c r="G251" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -33315,7 +33343,7 @@
         <v>0</v>
       </c>
       <c r="G252" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -33339,7 +33367,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -33363,7 +33391,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -33387,7 +33415,7 @@
         <v>0</v>
       </c>
       <c r="G255" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -33408,7 +33436,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="257" spans="2:7">
@@ -33429,7 +33457,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="258" spans="2:7">
@@ -33450,7 +33478,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="259" spans="2:7">
@@ -33471,7 +33499,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="260" spans="2:7">
@@ -33492,7 +33520,7 @@
         <v>1</v>
       </c>
       <c r="G260" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="261" spans="2:7">
@@ -33513,7 +33541,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="262" spans="2:7">
@@ -33534,7 +33562,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="263" spans="2:7">
@@ -33555,7 +33583,7 @@
         <v>1</v>
       </c>
       <c r="G263" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="264" spans="2:7">
@@ -33576,7 +33604,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="265" spans="2:7">
@@ -33597,7 +33625,7 @@
         <v>1</v>
       </c>
       <c r="G265" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="266" spans="2:7">
@@ -33618,7 +33646,7 @@
         <v>1</v>
       </c>
       <c r="G266" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="267" spans="2:7">
@@ -33639,7 +33667,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="268" spans="2:7">
@@ -33660,7 +33688,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="269" spans="2:7">
@@ -33680,7 +33708,7 @@
         <v>1</v>
       </c>
       <c r="G269" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="270" spans="2:7">
@@ -33700,7 +33728,7 @@
         <v>1</v>
       </c>
       <c r="G270" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -33764,28 +33792,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E1" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="F1" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="G1" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="H1" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="I1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J1" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -33828,28 +33856,28 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -33860,31 +33888,31 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D4" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E4" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F4" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="G4" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="H4" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="I4" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="J4" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="K4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -34300,7 +34328,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -34335,7 +34363,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -34434,7 +34462,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -34469,7 +34497,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -34632,7 +34660,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -34667,7 +34695,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -34702,7 +34730,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -34909,25 +34937,25 @@
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="F1" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="G1" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="H1" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="I1" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="K1" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="L1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -34971,23 +34999,23 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -35004,28 +35032,28 @@
         <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="F4" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="G4" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="H4" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="I4" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="J4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="K4" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="L4" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -35039,16 +35067,16 @@
         <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="F5" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="H5" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="K5" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -35062,16 +35090,16 @@
         <v>106</v>
       </c>
       <c r="E6" t="s">
+        <v>942</v>
+      </c>
+      <c r="F6" t="s">
         <v>939</v>
       </c>
-      <c r="F6" t="s">
-        <v>936</v>
-      </c>
       <c r="H6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="K6" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -35085,16 +35113,16 @@
         <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="F7" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="H7" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="K7" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -35108,16 +35136,16 @@
         <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="F8" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="H8" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="K8" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -35131,16 +35159,16 @@
         <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="F9" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="H9" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="K9" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -35154,16 +35182,16 @@
         <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="F10" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="H10" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="K10" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -35177,16 +35205,16 @@
         <v>640</v>
       </c>
       <c r="E11" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="F11" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="H11" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="J11" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -35200,16 +35228,16 @@
         <v>706</v>
       </c>
       <c r="E12" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="F12" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="H12" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="J12" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
   </sheetData>
@@ -35241,25 +35269,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D1" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="F1" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="G1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="H1" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="I1" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -35267,16 +35295,16 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="F2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G2" t="s">
         <v>29</v>
@@ -35293,25 +35321,25 @@
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -35319,31 +35347,31 @@
         <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C4" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D4" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E4" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="F4" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="G4" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="H4" t="s">
+        <v>977</v>
+      </c>
+      <c r="I4" t="s">
+        <v>978</v>
+      </c>
+      <c r="J4" t="s">
         <v>974</v>
-      </c>
-      <c r="I4" t="s">
-        <v>975</v>
-      </c>
-      <c r="J4" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -35354,7 +35382,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E6" t="str">
         <f>LOOKUP(B6,Item!B:B,Item!H:H)</f>
@@ -35364,10 +35392,10 @@
         <v>0.9</v>
       </c>
       <c r="G6" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H6" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -35385,7 +35413,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E7" t="str">
         <f>LOOKUP(B7,Item!B:B,Item!H:H)</f>
@@ -35395,10 +35423,10 @@
         <v>0.8</v>
       </c>
       <c r="G7" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H7" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -35416,7 +35444,7 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E8" t="str">
         <f>LOOKUP(B8,Item!B:B,Item!H:H)</f>
@@ -35426,10 +35454,10 @@
         <v>0.8</v>
       </c>
       <c r="G8" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H8" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -35447,7 +35475,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E9" t="str">
         <f>LOOKUP(B9,Item!B:B,Item!H:H)</f>
@@ -35457,10 +35485,10 @@
         <v>0.9</v>
       </c>
       <c r="G9" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H9" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -35478,7 +35506,7 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E10" t="str">
         <f>LOOKUP(B10,Item!B:B,Item!H:H)</f>
@@ -35488,10 +35516,10 @@
         <v>0.8</v>
       </c>
       <c r="G10" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H10" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -35509,7 +35537,7 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E11" t="str">
         <f>LOOKUP(B11,Item!B:B,Item!H:H)</f>
@@ -35519,10 +35547,10 @@
         <v>0.8</v>
       </c>
       <c r="G11" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H11" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -35540,7 +35568,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E12" t="str">
         <f>LOOKUP(B12,Item!B:B,Item!H:H)</f>
@@ -35550,10 +35578,10 @@
         <v>0.8</v>
       </c>
       <c r="G12" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H12" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -35571,7 +35599,7 @@
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E13" t="str">
         <f>LOOKUP(B13,Item!B:B,Item!H:H)</f>
@@ -35581,10 +35609,10 @@
         <v>0.9</v>
       </c>
       <c r="G13" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H13" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -35602,7 +35630,7 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E14" t="str">
         <f>LOOKUP(B14,Item!B:B,Item!H:H)</f>
@@ -35612,10 +35640,10 @@
         <v>0.7</v>
       </c>
       <c r="G14" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H14" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -35633,7 +35661,7 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E15" t="str">
         <f>LOOKUP(B15,Item!B:B,Item!H:H)</f>
@@ -35643,10 +35671,10 @@
         <v>0.9</v>
       </c>
       <c r="G15" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H15" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -35664,7 +35692,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E16" t="str">
         <f>LOOKUP(B16,Item!B:B,Item!H:H)</f>
@@ -35674,10 +35702,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H16" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I16">
         <v>100</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -21981,7 +21981,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{0a4b7713-0fd5-47b5-ba07-6aa0ec5707d4}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{ea5ceea5-1fad-481d-9db0-ba4d280ca3d3}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21995,7 +21995,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{60023efd-9649-403f-86a3-50632cf3e2c9}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{a5da9781-e364-4a5b-9bf6-edc4897214e4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22009,7 +22009,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{c202a918-d989-4da6-8a32-8dcbe53f516b}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{24a7aa05-abb6-4969-ae27-7d0a5b51c993}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22023,7 +22023,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{75179a25-0841-4c07-bacc-2375d39e186d}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{ffefa439-fe28-4011-8664-84ecbe6b5a7e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22037,7 +22037,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{79e0b37b-515a-4324-a260-43d2c87e6702}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{95b2c5b2-e14e-44e0-a017-d13a3b2ecb99}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22051,7 +22051,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{840efd7c-dd5c-47a3-a9ca-7a33e7ab2af1}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{4008a59f-1614-4024-a8ef-6def3f6d141f}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22065,7 +22065,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{7f4dfed4-b326-40cd-b0c6-39fc32071eed}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{b51c394d-e3b6-40a5-8826-d54b5c529b00}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22079,7 +22079,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{aa830b10-4c24-45f9-b0ab-6af4c301fb19}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{fa7ecb1f-8586-4a2e-8e8a-bfca88b966bb}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22093,7 +22093,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{bcf10269-9dc1-4fbe-a24e-fee794e76ded}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{3530b403-7560-4293-a5cf-7ccb38fd8623}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="12"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -5638,7 +5638,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.8"/>
+          <bgColor theme="7" tint="0.6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5652,7 +5652,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.6"/>
+          <bgColor theme="7" tint="0.8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -21981,7 +21981,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{ea5ceea5-1fad-481d-9db0-ba4d280ca3d3}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{9fa13c3a-0284-4f80-a9aa-9d544df456f5}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21995,7 +21995,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{a5da9781-e364-4a5b-9bf6-edc4897214e4}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{c2fb41ad-fc55-4df6-99fa-c266caec2c32}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22009,7 +22009,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{24a7aa05-abb6-4969-ae27-7d0a5b51c993}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{637ca012-0bbc-455b-b802-eb04ed86c12c}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22023,7 +22023,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{ffefa439-fe28-4011-8664-84ecbe6b5a7e}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{232182b4-e6cc-49b6-80da-a2480ec510f1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22037,7 +22037,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{95b2c5b2-e14e-44e0-a017-d13a3b2ecb99}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{7ed5cfcd-6845-4387-ae55-74667a7bb0b7}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22051,7 +22051,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{4008a59f-1614-4024-a8ef-6def3f6d141f}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{4c685db5-05d1-4038-90d0-9b9d290c8fb8}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22065,7 +22065,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{b51c394d-e3b6-40a5-8826-d54b5c529b00}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{d9e3acf4-eb69-40e9-b1e4-fbdbe462b35d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22079,7 +22079,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{fa7ecb1f-8586-4a2e-8e8a-bfca88b966bb}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{b249392e-f04b-4a9e-bd35-af64fc67566e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22093,7 +22093,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{3530b403-7560-4293-a5cf-7ccb38fd8623}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{6815efb3-ae69-4f25-a0f2-887c643e5122}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -25589,7 +25589,7 @@
         <v>824</v>
       </c>
       <c r="F21">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -32559,7 +32559,7 @@
         <v>11</v>
       </c>
       <c r="B220" s="19">
-        <f t="shared" ref="B220:B240" si="4">C220*100000+D220</f>
+        <f t="shared" ref="B220:B255" si="4">C220*100000+D220</f>
         <v>100207012</v>
       </c>
       <c r="C220">
@@ -33063,7 +33063,7 @@
         <v>11</v>
       </c>
       <c r="B241" s="19">
-        <f>C241*100000+D241</f>
+        <f t="shared" si="4"/>
         <v>200109001</v>
       </c>
       <c r="C241">
@@ -33087,7 +33087,7 @@
         <v>11</v>
       </c>
       <c r="B242" s="19">
-        <f>C242*100000+D242</f>
+        <f t="shared" si="4"/>
         <v>200109002</v>
       </c>
       <c r="C242">
@@ -33111,7 +33111,7 @@
         <v>11</v>
       </c>
       <c r="B243" s="19">
-        <f>C243*100000+D243</f>
+        <f t="shared" si="4"/>
         <v>200109003</v>
       </c>
       <c r="C243">
@@ -33135,7 +33135,7 @@
         <v>11</v>
       </c>
       <c r="B244" s="19">
-        <f>C244*100000+D244</f>
+        <f t="shared" si="4"/>
         <v>200109004</v>
       </c>
       <c r="C244">
@@ -33159,7 +33159,7 @@
         <v>11</v>
       </c>
       <c r="B245" s="19">
-        <f>C245*100000+D245</f>
+        <f t="shared" si="4"/>
         <v>200109005</v>
       </c>
       <c r="C245">
@@ -33183,7 +33183,7 @@
         <v>11</v>
       </c>
       <c r="B246" s="19">
-        <f>C246*100000+D246</f>
+        <f t="shared" si="4"/>
         <v>200109006</v>
       </c>
       <c r="C246">
@@ -33207,7 +33207,7 @@
         <v>11</v>
       </c>
       <c r="B247" s="19">
-        <f>C247*100000+D247</f>
+        <f t="shared" si="4"/>
         <v>200109007</v>
       </c>
       <c r="C247">
@@ -33231,7 +33231,7 @@
         <v>11</v>
       </c>
       <c r="B248" s="19">
-        <f>C248*100000+D248</f>
+        <f t="shared" si="4"/>
         <v>200109008</v>
       </c>
       <c r="C248">
@@ -33255,7 +33255,7 @@
         <v>11</v>
       </c>
       <c r="B249" s="19">
-        <f>C249*100000+D249</f>
+        <f t="shared" si="4"/>
         <v>200109009</v>
       </c>
       <c r="C249">
@@ -33279,7 +33279,7 @@
         <v>11</v>
       </c>
       <c r="B250" s="19">
-        <f>C250*100000+D250</f>
+        <f t="shared" si="4"/>
         <v>200109010</v>
       </c>
       <c r="C250">
@@ -33303,7 +33303,7 @@
         <v>11</v>
       </c>
       <c r="B251" s="19">
-        <f>C251*100000+D251</f>
+        <f t="shared" si="4"/>
         <v>200109011</v>
       </c>
       <c r="C251">
@@ -33327,7 +33327,7 @@
         <v>11</v>
       </c>
       <c r="B252" s="19">
-        <f>C252*100000+D252</f>
+        <f t="shared" si="4"/>
         <v>300151001</v>
       </c>
       <c r="C252">
@@ -33351,7 +33351,7 @@
         <v>11</v>
       </c>
       <c r="B253" s="19">
-        <f>C253*100000+D253</f>
+        <f t="shared" si="4"/>
         <v>300152001</v>
       </c>
       <c r="C253">
@@ -33375,7 +33375,7 @@
         <v>11</v>
       </c>
       <c r="B254" s="19">
-        <f>C254*100000+D254</f>
+        <f t="shared" si="4"/>
         <v>300191012</v>
       </c>
       <c r="C254">
@@ -33399,7 +33399,7 @@
         <v>11</v>
       </c>
       <c r="B255" s="19">
-        <f>C255*100000+D255</f>
+        <f t="shared" si="4"/>
         <v>300192005</v>
       </c>
       <c r="C255">
@@ -33420,7 +33420,7 @@
     </row>
     <row r="256" spans="1:7">
       <c r="B256" s="19">
-        <f t="shared" ref="B256:B270" si="5">C256*100000+D256</f>
+        <f>C256*100000+D256</f>
         <v>200202003</v>
       </c>
       <c r="C256">
@@ -33441,7 +33441,7 @@
     </row>
     <row r="257" spans="2:7">
       <c r="B257" s="19">
-        <f t="shared" si="5"/>
+        <f>C257*100000+D257</f>
         <v>200202009</v>
       </c>
       <c r="C257">
@@ -33462,14 +33462,14 @@
     </row>
     <row r="258" spans="2:7">
       <c r="B258" s="19">
-        <f t="shared" si="5"/>
-        <v>200202013</v>
+        <f t="shared" ref="B258:B269" si="5">C258*100000+D258</f>
+        <v>200202022</v>
       </c>
       <c r="C258">
         <v>2002</v>
       </c>
       <c r="D258">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="E258">
         <v>100</v>
@@ -33484,13 +33484,13 @@
     <row r="259" spans="2:7">
       <c r="B259" s="19">
         <f t="shared" si="5"/>
-        <v>200202022</v>
+        <v>200202029</v>
       </c>
       <c r="C259">
         <v>2002</v>
       </c>
       <c r="D259">
-        <v>2022</v>
+        <v>2029</v>
       </c>
       <c r="E259">
         <v>100</v>
@@ -33505,13 +33505,13 @@
     <row r="260" spans="2:7">
       <c r="B260" s="19">
         <f t="shared" si="5"/>
-        <v>200202029</v>
+        <v>200202032</v>
       </c>
       <c r="C260">
         <v>2002</v>
       </c>
       <c r="D260">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="E260">
         <v>100</v>
@@ -33526,13 +33526,13 @@
     <row r="261" spans="2:7">
       <c r="B261" s="19">
         <f t="shared" si="5"/>
-        <v>200202032</v>
+        <v>200205004</v>
       </c>
       <c r="C261">
         <v>2002</v>
       </c>
       <c r="D261">
-        <v>2032</v>
+        <v>5004</v>
       </c>
       <c r="E261">
         <v>100</v>
@@ -33547,13 +33547,13 @@
     <row r="262" spans="2:7">
       <c r="B262" s="19">
         <f t="shared" si="5"/>
-        <v>200205004</v>
+        <v>200206006</v>
       </c>
       <c r="C262">
         <v>2002</v>
       </c>
       <c r="D262">
-        <v>5004</v>
+        <v>6006</v>
       </c>
       <c r="E262">
         <v>100</v>
@@ -33568,13 +33568,13 @@
     <row r="263" spans="2:7">
       <c r="B263" s="19">
         <f t="shared" si="5"/>
-        <v>200206006</v>
+        <v>200208005</v>
       </c>
       <c r="C263">
         <v>2002</v>
       </c>
       <c r="D263">
-        <v>6006</v>
+        <v>8005</v>
       </c>
       <c r="E263">
         <v>100</v>
@@ -33589,13 +33589,13 @@
     <row r="264" spans="2:7">
       <c r="B264" s="19">
         <f t="shared" si="5"/>
-        <v>200208005</v>
+        <v>200206008</v>
       </c>
       <c r="C264">
         <v>2002</v>
       </c>
       <c r="D264">
-        <v>8005</v>
+        <v>6008</v>
       </c>
       <c r="E264">
         <v>100</v>
@@ -33610,13 +33610,13 @@
     <row r="265" spans="2:7">
       <c r="B265" s="19">
         <f t="shared" si="5"/>
-        <v>200206008</v>
+        <v>200207008</v>
       </c>
       <c r="C265">
         <v>2002</v>
       </c>
       <c r="D265">
-        <v>6008</v>
+        <v>7008</v>
       </c>
       <c r="E265">
         <v>100</v>
@@ -33631,13 +33631,13 @@
     <row r="266" spans="2:7">
       <c r="B266" s="19">
         <f t="shared" si="5"/>
-        <v>200207008</v>
+        <v>200208012</v>
       </c>
       <c r="C266">
         <v>2002</v>
       </c>
       <c r="D266">
-        <v>7008</v>
+        <v>8012</v>
       </c>
       <c r="E266">
         <v>100</v>
@@ -33652,13 +33652,13 @@
     <row r="267" spans="2:7">
       <c r="B267" s="19">
         <f t="shared" si="5"/>
-        <v>200208012</v>
+        <v>200301008</v>
       </c>
       <c r="C267">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D267">
-        <v>8012</v>
+        <v>1008</v>
       </c>
       <c r="E267">
         <v>100</v>
@@ -33667,19 +33667,18 @@
         <v>1</v>
       </c>
       <c r="G267" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="268" spans="2:7">
       <c r="B268" s="19">
-        <f t="shared" si="5"/>
-        <v>200301008</v>
+        <v>200301011</v>
       </c>
       <c r="C268">
         <v>2003</v>
       </c>
       <c r="D268">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E268">
         <v>100</v>
@@ -33693,13 +33692,13 @@
     </row>
     <row r="269" spans="2:7">
       <c r="B269" s="19">
-        <v>200301011</v>
+        <v>200301013</v>
       </c>
       <c r="C269">
         <v>2003</v>
       </c>
       <c r="D269">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="E269">
         <v>100</v>
@@ -33713,31 +33712,37 @@
     </row>
     <row r="270" spans="2:7">
       <c r="B270" s="19">
-        <v>200301013</v>
+        <f>C270*100000+D270</f>
+        <v>200302013</v>
       </c>
       <c r="C270">
         <v>2003</v>
       </c>
       <c r="D270">
-        <v>1013</v>
+        <v>2013</v>
       </c>
       <c r="E270">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F270" s="17" t="b">
         <v>1</v>
       </c>
       <c r="G270" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G$1:G$1048576">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
-      <formula>"标准盲盒"</formula>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
-      <formula>"新手盲盒"</formula>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"Demo盲盒普"</formula>
     </cfRule>
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -33749,16 +33754,11 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
-      <formula>"Demo盲盒普"</formula>
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+      <formula>"新手盲盒"</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"标准盲盒"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -21981,7 +21981,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{9fa13c3a-0284-4f80-a9aa-9d544df456f5}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{d4cd1199-a1c4-47ef-9823-72e6c86caa53}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -21995,7 +21995,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{c2fb41ad-fc55-4df6-99fa-c266caec2c32}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{b4140f4d-fa5c-4a93-b56e-a6ada8ca33a3}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22009,7 +22009,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{637ca012-0bbc-455b-b802-eb04ed86c12c}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{80a68643-71bc-46df-b12e-fd332b8bb052}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22023,7 +22023,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{232182b4-e6cc-49b6-80da-a2480ec510f1}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{01e9d38c-7ee7-4372-a902-43f3612762d6}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22037,7 +22037,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{7ed5cfcd-6845-4387-ae55-74667a7bb0b7}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{134d6378-f1d8-41a1-82d4-519039c8c7d4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22051,7 +22051,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{4c685db5-05d1-4038-90d0-9b9d290c8fb8}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{72999b9c-80ae-45fc-be3a-ea249a555456}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22065,7 +22065,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{d9e3acf4-eb69-40e9-b1e4-fbdbe462b35d}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{ad50e7ca-2e66-4969-ae9f-86335c0c2532}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22079,7 +22079,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{b249392e-f04b-4a9e-bd35-af64fc67566e}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{ee72aead-1930-4006-8e75-5d8517d95a00}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22093,7 +22093,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{6815efb3-ae69-4f25-a0f2-887c643e5122}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{38c8bc94-c43b-4449-9c48-533c6500d7c9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -25506,7 +25506,7 @@
         <v>37</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:22">
@@ -25533,19 +25533,19 @@
       </c>
       <c r="I20">
         <f>SUM($J$20:J20)</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="J20">
         <f>M20*$M$19</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K20">
         <f t="shared" ref="K20:K35" si="2">J20/60</f>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <f>SUM($K$20:K20)</f>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -25599,19 +25599,19 @@
       </c>
       <c r="I21">
         <f>SUM($J$20:J21)</f>
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J21">
         <f>M21*$M$19</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <f>SUM($K$20:K21)</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -25665,19 +25665,19 @@
       </c>
       <c r="I22">
         <f>SUM($J$20:J22)</f>
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="J22">
         <f t="shared" ref="J22:J34" si="3">M22*$M$19</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <f>SUM($K$20:K22)</f>
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -25731,19 +25731,19 @@
       </c>
       <c r="I23">
         <f>SUM($J$20:J23)</f>
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="J23">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>0.15</v>
+        <v>1.5</v>
       </c>
       <c r="L23">
         <f>SUM($K$20:K23)</f>
-        <v>0.45</v>
+        <v>4.5</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -25797,19 +25797,19 @@
       </c>
       <c r="I24">
         <f>SUM($J$20:J24)</f>
-        <v>36</v>
+        <v>360</v>
       </c>
       <c r="J24">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="K24">
         <f t="shared" si="2"/>
-        <v>0.15</v>
+        <v>1.5</v>
       </c>
       <c r="L24">
         <f>SUM($K$20:K24)</f>
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -25863,19 +25863,19 @@
       </c>
       <c r="I25">
         <f>SUM($J$20:J25)</f>
-        <v>48</v>
+        <v>480</v>
       </c>
       <c r="J25">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="K25">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="L25">
         <f>SUM($K$20:K25)</f>
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>12</v>
@@ -25929,19 +25929,19 @@
       </c>
       <c r="I26">
         <f>SUM($J$20:J26)</f>
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J26">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="K26">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="L26">
         <f>SUM($K$20:K26)</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>12</v>
@@ -25995,19 +25995,19 @@
       </c>
       <c r="I27">
         <f>SUM($J$20:J27)</f>
-        <v>75</v>
+        <v>750</v>
       </c>
       <c r="J27">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="K27">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L27">
         <f>SUM($K$20:K27)</f>
-        <v>1.25</v>
+        <v>12.5</v>
       </c>
       <c r="M27">
         <v>15</v>
@@ -26061,19 +26061,19 @@
       </c>
       <c r="I28">
         <f>SUM($J$20:J28)</f>
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="J28">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="K28">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L28">
         <f>SUM($K$20:K28)</f>
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="M28">
         <v>15</v>
@@ -26127,19 +26127,19 @@
       </c>
       <c r="I29">
         <f>SUM($J$20:J29)</f>
-        <v>108</v>
+        <v>1080</v>
       </c>
       <c r="J29">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="K29">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="L29">
         <f>SUM($K$20:K29)</f>
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="M29">
         <v>18</v>
@@ -26193,19 +26193,19 @@
       </c>
       <c r="I30">
         <f>SUM($J$20:J30)</f>
-        <v>126</v>
+        <v>1260</v>
       </c>
       <c r="J30">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="K30">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="L30">
         <f>SUM($K$20:K30)</f>
-        <v>2.1</v>
+        <v>21</v>
       </c>
       <c r="M30">
         <v>18</v>
@@ -26259,19 +26259,19 @@
       </c>
       <c r="I31">
         <f>SUM($J$20:J31)</f>
-        <v>147</v>
+        <v>1470</v>
       </c>
       <c r="J31">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="K31">
         <f t="shared" si="2"/>
-        <v>0.35</v>
+        <v>3.5</v>
       </c>
       <c r="L31">
         <f>SUM($K$20:K31)</f>
-        <v>2.45</v>
+        <v>24.5</v>
       </c>
       <c r="M31">
         <v>21</v>
@@ -26325,19 +26325,19 @@
       </c>
       <c r="I32">
         <f>SUM($J$20:J32)</f>
-        <v>168</v>
+        <v>1680</v>
       </c>
       <c r="J32">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="K32">
         <f t="shared" si="2"/>
-        <v>0.35</v>
+        <v>3.5</v>
       </c>
       <c r="L32">
         <f>SUM($K$20:K32)</f>
-        <v>2.8</v>
+        <v>28</v>
       </c>
       <c r="M32">
         <v>21</v>
@@ -26391,19 +26391,19 @@
       </c>
       <c r="I33">
         <f>SUM($J$20:J33)</f>
-        <v>192</v>
+        <v>1920</v>
       </c>
       <c r="J33">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="K33">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="L33">
         <f>SUM($K$20:K33)</f>
-        <v>3.2</v>
+        <v>32</v>
       </c>
       <c r="M33">
         <v>24</v>
@@ -26457,19 +26457,19 @@
       </c>
       <c r="I34">
         <f>SUM($J$20:J34)</f>
-        <v>222</v>
+        <v>2220</v>
       </c>
       <c r="J34">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="K34">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <f>SUM($K$20:K34)</f>
-        <v>3.7</v>
+        <v>37</v>
       </c>
       <c r="M34">
         <v>30</v>
@@ -32559,7 +32559,7 @@
         <v>11</v>
       </c>
       <c r="B220" s="19">
-        <f t="shared" ref="B220:B255" si="4">C220*100000+D220</f>
+        <f t="shared" ref="B220:B257" si="4">C220*100000+D220</f>
         <v>100207012</v>
       </c>
       <c r="C220">
@@ -33420,7 +33420,7 @@
     </row>
     <row r="256" spans="1:7">
       <c r="B256" s="19">
-        <f>C256*100000+D256</f>
+        <f t="shared" si="4"/>
         <v>200202003</v>
       </c>
       <c r="C256">
@@ -33441,7 +33441,7 @@
     </row>
     <row r="257" spans="2:7">
       <c r="B257" s="19">
-        <f>C257*100000+D257</f>
+        <f t="shared" si="4"/>
         <v>200202009</v>
       </c>
       <c r="C257">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -22519,7 +22519,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{be1c8502-6a73-4f97-bdd7-274e98943a3f}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{e8e8b8f1-b24b-4e7a-962e-6b5f0e4f1ad3}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22533,7 +22533,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{6462e9b6-e9d7-448b-af87-85861ae23e79}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{33ab540b-1ac7-4c37-ac6b-e6c6d4a9b92e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22547,7 +22547,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{5f97a353-58c3-4884-8a18-62091d26c09a}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{6a1be14e-074c-4b57-a18a-a02067d9c3a3}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22561,7 +22561,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{f20cb42c-5d68-4c56-8e82-1cffc206f6f8}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{2b2d4006-57e4-4ef5-9993-2eec743d907d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22575,7 +22575,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{bf3a0f08-6eba-4e75-8c1b-5a019ce0cd7b}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{1d96913b-cf79-436e-9b18-f265fedf0c88}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22589,7 +22589,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{a39d1f4f-776a-49f6-8ba4-ed5d77eb2e0b}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{8f91298e-e71b-4631-8070-8b4da943fef4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22603,7 +22603,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{df8f3843-dea7-44da-abbc-131b59d05b93}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{3501c5ab-bd3a-418f-9c63-23255b129b8d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22617,7 +22617,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{6b72a049-3424-4491-9e6f-311a90da4546}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{3686c69d-49a2-4517-8f04-1f708c10c0db}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22631,7 +22631,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{dd6fbaec-0395-4d8c-908b-5f2252a6c145}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{7380a901-7e2a-408b-9ac8-2e65a128fc50}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -26044,7 +26044,7 @@
         <v>39</v>
       </c>
       <c r="M19">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:22">
@@ -26071,19 +26071,19 @@
       </c>
       <c r="I20">
         <f>SUM($J$20:J20)</f>
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <f>M20*$M$19</f>
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <f t="shared" ref="K20:K35" si="2">J20/60</f>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L20">
         <f>SUM($K$20:K20)</f>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -26137,19 +26137,19 @@
       </c>
       <c r="I21">
         <f>SUM($J$20:J21)</f>
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J21">
         <f>M21*$M$19</f>
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L21">
         <f>SUM($K$20:K21)</f>
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -26203,19 +26203,19 @@
       </c>
       <c r="I22">
         <f>SUM($J$20:J22)</f>
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="J22">
         <f t="shared" ref="J22:J34" si="3">M22*$M$19</f>
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L22">
         <f>SUM($K$20:K22)</f>
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -26269,19 +26269,19 @@
       </c>
       <c r="I23">
         <f>SUM($J$20:J23)</f>
-        <v>270</v>
+        <v>27</v>
       </c>
       <c r="J23">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>0.15</v>
       </c>
       <c r="L23">
         <f>SUM($K$20:K23)</f>
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -26335,19 +26335,19 @@
       </c>
       <c r="I24">
         <f>SUM($J$20:J24)</f>
-        <v>360</v>
+        <v>36</v>
       </c>
       <c r="J24">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>0.15</v>
       </c>
       <c r="L24">
         <f>SUM($K$20:K24)</f>
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -26401,19 +26401,19 @@
       </c>
       <c r="I25">
         <f>SUM($J$20:J25)</f>
-        <v>480</v>
+        <v>48</v>
       </c>
       <c r="J25">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="K25">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L25">
         <f>SUM($K$20:K25)</f>
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="M25">
         <v>12</v>
@@ -26467,19 +26467,19 @@
       </c>
       <c r="I26">
         <f>SUM($J$20:J26)</f>
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="J26">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="K26">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L26">
         <f>SUM($K$20:K26)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <v>12</v>
@@ -26533,19 +26533,19 @@
       </c>
       <c r="I27">
         <f>SUM($J$20:J27)</f>
-        <v>750</v>
+        <v>75</v>
       </c>
       <c r="J27">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="K27">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="L27">
         <f>SUM($K$20:K27)</f>
-        <v>12.5</v>
+        <v>1.25</v>
       </c>
       <c r="M27">
         <v>15</v>
@@ -26599,19 +26599,19 @@
       </c>
       <c r="I28">
         <f>SUM($J$20:J28)</f>
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="J28">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="K28">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="L28">
         <f>SUM($K$20:K28)</f>
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="M28">
         <v>15</v>
@@ -26665,19 +26665,19 @@
       </c>
       <c r="I29">
         <f>SUM($J$20:J29)</f>
-        <v>1080</v>
+        <v>108</v>
       </c>
       <c r="J29">
         <f t="shared" si="3"/>
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="K29">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="L29">
         <f>SUM($K$20:K29)</f>
-        <v>18</v>
+        <v>1.8</v>
       </c>
       <c r="M29">
         <v>18</v>
@@ -26731,19 +26731,19 @@
       </c>
       <c r="I30">
         <f>SUM($J$20:J30)</f>
-        <v>1260</v>
+        <v>126</v>
       </c>
       <c r="J30">
         <f t="shared" si="3"/>
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="K30">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="L30">
         <f>SUM($K$20:K30)</f>
-        <v>21</v>
+        <v>2.1</v>
       </c>
       <c r="M30">
         <v>18</v>
@@ -26797,19 +26797,19 @@
       </c>
       <c r="I31">
         <f>SUM($J$20:J31)</f>
-        <v>1470</v>
+        <v>147</v>
       </c>
       <c r="J31">
         <f t="shared" si="3"/>
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="K31">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>0.35</v>
       </c>
       <c r="L31">
         <f>SUM($K$20:K31)</f>
-        <v>24.5</v>
+        <v>2.45</v>
       </c>
       <c r="M31">
         <v>21</v>
@@ -26863,19 +26863,19 @@
       </c>
       <c r="I32">
         <f>SUM($J$20:J32)</f>
-        <v>1680</v>
+        <v>168</v>
       </c>
       <c r="J32">
         <f t="shared" si="3"/>
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="K32">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>0.35</v>
       </c>
       <c r="L32">
         <f>SUM($K$20:K32)</f>
-        <v>28</v>
+        <v>2.8</v>
       </c>
       <c r="M32">
         <v>21</v>
@@ -26929,19 +26929,19 @@
       </c>
       <c r="I33">
         <f>SUM($J$20:J33)</f>
-        <v>1920</v>
+        <v>192</v>
       </c>
       <c r="J33">
         <f t="shared" si="3"/>
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="K33">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="L33">
         <f>SUM($K$20:K33)</f>
-        <v>32</v>
+        <v>3.2</v>
       </c>
       <c r="M33">
         <v>24</v>
@@ -26995,19 +26995,19 @@
       </c>
       <c r="I34">
         <f>SUM($J$20:J34)</f>
-        <v>2220</v>
+        <v>222</v>
       </c>
       <c r="J34">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="K34">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="L34">
         <f>SUM($K$20:K34)</f>
-        <v>37</v>
+        <v>3.7</v>
       </c>
       <c r="M34">
         <v>30</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4208" uniqueCount="1512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4208" uniqueCount="1514">
   <si>
     <t>##var</t>
   </si>
@@ -3473,6 +3473,12 @@
   </si>
   <si>
     <t>Test04</t>
+  </si>
+  <si>
+    <t>steam://openurl/https://steamcommunity.com/app/2583700?utm_source=linktree&amp;utm_medium=in_game_client&amp;utm_campaign=linktree_pre_claim</t>
+  </si>
+  <si>
+    <t>steam://openurl/https://store.steampowered.com/app/2583700?utm_source=linktree&amp;utm_medium=in_game_client&amp;utm_campaign=linktree_pre_claim</t>
   </si>
   <si>
     <t>Type</t>
@@ -11713,7 +11719,7 @@
         <v>378</v>
       </c>
       <c r="F90" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I90" t="s">
         <v>100</v>
@@ -15510,7 +15516,7 @@
         <v>640</v>
       </c>
       <c r="F147" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G147" t="s">
         <v>209</v>
@@ -16369,7 +16375,7 @@
     <col min="8" max="8" width="16.8333333333333" customWidth="1"/>
     <col min="9" max="9" width="36.75" customWidth="1"/>
     <col min="10" max="10" width="22.75" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="11" max="11" width="76.5833333333333" customWidth="1"/>
     <col min="12" max="12" width="13.0833333333333" customWidth="1"/>
     <col min="13" max="13" width="21.3333333333333" customWidth="1"/>
     <col min="14" max="14" width="21.6666666666667" customWidth="1"/>
@@ -17509,7 +17515,7 @@
         <v>1056</v>
       </c>
       <c r="K21" t="s">
-        <v>1065</v>
+        <v>1082</v>
       </c>
       <c r="L21" t="s">
         <v>1065</v>
@@ -17559,7 +17565,7 @@
         <v>1056</v>
       </c>
       <c r="K22" t="s">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="L22" t="s">
         <v>1071</v>
@@ -17688,46 +17694,46 @@
         <v>999</v>
       </c>
       <c r="E1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H1" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="I1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="J1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="K1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="L1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="M1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="N1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="O1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="P1" t="s">
         <v>791</v>
       </c>
       <c r="Q1" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="R1" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -17788,52 +17794,52 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -17841,55 +17847,55 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C4" t="s">
         <v>1036</v>
       </c>
       <c r="D4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E4" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="F4" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="I4" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="J4" t="s">
         <v>74</v>
       </c>
       <c r="K4" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="L4" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="M4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="N4" t="s">
         <v>76</v>
       </c>
       <c r="O4" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="P4" t="s">
         <v>1039</v>
       </c>
       <c r="Q4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="R4" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -17900,22 +17906,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="D5" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="E5" t="s">
         <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="G5" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="H5" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -17956,22 +17962,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D6" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E6" t="s">
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="G6" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="H6" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -18012,22 +18018,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D7" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="E7" t="s">
         <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="G7" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="H7" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -18068,22 +18074,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D8" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E8" t="s">
         <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="G8" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="H8" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -18124,22 +18130,22 @@
         <v>401005</v>
       </c>
       <c r="C9" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D9" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="E9" t="s">
         <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="G9" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="H9" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -18180,22 +18186,22 @@
         <v>401006</v>
       </c>
       <c r="C10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="D10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="G10" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="H10" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -18236,22 +18242,22 @@
         <v>401007</v>
       </c>
       <c r="C11" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D11" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="E11" t="s">
         <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="G11" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="H11" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -18292,22 +18298,22 @@
         <v>401008</v>
       </c>
       <c r="C12" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D12" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E12" t="s">
         <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="G12" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="H12" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -18348,22 +18354,22 @@
         <v>410001</v>
       </c>
       <c r="C13" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D13" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E13" t="s">
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="G13" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="H13" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -18401,22 +18407,22 @@
         <v>410002</v>
       </c>
       <c r="C14" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="D14" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="E14" t="s">
         <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="G14" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="H14" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -18451,22 +18457,22 @@
         <v>410003</v>
       </c>
       <c r="C15" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D15" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E15" t="s">
         <v>90</v>
       </c>
       <c r="F15" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="G15" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="H15" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -18501,22 +18507,22 @@
         <v>410004</v>
       </c>
       <c r="C16" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D16" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="E16" t="s">
         <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="G16" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="H16" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -18554,22 +18560,22 @@
         <v>410101</v>
       </c>
       <c r="C17" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D17" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E17" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F17" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="G17" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="H17" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -18590,7 +18596,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
@@ -18607,22 +18613,22 @@
         <v>410102</v>
       </c>
       <c r="C18" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D18" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E18" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F18" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="G18" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="H18" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -18643,7 +18649,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -18660,22 +18666,22 @@
         <v>410103</v>
       </c>
       <c r="C19" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E19" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F19" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="G19" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="H19" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -18696,7 +18702,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
@@ -18713,22 +18719,22 @@
         <v>410104</v>
       </c>
       <c r="C20" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D20" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E20" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F20" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="G20" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="H20" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -18749,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
@@ -18766,7 +18772,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -18777,19 +18783,19 @@
         <v>402001</v>
       </c>
       <c r="C22" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D22" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E22" t="s">
         <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="G22" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -18827,19 +18833,19 @@
         <v>402002</v>
       </c>
       <c r="C23" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D23" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E23" t="s">
         <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="G23" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -18874,19 +18880,19 @@
         <v>402003</v>
       </c>
       <c r="C24" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D24" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E24" t="s">
         <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="G24" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -18921,7 +18927,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -18932,19 +18938,19 @@
         <v>403001</v>
       </c>
       <c r="C26" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D26" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E26" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F26" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="G26" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="H26" t="s">
         <v>209</v>
@@ -18968,7 +18974,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -18985,19 +18991,19 @@
         <v>403002</v>
       </c>
       <c r="C27" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D27" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="E27" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F27" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="G27" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -19018,7 +19024,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -19035,40 +19041,40 @@
         <v>403003</v>
       </c>
       <c r="C28" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D28" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1209</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
         <v>1205</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1207</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" t="b">
-        <v>1</v>
-      </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>1203</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -19085,7 +19091,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -19093,19 +19099,19 @@
         <v>404001</v>
       </c>
       <c r="C30" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D30" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E30" t="s">
         <v>771</v>
       </c>
       <c r="F30" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="G30" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -19126,7 +19132,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -19143,19 +19149,19 @@
         <v>404002</v>
       </c>
       <c r="C31" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D31" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E31" t="s">
         <v>771</v>
       </c>
       <c r="F31" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="G31" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -19176,7 +19182,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -19193,19 +19199,19 @@
         <v>404004</v>
       </c>
       <c r="C32" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D32" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E32" t="s">
         <v>771</v>
       </c>
       <c r="F32" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="G32" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -19226,7 +19232,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -19243,19 +19249,19 @@
         <v>404005</v>
       </c>
       <c r="C33" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D33" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E33" t="s">
         <v>771</v>
       </c>
       <c r="F33" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="G33" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -19276,7 +19282,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -19293,19 +19299,19 @@
         <v>404007</v>
       </c>
       <c r="C34" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="D34" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="E34" t="s">
         <v>771</v>
       </c>
       <c r="F34" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="G34" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -19326,7 +19332,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -19343,19 +19349,19 @@
         <v>404008</v>
       </c>
       <c r="C35" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D35" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E35" t="s">
         <v>771</v>
       </c>
       <c r="F35" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="G35" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -19376,7 +19382,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -19393,19 +19399,19 @@
         <v>404010</v>
       </c>
       <c r="C36" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D36" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="E36" t="s">
         <v>771</v>
       </c>
       <c r="F36" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="G36" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -19426,7 +19432,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -19443,19 +19449,19 @@
         <v>404011</v>
       </c>
       <c r="C37" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D37" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="E37" t="s">
         <v>771</v>
       </c>
       <c r="F37" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="G37" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -19476,7 +19482,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -19493,19 +19499,19 @@
         <v>404013</v>
       </c>
       <c r="C38" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="D38" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="E38" t="s">
         <v>771</v>
       </c>
       <c r="F38" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="G38" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -19526,7 +19532,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -19543,7 +19549,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -19551,19 +19557,19 @@
         <v>405001</v>
       </c>
       <c r="C40" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="D40" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E40" t="s">
         <v>771</v>
       </c>
       <c r="F40" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="G40" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -19584,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -19601,7 +19607,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -19609,22 +19615,22 @@
         <v>406005</v>
       </c>
       <c r="C42" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="D42" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E42" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F42" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="G42" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="H42" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -19645,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -19662,22 +19668,22 @@
         <v>406006</v>
       </c>
       <c r="C43" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D43" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E43" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F43" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="G43" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="H43" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -19698,7 +19704,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -19715,22 +19721,22 @@
         <v>406007</v>
       </c>
       <c r="C44" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D44" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E44" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F44" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="G44" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="H44" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I44" t="b">
         <v>1</v>
@@ -19751,7 +19757,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -19768,22 +19774,22 @@
         <v>406008</v>
       </c>
       <c r="C45" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D45" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E45" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F45" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="G45" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="H45" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -19804,7 +19810,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -19826,7 +19832,7 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C47" t="s">
         <v>209</v>
@@ -19885,19 +19891,19 @@
         <v>201001</v>
       </c>
       <c r="C48" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="D48" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E48" t="s">
         <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="G48" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="H48" t="s">
         <v>209</v>
@@ -19941,19 +19947,19 @@
         <v>201002</v>
       </c>
       <c r="C49" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D49" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E49" t="s">
         <v>90</v>
       </c>
       <c r="F49" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="G49" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="H49" t="s">
         <v>209</v>
@@ -19997,19 +20003,19 @@
         <v>204001</v>
       </c>
       <c r="C50" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D50" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E50" t="s">
         <v>90</v>
       </c>
       <c r="F50" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="G50" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="H50" t="s">
         <v>209</v>
@@ -20050,7 +20056,7 @@
         <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C51" t="s">
         <v>209</v>
@@ -20109,19 +20115,19 @@
         <v>301001</v>
       </c>
       <c r="C52" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="D52" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="E52" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F52" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="G52" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="H52" t="s">
         <v>209</v>
@@ -20145,7 +20151,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -20165,43 +20171,43 @@
         <v>301002</v>
       </c>
       <c r="C53" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D53" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H53" t="s">
+        <v>209</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
         <v>1205</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F53" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G53" t="s">
-        <v>1207</v>
-      </c>
-      <c r="H53" t="s">
-        <v>209</v>
-      </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" t="b">
-        <v>1</v>
-      </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
-      <c r="O53" t="s">
-        <v>1203</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -20218,7 +20224,7 @@
         <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -20226,22 +20232,22 @@
         <v>500005</v>
       </c>
       <c r="C55" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D55" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E55" t="s">
         <v>90</v>
       </c>
       <c r="F55" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="G55" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="H55" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -20279,22 +20285,22 @@
         <v>500012</v>
       </c>
       <c r="C56" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="D56" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="E56" t="s">
         <v>90</v>
       </c>
       <c r="F56" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G56" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="H56" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
@@ -20332,7 +20338,7 @@
         <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C57" t="s">
         <v>209</v>
@@ -20391,22 +20397,22 @@
         <v>501001</v>
       </c>
       <c r="C58" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="D58" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E58" t="s">
         <v>90</v>
       </c>
       <c r="F58" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="G58" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="H58" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
@@ -20447,22 +20453,22 @@
         <v>501002</v>
       </c>
       <c r="C59" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="D59" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E59" t="s">
         <v>90</v>
       </c>
       <c r="F59" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="G59" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="H59" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
@@ -20503,22 +20509,22 @@
         <v>501003</v>
       </c>
       <c r="C60" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D60" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E60" t="s">
         <v>90</v>
       </c>
       <c r="F60" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="G60" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="H60" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
@@ -20559,22 +20565,22 @@
         <v>501004</v>
       </c>
       <c r="C61" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="D61" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="E61" t="s">
         <v>90</v>
       </c>
       <c r="F61" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="G61" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="H61" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
@@ -20615,22 +20621,22 @@
         <v>501005</v>
       </c>
       <c r="C62" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D62" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E62" t="s">
         <v>90</v>
       </c>
       <c r="F62" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="G62" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="H62" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
@@ -20671,22 +20677,22 @@
         <v>501006</v>
       </c>
       <c r="C63" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D63" t="s">
         <v>1299</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1297</v>
       </c>
       <c r="E63" t="s">
         <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="G63" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="H63" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
@@ -20727,22 +20733,22 @@
         <v>501007</v>
       </c>
       <c r="C64" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D64" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="E64" t="s">
         <v>90</v>
       </c>
       <c r="F64" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="G64" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="H64" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
@@ -20780,7 +20786,7 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="C65" t="s">
         <v>209</v>
@@ -20839,22 +20845,22 @@
         <v>601001</v>
       </c>
       <c r="C66" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D66" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E66" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F66" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="G66" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="H66" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I66" t="b">
         <v>1</v>
@@ -20875,7 +20881,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
@@ -20895,22 +20901,22 @@
         <v>601002</v>
       </c>
       <c r="C67" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="D67" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E67" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F67" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="G67" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="H67" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I67" t="b">
         <v>1</v>
@@ -20931,7 +20937,7 @@
         <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -20951,22 +20957,22 @@
         <v>601003</v>
       </c>
       <c r="C68" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D68" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E68" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F68" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="G68" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="H68" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I68" t="b">
         <v>1</v>
@@ -20987,7 +20993,7 @@
         <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -21007,22 +21013,22 @@
         <v>601004</v>
       </c>
       <c r="C69" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="D69" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E69" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F69" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="G69" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="H69" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I69" t="b">
         <v>1</v>
@@ -21043,7 +21049,7 @@
         <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
@@ -21063,22 +21069,22 @@
         <v>601005</v>
       </c>
       <c r="C70" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="D70" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E70" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F70" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="G70" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="H70" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I70" t="b">
         <v>1</v>
@@ -21099,7 +21105,7 @@
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -21119,22 +21125,22 @@
         <v>601006</v>
       </c>
       <c r="C71" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="D71" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E71" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F71" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="G71" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="H71" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I71" t="b">
         <v>1</v>
@@ -21155,7 +21161,7 @@
         <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="P71" t="b">
         <v>0</v>
@@ -21175,22 +21181,22 @@
         <v>601007</v>
       </c>
       <c r="C72" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D72" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E72" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F72" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="G72" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="H72" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="I72" t="b">
         <v>1</v>
@@ -21211,7 +21217,7 @@
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -21228,7 +21234,7 @@
         <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C73" t="s">
         <v>209</v>
@@ -21287,19 +21293,19 @@
         <v>700001</v>
       </c>
       <c r="C74" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="D74" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="E74" t="s">
         <v>771</v>
       </c>
       <c r="F74" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="G74" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="H74" t="s">
         <v>209</v>
@@ -21323,7 +21329,7 @@
         <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -21343,19 +21349,19 @@
         <v>700002</v>
       </c>
       <c r="C75" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D75" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="E75" t="s">
         <v>771</v>
       </c>
       <c r="F75" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="G75" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="H75" t="s">
         <v>209</v>
@@ -21379,7 +21385,7 @@
         <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -21399,19 +21405,19 @@
         <v>700004</v>
       </c>
       <c r="C76" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="D76" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="E76" t="s">
         <v>771</v>
       </c>
       <c r="F76" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="G76" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="H76" t="s">
         <v>209</v>
@@ -21435,7 +21441,7 @@
         <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -21455,19 +21461,19 @@
         <v>700005</v>
       </c>
       <c r="C77" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="D77" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="E77" t="s">
         <v>771</v>
       </c>
       <c r="F77" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="G77" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="H77" t="s">
         <v>209</v>
@@ -21491,7 +21497,7 @@
         <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -21511,19 +21517,19 @@
         <v>700007</v>
       </c>
       <c r="C78" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="D78" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="E78" t="s">
         <v>771</v>
       </c>
       <c r="F78" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="G78" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="H78" t="s">
         <v>209</v>
@@ -21547,7 +21553,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -21567,19 +21573,19 @@
         <v>700008</v>
       </c>
       <c r="C79" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D79" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E79" t="s">
         <v>771</v>
       </c>
       <c r="F79" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="G79" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="H79" t="s">
         <v>209</v>
@@ -21603,7 +21609,7 @@
         <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -21623,19 +21629,19 @@
         <v>700010</v>
       </c>
       <c r="C80" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="D80" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="E80" t="s">
         <v>771</v>
       </c>
       <c r="F80" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="G80" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="H80" t="s">
         <v>209</v>
@@ -21659,7 +21665,7 @@
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -21679,19 +21685,19 @@
         <v>700011</v>
       </c>
       <c r="C81" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="D81" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="E81" t="s">
         <v>771</v>
       </c>
       <c r="F81" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="G81" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="H81" t="s">
         <v>209</v>
@@ -21715,7 +21721,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -21732,7 +21738,7 @@
         <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -21740,19 +21746,19 @@
         <v>700101</v>
       </c>
       <c r="C83" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="D83" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="E83" t="s">
         <v>771</v>
       </c>
       <c r="F83" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="G83" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="H83" t="s">
         <v>209</v>
@@ -21776,7 +21782,7 @@
         <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -21793,19 +21799,19 @@
         <v>700102</v>
       </c>
       <c r="C84" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="D84" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="E84" t="s">
         <v>771</v>
       </c>
       <c r="F84" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="G84" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="H84" t="s">
         <v>209</v>
@@ -21829,7 +21835,7 @@
         <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -21846,19 +21852,19 @@
         <v>700104</v>
       </c>
       <c r="C85" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="D85" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="E85" t="s">
         <v>771</v>
       </c>
       <c r="F85" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="G85" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="H85" t="s">
         <v>209</v>
@@ -21882,7 +21888,7 @@
         <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -21899,19 +21905,19 @@
         <v>700105</v>
       </c>
       <c r="C86" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="D86" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E86" t="s">
         <v>771</v>
       </c>
       <c r="F86" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="G86" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="H86" t="s">
         <v>209</v>
@@ -21935,7 +21941,7 @@
         <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -21952,19 +21958,19 @@
         <v>700107</v>
       </c>
       <c r="C87" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="D87" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="E87" t="s">
         <v>771</v>
       </c>
       <c r="F87" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="G87" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="H87" t="s">
         <v>209</v>
@@ -21988,7 +21994,7 @@
         <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -22005,19 +22011,19 @@
         <v>700108</v>
       </c>
       <c r="C88" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="D88" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="E88" t="s">
         <v>771</v>
       </c>
       <c r="F88" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="G88" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="H88" t="s">
         <v>209</v>
@@ -22041,7 +22047,7 @@
         <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -22058,19 +22064,19 @@
         <v>700110</v>
       </c>
       <c r="C89" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="D89" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="E89" t="s">
         <v>771</v>
       </c>
       <c r="F89" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="G89" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="H89" t="s">
         <v>209</v>
@@ -22094,7 +22100,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -22111,19 +22117,19 @@
         <v>700111</v>
       </c>
       <c r="C90" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="D90" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="E90" t="s">
         <v>771</v>
       </c>
       <c r="F90" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="G90" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="H90" t="s">
         <v>209</v>
@@ -22147,7 +22153,7 @@
         <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -22164,7 +22170,7 @@
         <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="C91" t="s">
         <v>209</v>
@@ -22223,19 +22229,19 @@
         <v>701001</v>
       </c>
       <c r="C92" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="D92" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="E92" t="s">
         <v>771</v>
       </c>
       <c r="F92" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="G92" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="H92" t="s">
         <v>209</v>
@@ -22259,7 +22265,7 @@
         <v>0</v>
       </c>
       <c r="O92" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -22276,7 +22282,7 @@
         <v>39</v>
       </c>
       <c r="B93" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -22284,19 +22290,19 @@
         <v>701101</v>
       </c>
       <c r="C94" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="D94" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="E94" t="s">
         <v>771</v>
       </c>
       <c r="F94" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="G94" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="H94" t="s">
         <v>209</v>
@@ -22320,7 +22326,7 @@
         <v>0</v>
       </c>
       <c r="O94" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -22519,7 +22525,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{e8e8b8f1-b24b-4e7a-962e-6b5f0e4f1ad3}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{be15d0e2-e084-4d65-94ac-e79f7f45b1fc}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22533,7 +22539,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{33ab540b-1ac7-4c37-ac6b-e6c6d4a9b92e}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{e5b1f50d-8854-4e42-b4cf-c3d50b5666f9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22547,7 +22553,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{6a1be14e-074c-4b57-a18a-a02067d9c3a3}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{10471fed-4df1-4370-9cce-ab4037d824f1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22561,7 +22567,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{2b2d4006-57e4-4ef5-9993-2eec743d907d}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{e35e3b31-ba04-44c5-91b3-8d7334033942}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22575,7 +22581,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{1d96913b-cf79-436e-9b18-f265fedf0c88}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{dab0fb34-d354-4449-bc17-ccbc98bb3ccd}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22589,7 +22595,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{8f91298e-e71b-4631-8070-8b4da943fef4}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{ac4ecf29-c990-4ed0-9342-085d7dc3c6fc}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22603,7 +22609,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{3501c5ab-bd3a-418f-9c63-23255b129b8d}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{bf527d8b-e1de-4617-8f48-bb4bce941df1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22617,7 +22623,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{3686c69d-49a2-4517-8f04-1f708c10c0db}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{9a05c627-d184-44e2-b804-e53f747f86df}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22631,7 +22637,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{7380a901-7e2a-408b-9ac8-2e65a128fc50}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{af3a5d6c-9ba8-44b1-ab4f-395a44b93296}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22670,19 +22676,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="D1" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="G1" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -22739,13 +22745,13 @@
         <v>707</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>746</v>
@@ -22768,13 +22774,13 @@
         <v>199999</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>747</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="6" ht="52.2" spans="1:7">
@@ -22791,13 +22797,13 @@
         <v>299999</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="G6" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="7" ht="87" spans="1:7">
@@ -22814,13 +22820,13 @@
         <v>229999</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="8" ht="84" customHeight="1" spans="1:7">
@@ -22834,13 +22840,13 @@
         <v>209999</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="9" ht="65" customHeight="1" spans="1:7">
@@ -22857,13 +22863,13 @@
         <v>299999</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="G9" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="10" ht="69.6" spans="1:7">
@@ -22880,13 +22886,13 @@
         <v>399999</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="11" ht="67" customHeight="1" spans="1:7">
@@ -22900,13 +22906,13 @@
         <v>399999</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G11" t="s">
         <v>1421</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="12" ht="34.8" spans="1:7">
@@ -22923,13 +22929,13 @@
         <v>301999</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:7">
@@ -22943,13 +22949,13 @@
         <v>301999</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G13" t="s">
         <v>1426</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="14" ht="34.8" spans="1:7">
@@ -22966,13 +22972,13 @@
         <v>302999</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G14" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="15" ht="34.8" spans="1:7">
@@ -22989,13 +22995,13 @@
         <v>399999</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="G15" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="16" ht="87" spans="1:7">
@@ -23012,13 +23018,13 @@
         <v>499999</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="G16" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="17" ht="52.2" spans="1:7">
@@ -23035,13 +23041,13 @@
         <v>409999</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="G17" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="18" ht="52.2" spans="1:7">
@@ -23058,13 +23064,13 @@
         <v>499999</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="G18" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="19" ht="52.2" spans="1:7">
@@ -23081,13 +23087,13 @@
         <v>599999</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="G19" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="20" ht="52.2" spans="1:7">
@@ -23101,13 +23107,13 @@
         <v>500999</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="G20" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="21" ht="34.8" spans="1:7">
@@ -23124,13 +23130,13 @@
         <v>501999</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="G21" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="22" ht="34.8" spans="1:7">
@@ -23147,13 +23153,13 @@
         <v>502999</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="G22" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="23" ht="34.8" spans="1:7">
@@ -23170,13 +23176,13 @@
         <v>599999</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="G23" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="24" ht="87" spans="1:7">
@@ -23193,13 +23199,13 @@
         <v>699999</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="G24" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="25" ht="34.8" spans="1:7">
@@ -23216,13 +23222,13 @@
         <v>601999</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="G25" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="26" ht="34.8" spans="1:7">
@@ -23239,13 +23245,13 @@
         <v>602999</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="G26" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="27" ht="34.8" spans="1:7">
@@ -23262,13 +23268,13 @@
         <v>603999</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="G27" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="28" ht="34.8" spans="1:7">
@@ -23285,13 +23291,13 @@
         <v>699999</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="G28" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="29" ht="34.8" spans="1:7">
@@ -23308,13 +23314,13 @@
         <v>799999</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="G29" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="30" ht="52.2" spans="1:7">
@@ -23331,13 +23337,13 @@
         <v>709999</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="G30" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="31" ht="34.8" spans="1:7">
@@ -23354,13 +23360,13 @@
         <v>700999</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="32" ht="52.2" spans="1:7">
@@ -23374,13 +23380,13 @@
         <v>700999</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="G32" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="33" ht="34.8" spans="1:7">
@@ -23394,13 +23400,13 @@
         <v>700099</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="G33" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="34" ht="34.8" spans="1:7">
@@ -23414,13 +23420,13 @@
         <v>700999</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="G34" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="35" ht="34.8" spans="1:7">
@@ -23437,13 +23443,13 @@
         <v>701999</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="36" ht="71" customHeight="1" spans="1:7">
@@ -23457,13 +23463,13 @@
         <v>701999</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="G36" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="37" ht="71" customHeight="1" spans="1:7">
@@ -23477,13 +23483,13 @@
         <v>701099</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="G37" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="38" ht="71" customHeight="1" spans="1:7">
@@ -23497,13 +23503,13 @@
         <v>701999</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="G38" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="39" ht="34.8" spans="1:7">
@@ -23520,13 +23526,13 @@
         <v>709999</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="G39" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="40" ht="34.8" spans="1:7">
@@ -23543,13 +23549,13 @@
         <v>799999</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="G40" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="41" ht="34.8" spans="1:7">
@@ -23566,10 +23572,10 @@
         <v>999999</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="G41" t="s">
         <v>779</v>
@@ -23589,13 +23595,13 @@
         <v>99999</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="G42" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="43" spans="1:7">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -2913,6 +2913,12 @@
     <t>新手盲盒概率会高一点</t>
   </si>
   <si>
+    <t>Demo盲盒普</t>
+  </si>
+  <si>
+    <t>Demo盲盒狗</t>
+  </si>
+  <si>
     <t>测试活动盲盒：特殊1</t>
   </si>
   <si>
@@ -2941,12 +2947,6 @@
   </si>
   <si>
     <t>特殊盲盒</t>
-  </si>
-  <si>
-    <t>Demo盲盒普</t>
-  </si>
-  <si>
-    <t>Demo盲盒狗</t>
   </si>
   <si>
     <t>ActualRarity</t>
@@ -5608,7 +5608,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="34">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5690,6 +5690,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="7" tint="0.8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5914,25 +5921,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="22"/>
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstColumn" dxfId="19"/>
-      <tableStyleElement type="lastColumn" dxfId="18"/>
-      <tableStyleElement type="firstRowStripe" dxfId="17"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
+      <tableStyleElement type="wholeTable" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="totalRow" dxfId="21"/>
+      <tableStyleElement type="firstColumn" dxfId="20"/>
+      <tableStyleElement type="lastColumn" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="32"/>
-      <tableStyleElement type="totalRow" dxfId="31"/>
-      <tableStyleElement type="firstRowStripe" dxfId="30"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="29"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="28"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="27"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="26"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="25"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="24"/>
-      <tableStyleElement type="pageFieldValues" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="33"/>
+      <tableStyleElement type="totalRow" dxfId="32"/>
+      <tableStyleElement type="firstRowStripe" dxfId="31"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="30"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="29"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="28"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="27"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="26"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="25"/>
+      <tableStyleElement type="pageFieldValues" dxfId="24"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -17730,12 +17737,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",F15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F14 F16:F1048576">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22426,182 +22433,182 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I62">
-    <cfRule type="cellIs" dxfId="13" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="50" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N62">
-    <cfRule type="cellIs" dxfId="13" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="48" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P62">
-    <cfRule type="containsText" dxfId="14" priority="46" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="46" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q62">
-    <cfRule type="cellIs" dxfId="15" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63">
-    <cfRule type="cellIs" dxfId="13" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="45" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N63">
-    <cfRule type="cellIs" dxfId="13" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="43" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P63">
-    <cfRule type="containsText" dxfId="14" priority="41" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="41" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63">
-    <cfRule type="cellIs" dxfId="15" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="42" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64">
-    <cfRule type="cellIs" dxfId="13" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="30" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N64">
-    <cfRule type="cellIs" dxfId="13" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="28" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P64">
-    <cfRule type="containsText" dxfId="14" priority="26" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="26" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q64">
-    <cfRule type="cellIs" dxfId="15" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="27" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I70">
-    <cfRule type="cellIs" dxfId="13" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="40" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N70">
-    <cfRule type="cellIs" dxfId="13" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="38" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P70">
-    <cfRule type="containsText" dxfId="14" priority="36" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="36" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q70">
-    <cfRule type="cellIs" dxfId="15" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="37" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I71">
-    <cfRule type="cellIs" dxfId="13" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="35" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N71">
-    <cfRule type="cellIs" dxfId="13" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="33" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P71">
-    <cfRule type="containsText" dxfId="14" priority="31" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="31" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P71)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71">
-    <cfRule type="cellIs" dxfId="15" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="32" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I72">
-    <cfRule type="cellIs" dxfId="13" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="25" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N72">
-    <cfRule type="cellIs" dxfId="13" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="23" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P72">
-    <cfRule type="containsText" dxfId="14" priority="21" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="21" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P72)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q72">
-    <cfRule type="cellIs" dxfId="15" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="22" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I16">
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17:I20">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13:N16">
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N17:N20">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:P16">
-    <cfRule type="containsText" dxfId="14" priority="6" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="6" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P17:P20">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q13:Q16">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17:Q20">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I12 I21:I61 I65:I69 I73:I1048576">
-    <cfRule type="cellIs" dxfId="13" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="55" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N12 N21:N61 N65:N69 N73:N1048576">
-    <cfRule type="cellIs" dxfId="13" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="53" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:P12 P21:P61 P65:P69 P73:P1048576">
-    <cfRule type="containsText" dxfId="14" priority="51" operator="between" text="FALSE">
+    <cfRule type="containsText" dxfId="15" priority="51" operator="between" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",P1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:Q12 Q21:Q61 Q65:Q69 Q73:Q1048576">
-    <cfRule type="cellIs" dxfId="15" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="52" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22611,7 +22618,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{125adfa4-bf49-44be-ae1e-4384422e272a}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{74e1bce9-ee91-4a9e-b40c-5b960f076526}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22625,7 +22632,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{9342d726-6bde-4361-b68e-bb93cde921a9}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{aa462234-92bf-449c-855a-51430fc09cb6}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22639,7 +22646,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{ad483497-796d-421b-a84f-f687ee489da6}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{27e5afb1-337b-406a-acb1-4864b070d93e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22653,7 +22660,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{70f38fde-287e-41be-a763-1b09eb468a58}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{2c064d7f-00ec-4ce9-9725-6a0377e493c5}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22667,7 +22674,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{5fa5f3a3-8a4a-4982-aedb-630f4c13bb22}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{a199e64e-b339-4c48-994c-e73986d55fec}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22681,7 +22688,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{8bb8031f-1808-4c2f-9ecd-3818ac60d881}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{b1220e1c-8c91-4d90-b636-99d4c5b00c57}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22695,7 +22702,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{3b5b39d3-5f96-402a-895a-1220c079961d}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{b187bbeb-c763-4ba2-aeaf-24bfb50267d4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22709,7 +22716,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{3f1c41f0-e467-4a50-aed3-2bac7647ee63}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{27ae4905-7201-4939-a242-b6a8716164e1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22723,7 +22730,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{ab195605-99c3-4076-832e-41d7d07eb4cf}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{cb1904f3-dd60-4bc4-a26f-5e623fdd05ea}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -27680,7 +27687,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>724</v>
+        <v>896</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -27704,7 +27711,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>724</v>
+        <v>896</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27728,7 +27735,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>724</v>
+        <v>896</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -27752,7 +27759,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>724</v>
+        <v>896</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -27776,7 +27783,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>724</v>
+        <v>896</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -27800,7 +27807,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>724</v>
+        <v>896</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -27826,14 +27833,14 @@
         <v>0</v>
       </c>
       <c r="F33" s="17">
-        <f t="shared" ref="F33:F38" si="3">E33/10000</f>
+        <f>E33/SUM($E$33:$E$38)</f>
         <v>0</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27850,14 +27857,14 @@
         <v>0</v>
       </c>
       <c r="F34" s="17">
-        <f t="shared" si="3"/>
+        <f>E34/SUM($E$33:$E$38)</f>
         <v>0</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -27874,14 +27881,14 @@
         <v>0</v>
       </c>
       <c r="F35" s="17">
-        <f t="shared" si="3"/>
+        <f>E35/SUM($E$33:$E$38)</f>
         <v>0</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -27898,14 +27905,14 @@
         <v>1000</v>
       </c>
       <c r="F36" s="17">
-        <f t="shared" si="3"/>
-        <v>0.1</v>
+        <f>E36/SUM($E$33:$E$38)</f>
+        <v>0.434782608695652</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -27919,17 +27926,17 @@
         <v>113</v>
       </c>
       <c r="E37">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F37" s="17">
-        <f t="shared" si="3"/>
-        <v>0.1</v>
+        <f>E37/SUM($E$33:$E$38)</f>
+        <v>0.347826086956522</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -27943,17 +27950,17 @@
         <v>129</v>
       </c>
       <c r="E38">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F38" s="17">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
+        <f>E38/SUM($E$33:$E$38)</f>
+        <v>0.217391304347826</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -27962,7 +27969,7 @@
       </c>
       <c r="F39" s="17">
         <f>SUM(F33:F38)</f>
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -27982,7 +27989,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -28004,14 +28011,14 @@
         <v>0</v>
       </c>
       <c r="F42" s="17">
-        <f t="shared" ref="F42:F47" si="4">E42/10000</f>
+        <f t="shared" ref="F42:F47" si="3">E42/10000</f>
         <v>0</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -28028,7 +28035,7 @@
         <v>6700</v>
       </c>
       <c r="F43" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.67</v>
       </c>
       <c r="G43" t="b">
@@ -28049,7 +28056,7 @@
         <v>2200</v>
       </c>
       <c r="F44" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.22</v>
       </c>
       <c r="G44" t="b">
@@ -28070,7 +28077,7 @@
         <v>900</v>
       </c>
       <c r="F45" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.09</v>
       </c>
       <c r="G45" t="b">
@@ -28091,7 +28098,7 @@
         <v>180</v>
       </c>
       <c r="F46" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.018</v>
       </c>
       <c r="G46" t="b">
@@ -28112,7 +28119,7 @@
         <v>20</v>
       </c>
       <c r="F47" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.002</v>
       </c>
       <c r="G47" t="b">
@@ -28158,7 +28165,7 @@
         <v>845</v>
       </c>
       <c r="D1" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E1" t="s">
         <v>889</v>
@@ -28198,19 +28205,19 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>859</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>209</v>
@@ -28227,10 +28234,10 @@
         <v>811</v>
       </c>
       <c r="D4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E4" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>821</v>
@@ -33973,7 +33980,7 @@
         <v>0</v>
       </c>
       <c r="G252" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -33997,7 +34004,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -34021,7 +34028,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -34045,7 +34052,7 @@
         <v>0</v>
       </c>
       <c r="G255" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -34066,7 +34073,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="257" spans="2:7">
@@ -34087,7 +34094,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="258" spans="2:7">
@@ -34108,7 +34115,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="259" spans="2:7">
@@ -34129,7 +34136,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="260" spans="2:7">
@@ -34150,7 +34157,7 @@
         <v>1</v>
       </c>
       <c r="G260" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="261" spans="2:7">
@@ -34171,7 +34178,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="262" spans="2:7">
@@ -34192,7 +34199,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="263" spans="2:7">
@@ -34213,7 +34220,7 @@
         <v>1</v>
       </c>
       <c r="G263" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="264" spans="2:7">
@@ -34234,7 +34241,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="265" spans="2:7">
@@ -34255,7 +34262,7 @@
         <v>1</v>
       </c>
       <c r="G265" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="266" spans="2:7">
@@ -34276,7 +34283,7 @@
         <v>1</v>
       </c>
       <c r="G266" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
     </row>
     <row r="267" spans="2:7">
@@ -34297,7 +34304,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
     </row>
     <row r="268" spans="2:7">
@@ -34317,7 +34324,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
     </row>
     <row r="269" spans="2:7">
@@ -34337,7 +34344,7 @@
         <v>1</v>
       </c>
       <c r="G269" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
     </row>
     <row r="270" spans="2:7">
@@ -34352,43 +34359,28 @@
         <v>2013</v>
       </c>
       <c r="E270">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F270" s="17" t="b">
         <v>1</v>
       </c>
       <c r="G270" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G$1:G$1048576">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"Demo盲盒普"</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"新手盲盒"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"标准盲盒"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>"Demo盲盒狗"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35899,7 +35891,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C1" t="s">
         <v>964</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -16040,10 +16040,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I76 I5:I41 I43:I52 I55:I75 I77:I120 I122:I129 I133:I153">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I41 I43:I52 I55:I120 I122:I129 I133:I153">
       <formula1>表说明!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L41 L43:L52 L55:L74 L75:L76 L77:L120 L122:L130 L133:L153">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L41 L43:L52 L55:L120 L122:L130 L133:L153">
       <formula1>表说明!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -22618,7 +22618,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{74e1bce9-ee91-4a9e-b40c-5b960f076526}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{5cd8f23a-fd2a-4d4c-8669-e72a915161df}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22632,7 +22632,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{aa462234-92bf-449c-855a-51430fc09cb6}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{bc619b5b-3fe7-4113-9173-c84547240797}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22646,7 +22646,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{27e5afb1-337b-406a-acb1-4864b070d93e}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{b2a6a966-bc09-47c8-bdc1-e52804d2ee47}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22660,7 +22660,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{2c064d7f-00ec-4ce9-9725-6a0377e493c5}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{719dcc94-2956-4c0e-a8a7-353b4f4fe1ca}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22674,7 +22674,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{a199e64e-b339-4c48-994c-e73986d55fec}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{db71dfd4-292d-416f-9655-3bd93b893ad4}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22688,7 +22688,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{b1220e1c-8c91-4d90-b636-99d4c5b00c57}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{b7155e30-071e-45e0-8c0e-42ae47e9895c}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22702,7 +22702,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{b187bbeb-c763-4ba2-aeaf-24bfb50267d4}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{7eea5c30-edb1-44b2-b9eb-69bd8e5c03a9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22716,7 +22716,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{27ae4905-7201-4939-a242-b6a8716164e1}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{ca1c20b9-ffbe-4e5a-848c-b4f2f52a3dd2}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22730,7 +22730,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{cb1904f3-dd60-4bc4-a26f-5e623fdd05ea}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{ac386404-1c82-4862-9c46-7356706f9c8a}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -26143,7 +26143,7 @@
         <v>39</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:22">
@@ -26170,19 +26170,19 @@
       </c>
       <c r="I20">
         <f>SUM($J$20:J20)</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="J20">
         <f>M20*$M$19</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K20">
         <f t="shared" ref="K20:K35" si="2">J20/60</f>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <f>SUM($K$20:K20)</f>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -26236,19 +26236,19 @@
       </c>
       <c r="I21">
         <f>SUM($J$20:J21)</f>
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J21">
         <f>M21*$M$19</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <f>SUM($K$20:K21)</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -26302,19 +26302,19 @@
       </c>
       <c r="I22">
         <f>SUM($J$20:J22)</f>
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="J22">
         <f t="shared" ref="J22:J34" si="3">M22*$M$19</f>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <f>SUM($K$20:K22)</f>
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -26368,19 +26368,19 @@
       </c>
       <c r="I23">
         <f>SUM($J$20:J23)</f>
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="J23">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>0.15</v>
+        <v>1.5</v>
       </c>
       <c r="L23">
         <f>SUM($K$20:K23)</f>
-        <v>0.45</v>
+        <v>4.5</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -26434,19 +26434,19 @@
       </c>
       <c r="I24">
         <f>SUM($J$20:J24)</f>
-        <v>36</v>
+        <v>360</v>
       </c>
       <c r="J24">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="K24">
         <f t="shared" si="2"/>
-        <v>0.15</v>
+        <v>1.5</v>
       </c>
       <c r="L24">
         <f>SUM($K$20:K24)</f>
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -26500,19 +26500,19 @@
       </c>
       <c r="I25">
         <f>SUM($J$20:J25)</f>
-        <v>48</v>
+        <v>480</v>
       </c>
       <c r="J25">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="K25">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="L25">
         <f>SUM($K$20:K25)</f>
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>12</v>
@@ -26566,19 +26566,19 @@
       </c>
       <c r="I26">
         <f>SUM($J$20:J26)</f>
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="J26">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="K26">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="L26">
         <f>SUM($K$20:K26)</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>12</v>
@@ -26632,19 +26632,19 @@
       </c>
       <c r="I27">
         <f>SUM($J$20:J27)</f>
-        <v>75</v>
+        <v>750</v>
       </c>
       <c r="J27">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="K27">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L27">
         <f>SUM($K$20:K27)</f>
-        <v>1.25</v>
+        <v>12.5</v>
       </c>
       <c r="M27">
         <v>15</v>
@@ -26698,19 +26698,19 @@
       </c>
       <c r="I28">
         <f>SUM($J$20:J28)</f>
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="J28">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="K28">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L28">
         <f>SUM($K$20:K28)</f>
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="M28">
         <v>15</v>
@@ -26764,19 +26764,19 @@
       </c>
       <c r="I29">
         <f>SUM($J$20:J29)</f>
-        <v>108</v>
+        <v>1080</v>
       </c>
       <c r="J29">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="K29">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="L29">
         <f>SUM($K$20:K29)</f>
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="M29">
         <v>18</v>
@@ -26830,19 +26830,19 @@
       </c>
       <c r="I30">
         <f>SUM($J$20:J30)</f>
-        <v>126</v>
+        <v>1260</v>
       </c>
       <c r="J30">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="K30">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="L30">
         <f>SUM($K$20:K30)</f>
-        <v>2.1</v>
+        <v>21</v>
       </c>
       <c r="M30">
         <v>18</v>
@@ -26896,19 +26896,19 @@
       </c>
       <c r="I31">
         <f>SUM($J$20:J31)</f>
-        <v>147</v>
+        <v>1470</v>
       </c>
       <c r="J31">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="K31">
         <f t="shared" si="2"/>
-        <v>0.35</v>
+        <v>3.5</v>
       </c>
       <c r="L31">
         <f>SUM($K$20:K31)</f>
-        <v>2.45</v>
+        <v>24.5</v>
       </c>
       <c r="M31">
         <v>21</v>
@@ -26962,19 +26962,19 @@
       </c>
       <c r="I32">
         <f>SUM($J$20:J32)</f>
-        <v>168</v>
+        <v>1680</v>
       </c>
       <c r="J32">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="K32">
         <f t="shared" si="2"/>
-        <v>0.35</v>
+        <v>3.5</v>
       </c>
       <c r="L32">
         <f>SUM($K$20:K32)</f>
-        <v>2.8</v>
+        <v>28</v>
       </c>
       <c r="M32">
         <v>21</v>
@@ -27028,19 +27028,19 @@
       </c>
       <c r="I33">
         <f>SUM($J$20:J33)</f>
-        <v>192</v>
+        <v>1920</v>
       </c>
       <c r="J33">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="K33">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="L33">
         <f>SUM($K$20:K33)</f>
-        <v>3.2</v>
+        <v>32</v>
       </c>
       <c r="M33">
         <v>24</v>
@@ -27094,19 +27094,19 @@
       </c>
       <c r="I34">
         <f>SUM($J$20:J34)</f>
-        <v>222</v>
+        <v>2220</v>
       </c>
       <c r="J34">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="K34">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <f>SUM($K$20:K34)</f>
-        <v>3.7</v>
+        <v>37</v>
       </c>
       <c r="M34">
         <v>30</v>
@@ -27833,7 +27833,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="17">
-        <f>E33/SUM($E$33:$E$38)</f>
+        <f t="shared" ref="F33:F38" si="3">E33/SUM($E$33:$E$38)</f>
         <v>0</v>
       </c>
       <c r="G33" t="b">
@@ -27857,7 +27857,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="17">
-        <f>E34/SUM($E$33:$E$38)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G34" t="b">
@@ -27881,7 +27881,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="17">
-        <f>E35/SUM($E$33:$E$38)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G35" t="b">
@@ -27905,7 +27905,7 @@
         <v>1000</v>
       </c>
       <c r="F36" s="17">
-        <f>E36/SUM($E$33:$E$38)</f>
+        <f t="shared" si="3"/>
         <v>0.434782608695652</v>
       </c>
       <c r="G36" t="b">
@@ -27929,7 +27929,7 @@
         <v>800</v>
       </c>
       <c r="F37" s="17">
-        <f>E37/SUM($E$33:$E$38)</f>
+        <f t="shared" si="3"/>
         <v>0.347826086956522</v>
       </c>
       <c r="G37" t="b">
@@ -27953,7 +27953,7 @@
         <v>500</v>
       </c>
       <c r="F38" s="17">
-        <f>E38/SUM($E$33:$E$38)</f>
+        <f t="shared" si="3"/>
         <v>0.217391304347826</v>
       </c>
       <c r="G38" t="b">
@@ -28011,7 +28011,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="17">
-        <f t="shared" ref="F42:F47" si="3">E42/10000</f>
+        <f t="shared" ref="F42:F47" si="4">E42/10000</f>
         <v>0</v>
       </c>
       <c r="G42" t="b">
@@ -28035,7 +28035,7 @@
         <v>6700</v>
       </c>
       <c r="F43" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.67</v>
       </c>
       <c r="G43" t="b">
@@ -28056,7 +28056,7 @@
         <v>2200</v>
       </c>
       <c r="F44" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.22</v>
       </c>
       <c r="G44" t="b">
@@ -28077,7 +28077,7 @@
         <v>900</v>
       </c>
       <c r="F45" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.09</v>
       </c>
       <c r="G45" t="b">
@@ -28098,7 +28098,7 @@
         <v>180</v>
       </c>
       <c r="F46" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.018</v>
       </c>
       <c r="G46" t="b">
@@ -28119,7 +28119,7 @@
         <v>20</v>
       </c>
       <c r="F47" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.002</v>
       </c>
       <c r="G47" t="b">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="12851" tabRatio="812" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -22642,7 +22642,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{6ee9f4dc-ba67-4172-8e97-6325004788a8}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{cc9b94e1-10b8-4681-ba51-208005966965}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22656,7 +22656,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{b3dcd9fa-6fee-47c7-9e06-f09e5e3062bc}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{11c639cb-7d41-472a-bf30-e6288d2e1a5c}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22670,7 +22670,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{a9a321f8-4698-4d0e-8a76-f87582882ee1}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{77a7fb3f-2135-4e35-b1a1-a7eba2ecc045}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22684,7 +22684,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{12f0b3e4-5ff1-4dab-9c15-8ad159cfaa26}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{1710f7a4-9cea-4018-987a-06ffd3718110}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22698,7 +22698,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{a896f263-bf0d-413e-a73a-485ba4bfeb1c}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{ce25aff1-1d39-42da-84eb-6e911686a559}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22712,7 +22712,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{94200d09-c3a4-486c-aa25-c2d2ce84ca4c}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{05bdb030-492c-4b1e-b55e-df641a7bc0ce}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22726,7 +22726,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{b82c3310-e43e-4007-b15b-a018446d634d}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{7460289d-0e01-47bf-9fc4-1ea086902fc0}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22740,7 +22740,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{9da26838-e4ce-46eb-9127-e0cf7ae6dae6}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{7b78b252-a15d-48c9-97a9-61e68c0afaac}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22754,7 +22754,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{e3d1ae88-53cb-4f02-8958-fc40a1e97364}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{14c66c72-7b4b-4a84-93e3-1e760d2416cd}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -34641,14 +34641,14 @@
     </row>
     <row r="271" spans="2:8">
       <c r="B271" s="21">
-        <f t="shared" ref="B271:B285" si="6">C271*100000+D271</f>
-        <v>400202003</v>
+        <f>C271*100000+D271</f>
+        <v>400202018</v>
       </c>
       <c r="C271">
         <v>4002</v>
       </c>
       <c r="D271">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="E271">
         <v>100</v>
@@ -34662,14 +34662,14 @@
     </row>
     <row r="272" spans="2:8">
       <c r="B272" s="21">
-        <f t="shared" si="6"/>
-        <v>400202009</v>
+        <f>C272*100000+D272</f>
+        <v>400201020</v>
       </c>
       <c r="C272">
         <v>4002</v>
       </c>
       <c r="D272">
-        <v>2009</v>
+        <v>1020</v>
       </c>
       <c r="E272">
         <v>100</v>
@@ -34683,7 +34683,7 @@
     </row>
     <row r="273" spans="2:7">
       <c r="B273" s="21">
-        <f t="shared" si="6"/>
+        <f>C273*100000+D273</f>
         <v>400202022</v>
       </c>
       <c r="C273">
@@ -34704,7 +34704,7 @@
     </row>
     <row r="274" spans="2:7">
       <c r="B274" s="21">
-        <f t="shared" si="6"/>
+        <f>C274*100000+D274</f>
         <v>400202029</v>
       </c>
       <c r="C274">
@@ -34724,235 +34724,37 @@
       </c>
     </row>
     <row r="275" spans="2:7">
-      <c r="B275" s="21">
-        <f t="shared" si="6"/>
-        <v>400202032</v>
-      </c>
-      <c r="C275">
-        <v>4002</v>
-      </c>
-      <c r="D275">
-        <v>2032</v>
-      </c>
-      <c r="E275">
-        <v>100</v>
-      </c>
-      <c r="F275" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G275" s="18">
-        <v>5</v>
-      </c>
+      <c r="B275" s="21"/>
     </row>
     <row r="276" spans="2:7">
-      <c r="B276" s="21">
-        <f t="shared" si="6"/>
-        <v>400205004</v>
-      </c>
-      <c r="C276">
-        <v>4002</v>
-      </c>
-      <c r="D276">
-        <v>5004</v>
-      </c>
-      <c r="E276">
-        <v>100</v>
-      </c>
-      <c r="F276" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G276" s="18">
-        <v>6</v>
-      </c>
+      <c r="B276" s="21"/>
     </row>
     <row r="277" spans="2:7">
-      <c r="B277" s="21">
-        <f t="shared" si="6"/>
-        <v>400206006</v>
-      </c>
-      <c r="C277">
-        <v>4002</v>
-      </c>
-      <c r="D277">
-        <v>6006</v>
-      </c>
-      <c r="E277">
-        <v>100</v>
-      </c>
-      <c r="F277" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G277" s="18">
-        <v>7</v>
-      </c>
+      <c r="B277" s="21"/>
     </row>
     <row r="278" spans="2:7">
-      <c r="B278" s="21">
-        <f t="shared" si="6"/>
-        <v>400208005</v>
-      </c>
-      <c r="C278">
-        <v>4002</v>
-      </c>
-      <c r="D278">
-        <v>8005</v>
-      </c>
-      <c r="E278">
-        <v>100</v>
-      </c>
-      <c r="F278" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G278" s="18">
-        <v>8</v>
-      </c>
+      <c r="B278" s="21"/>
     </row>
     <row r="279" spans="2:7">
-      <c r="B279" s="21">
-        <f t="shared" si="6"/>
-        <v>400206008</v>
-      </c>
-      <c r="C279">
-        <v>4002</v>
-      </c>
-      <c r="D279">
-        <v>6008</v>
-      </c>
-      <c r="E279">
-        <v>100</v>
-      </c>
-      <c r="F279" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G279" s="18">
-        <v>9</v>
-      </c>
+      <c r="B279" s="21"/>
     </row>
     <row r="280" spans="2:7">
-      <c r="B280" s="21">
-        <f t="shared" si="6"/>
-        <v>400207008</v>
-      </c>
-      <c r="C280">
-        <v>4002</v>
-      </c>
-      <c r="D280">
-        <v>7008</v>
-      </c>
-      <c r="E280">
-        <v>100</v>
-      </c>
-      <c r="F280" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G280" s="18">
-        <v>10</v>
-      </c>
+      <c r="B280" s="21"/>
     </row>
     <row r="281" spans="2:7">
-      <c r="B281" s="21">
-        <f t="shared" si="6"/>
-        <v>400208012</v>
-      </c>
-      <c r="C281">
-        <v>4002</v>
-      </c>
-      <c r="D281">
-        <v>8012</v>
-      </c>
-      <c r="E281">
-        <v>100</v>
-      </c>
-      <c r="F281" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G281" s="18">
-        <v>11</v>
-      </c>
+      <c r="B281" s="21"/>
     </row>
     <row r="282" spans="2:7">
-      <c r="B282" s="21">
-        <f t="shared" si="6"/>
-        <v>400201008</v>
-      </c>
-      <c r="C282">
-        <v>4002</v>
-      </c>
-      <c r="D282">
-        <v>1008</v>
-      </c>
-      <c r="E282">
-        <v>100</v>
-      </c>
-      <c r="F282" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G282" s="18">
-        <v>12</v>
-      </c>
+      <c r="B282" s="21"/>
     </row>
     <row r="283" spans="2:7">
-      <c r="B283" s="21">
-        <f t="shared" si="6"/>
-        <v>400201011</v>
-      </c>
-      <c r="C283">
-        <v>4002</v>
-      </c>
-      <c r="D283">
-        <v>1011</v>
-      </c>
-      <c r="E283">
-        <v>100</v>
-      </c>
-      <c r="F283" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G283" s="18">
-        <v>13</v>
-      </c>
+      <c r="B283" s="21"/>
     </row>
     <row r="284" spans="2:7">
-      <c r="B284" s="21">
-        <f t="shared" si="6"/>
-        <v>400201013</v>
-      </c>
-      <c r="C284">
-        <v>4002</v>
-      </c>
-      <c r="D284">
-        <v>1013</v>
-      </c>
-      <c r="E284">
-        <v>100</v>
-      </c>
-      <c r="F284" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G284" s="18">
-        <v>14</v>
-      </c>
+      <c r="B284" s="21"/>
     </row>
     <row r="285" spans="2:7">
-      <c r="B285" s="21">
-        <f t="shared" si="6"/>
-        <v>400202013</v>
-      </c>
-      <c r="C285">
-        <v>4002</v>
-      </c>
-      <c r="D285">
-        <v>2013</v>
-      </c>
-      <c r="E285">
-        <v>100</v>
-      </c>
-      <c r="F285" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G285" s="18">
-        <v>15</v>
-      </c>
+      <c r="B285" s="21"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H$1:H$1048576">

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -22618,7 +22618,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{5cd8f23a-fd2a-4d4c-8669-e72a915161df}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{8372462d-e797-4f75-9d41-d8387bc35fe1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22632,7 +22632,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{bc619b5b-3fe7-4113-9173-c84547240797}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{e5029054-174c-4952-ae8d-fe3332739aaa}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22646,7 +22646,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{b2a6a966-bc09-47c8-bdc1-e52804d2ee47}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{a2e036b5-41b2-4486-9c22-94b3fddd5a6c}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22660,7 +22660,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{719dcc94-2956-4c0e-a8a7-353b4f4fe1ca}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{28596754-e23a-4da2-86ce-9148aa0190a1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22674,7 +22674,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{db71dfd4-292d-416f-9655-3bd93b893ad4}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{416d3694-2cce-4b64-9f1e-2ecb39f0707d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22688,7 +22688,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{b7155e30-071e-45e0-8c0e-42ae47e9895c}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{3fbcbc3a-e0af-4b05-9413-c4be44912a8d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22702,7 +22702,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{7eea5c30-edb1-44b2-b9eb-69bd8e5c03a9}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{1ccc93b7-acad-4d7e-bea4-543fb733d2e5}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22716,7 +22716,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{ca1c20b9-ffbe-4e5a-848c-b4f2f52a3dd2}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{e3498915-f9b7-491b-9231-cbfcfa9864cb}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22730,7 +22730,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{ac386404-1c82-4862-9c46-7356706f9c8a}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{83bd4069-b790-49ab-aa3a-a5ef06b34b5a}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -24724,7 +24724,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" t="s">
         <v>827</v>
@@ -24765,7 +24765,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
         <v>827</v>
@@ -24806,7 +24806,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" t="s">
         <v>827</v>
@@ -24847,7 +24847,7 @@
         <v>3</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="s">
         <v>827</v>
@@ -24888,7 +24888,7 @@
         <v>3</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9" t="s">
         <v>827</v>
@@ -24929,7 +24929,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" t="s">
         <v>827</v>
@@ -24967,7 +24967,7 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L11" t="s">
         <v>841</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -22618,7 +22618,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{8372462d-e797-4f75-9d41-d8387bc35fe1}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{49f9efb7-d0c8-414c-ba11-0f8eb78e8198}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22632,7 +22632,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{e5029054-174c-4952-ae8d-fe3332739aaa}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{aee4a3b5-d03a-4f37-b79c-661959e8915a}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22646,7 +22646,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{a2e036b5-41b2-4486-9c22-94b3fddd5a6c}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{6b014290-d447-435e-9438-beb3b698dda1}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22660,7 +22660,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{28596754-e23a-4da2-86ce-9148aa0190a1}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{6b39e71d-f822-471f-af13-90a78768e535}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22674,7 +22674,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{416d3694-2cce-4b64-9f1e-2ecb39f0707d}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{dd047a01-9b84-4675-81f4-4909f280f661}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22688,7 +22688,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{3fbcbc3a-e0af-4b05-9413-c4be44912a8d}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{813bd0e1-ad11-4ced-b969-b78fd949d4ad}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22702,7 +22702,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{1ccc93b7-acad-4d7e-bea4-543fb733d2e5}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{55703813-4541-4659-976d-c7154c482115}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22716,7 +22716,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{e3498915-f9b7-491b-9231-cbfcfa9864cb}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{911ad369-3e85-4ce3-887f-60b13982560d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22730,7 +22730,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{83bd4069-b790-49ab-aa3a-a5ef06b34b5a}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{459c31c3-7ae8-43b9-a703-2f29ab1bae9e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -24838,7 +24838,7 @@
         <v>825</v>
       </c>
       <c r="H8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="I8" t="s">
         <v>826</v>
@@ -24879,7 +24879,7 @@
         <v>825</v>
       </c>
       <c r="H9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="I9" t="s">
         <v>826</v>
@@ -26206,7 +26206,7 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -26272,7 +26272,7 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -26338,7 +26338,7 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -26404,7 +26404,7 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -26470,7 +26470,7 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -26536,7 +26536,7 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -26602,7 +26602,7 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -26668,7 +26668,7 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -26734,7 +26734,7 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -26800,7 +26800,7 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -26866,7 +26866,7 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -26932,7 +26932,7 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -26998,7 +26998,7 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -27064,7 +27064,7 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -27130,7 +27130,7 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V34">
         <v>0</v>

--- a/luban-excels/xlsx/Items.xlsx
+++ b/luban-excels/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="12851" tabRatio="812" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -22642,7 +22642,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{cc9b94e1-10b8-4681-ba51-208005966965}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{1f2f65b8-84f7-4abb-b4ab-e76391d86592}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L62)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22656,7 +22656,7 @@
           <xm:sqref>L62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{11c639cb-7d41-472a-bf30-e6288d2e1a5c}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{752aede5-0836-471a-8f75-7c1f7c6fd7f9}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L63)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22670,7 +22670,7 @@
           <xm:sqref>L63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{77a7fb3f-2135-4e35-b1a1-a7eba2ecc045}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{8a3dec2d-f6fe-4512-9623-33bd0a254a9a}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L64)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22684,7 +22684,7 @@
           <xm:sqref>L64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{1710f7a4-9cea-4018-987a-06ffd3718110}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{19ad3260-f832-4893-a669-0c1479b0ef5f}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L70)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22698,7 +22698,7 @@
           <xm:sqref>L70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{ce25aff1-1d39-42da-84eb-6e911686a559}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{844be943-525f-4fe5-95fc-3a6f243a674e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L71)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22712,7 +22712,7 @@
           <xm:sqref>L71</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{05bdb030-492c-4b1e-b55e-df641a7bc0ce}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{a4a4377e-39b6-499b-8679-48178d0f0594}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L72)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22726,7 +22726,7 @@
           <xm:sqref>L72</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{7460289d-0e01-47bf-9fc4-1ea086902fc0}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{59456909-59a9-4470-a7cd-2aaf30496b60}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L13)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22740,7 +22740,7 @@
           <xm:sqref>L13:L16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{7b78b252-a15d-48c9-97a9-61e68c0afaac}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{ede9442d-536c-4e57-825a-016dc13975b5}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L17)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -22754,7 +22754,7 @@
           <xm:sqref>L17:L20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{14c66c72-7b4b-4a84-93e3-1e760d2416cd}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{52aeb0ed-bb8b-4f17-ac77-e31ad6fde35d}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -24748,7 +24748,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" t="s">
         <v>827</v>
@@ -24789,7 +24789,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
         <v>827</v>
@@ -24830,7 +24830,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" t="s">
         <v>827</v>
@@ -24862,7 +24862,7 @@
         <v>825</v>
       </c>
       <c r="H8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="I8" t="s">
         <v>826</v>
@@ -24871,7 +24871,7 @@
         <v>3</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="s">
         <v>827</v>
@@ -24903,7 +24903,7 @@
         <v>825</v>
       </c>
       <c r="H9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="I9" t="s">
         <v>826</v>
@@ -24912,7 +24912,7 @@
         <v>3</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9" t="s">
         <v>827</v>
@@ -24953,7 +24953,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" t="s">
         <v>827</v>
@@ -24991,7 +24991,7 @@
         <v>3</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L11" t="s">
         <v>841</v>
@@ -25032,7 +25032,7 @@
         <v>3</v>
       </c>
       <c r="K12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L12" t="s">
         <v>827</v>
@@ -26271,7 +26271,7 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -26403,7 +26403,7 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -26469,7 +26469,7 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -26535,7 +26535,7 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -26601,7 +26601,7 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -26667,7 +26667,7 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -26733,7 +26733,7 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -26799,7 +26799,7 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -26865,7 +26865,7 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -26931,7 +26931,7 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -26997,7 +26997,7 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -27063,7 +27063,7 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -27129,7 +27129,7 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -27195,7 +27195,7 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V34">
         <v>0</v>
